--- a/03_Output/final_run/master_panel_clean.xlsx
+++ b/03_Output/final_run/master_panel_clean.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M217"/>
+  <dimension ref="A1:L217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,50 +434,45 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Employment In HTEC</t>
+          <t>Internet Access</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Internet Access</t>
+          <t>Internet Purchases</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Internet Purchases</t>
+          <t>Internet Use</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Internet Use</t>
+          <t>R&amp;D expenditure</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>R&amp;D expenditure</t>
+          <t>Tertiary_Education</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tertiary_Education</t>
+          <t>Cloud Computing</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Cloud Computing</t>
+          <t>Fixed_Broadband</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Fixed_Broadband</t>
+          <t>Secure_Servers</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
-        <is>
-          <t>Secure_Servers</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
         <is>
           <t>HighTech_Exports</t>
         </is>
@@ -496,33 +491,30 @@
         <v>37012.2</v>
       </c>
       <c r="D2" t="n">
-        <v>4244.9</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>88.79000000000001</v>
+        <v>61.56</v>
       </c>
       <c r="F2" t="n">
-        <v>61.56</v>
+        <v>87.94</v>
       </c>
       <c r="G2" t="n">
-        <v>87.94</v>
+        <v>1286.898</v>
       </c>
       <c r="H2" t="n">
-        <v>1286.898</v>
+        <v>80.7</v>
       </c>
       <c r="I2" t="n">
-        <v>80.7</v>
+        <v>19.2</v>
       </c>
       <c r="J2" t="n">
-        <v>19.2</v>
+        <v>28.5425998928488</v>
       </c>
       <c r="K2" t="n">
-        <v>28.5425998928488</v>
+        <v>7431.71463561626</v>
       </c>
       <c r="L2" t="n">
-        <v>7431.71463561626</v>
-      </c>
-      <c r="M2" t="n">
         <v>12.8851997037889</v>
       </c>
     </row>
@@ -539,33 +531,30 @@
         <v>38419.4</v>
       </c>
       <c r="D3" t="n">
-        <v>4303.9</v>
+        <v>88.78</v>
       </c>
       <c r="E3" t="n">
-        <v>88.78</v>
+        <v>60.3</v>
       </c>
       <c r="F3" t="n">
-        <v>60.3</v>
+        <v>87.48</v>
       </c>
       <c r="G3" t="n">
-        <v>87.48</v>
+        <v>1350.22</v>
       </c>
       <c r="H3" t="n">
-        <v>1350.22</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>81.09999999999999</v>
+        <v>20.59</v>
       </c>
       <c r="J3" t="n">
-        <v>20.59</v>
+        <v>28.5150396136468</v>
       </c>
       <c r="K3" t="n">
-        <v>28.5150396136468</v>
+        <v>16705.0109377038</v>
       </c>
       <c r="L3" t="n">
-        <v>16705.0109377038</v>
-      </c>
-      <c r="M3" t="n">
         <v>11.6500759838374</v>
       </c>
     </row>
@@ -582,33 +571,30 @@
         <v>39263.8</v>
       </c>
       <c r="D4" t="n">
-        <v>4338.2</v>
+        <v>89.91</v>
       </c>
       <c r="E4" t="n">
-        <v>89.91</v>
+        <v>62.41</v>
       </c>
       <c r="F4" t="n">
-        <v>62.41</v>
+        <v>87.75</v>
       </c>
       <c r="G4" t="n">
-        <v>87.75</v>
+        <v>1404.396</v>
       </c>
       <c r="H4" t="n">
-        <v>1404.396</v>
+        <v>81.3</v>
       </c>
       <c r="I4" t="n">
-        <v>81.3</v>
+        <v>28.1</v>
       </c>
       <c r="J4" t="n">
-        <v>28.1</v>
+        <v>28.3631930003301</v>
       </c>
       <c r="K4" t="n">
-        <v>28.3631930003301</v>
+        <v>26298.32250741</v>
       </c>
       <c r="L4" t="n">
-        <v>26298.32250741</v>
-      </c>
-      <c r="M4" t="n">
         <v>11.4825348767666</v>
       </c>
     </row>
@@ -625,33 +611,30 @@
         <v>37385.6</v>
       </c>
       <c r="D5" t="n">
-        <v>4281.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>90.40000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="F5" t="n">
-        <v>66.3</v>
+        <v>87.53</v>
       </c>
       <c r="G5" t="n">
-        <v>87.53</v>
+        <v>1370.513</v>
       </c>
       <c r="H5" t="n">
-        <v>1370.513</v>
+        <v>81.3</v>
       </c>
       <c r="I5" t="n">
-        <v>81.3</v>
+        <v>35.61</v>
       </c>
       <c r="J5" t="n">
-        <v>35.61</v>
+        <v>29.2106456326106</v>
       </c>
       <c r="K5" t="n">
-        <v>29.2106456326106</v>
+        <v>33802.6911703487</v>
       </c>
       <c r="L5" t="n">
-        <v>33802.6911703487</v>
-      </c>
-      <c r="M5" t="n">
         <v>12.2718957660446</v>
       </c>
     </row>
@@ -668,33 +651,30 @@
         <v>40185.6</v>
       </c>
       <c r="D6" t="n">
-        <v>4295.9</v>
+        <v>95</v>
       </c>
       <c r="E6" t="n">
-        <v>95</v>
+        <v>63.17</v>
       </c>
       <c r="F6" t="n">
-        <v>63.17</v>
+        <v>92.53</v>
       </c>
       <c r="G6" t="n">
-        <v>92.53</v>
+        <v>1480.576</v>
       </c>
       <c r="H6" t="n">
-        <v>1480.576</v>
+        <v>81.5</v>
       </c>
       <c r="I6" t="n">
-        <v>81.5</v>
+        <v>37</v>
       </c>
       <c r="J6" t="n">
-        <v>37</v>
+        <v>29.2537339731419</v>
       </c>
       <c r="K6" t="n">
-        <v>29.2537339731419</v>
+        <v>39775.2427840872</v>
       </c>
       <c r="L6" t="n">
-        <v>39775.2427840872</v>
-      </c>
-      <c r="M6" t="n">
         <v>11.017122140568</v>
       </c>
     </row>
@@ -711,33 +691,30 @@
         <v>44569.5</v>
       </c>
       <c r="D7" t="n">
-        <v>4430.9</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>93.15000000000001</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>65.65000000000001</v>
+        <v>93.61</v>
       </c>
       <c r="G7" t="n">
-        <v>93.61</v>
+        <v>1585.55</v>
       </c>
       <c r="H7" t="n">
-        <v>1585.55</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>81.40000000000001</v>
+        <v>39.76000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>39.76000000000001</v>
+        <v>29.2342573265435</v>
       </c>
       <c r="K7" t="n">
-        <v>29.2342573265435</v>
+        <v>39544.447259748</v>
       </c>
       <c r="L7" t="n">
-        <v>39544.447259748</v>
-      </c>
-      <c r="M7" t="n">
         <v>14.9141702472602</v>
       </c>
     </row>
@@ -754,33 +731,30 @@
         <v>46390.3</v>
       </c>
       <c r="D8" t="n">
-        <v>4471.8</v>
+        <v>94.98</v>
       </c>
       <c r="E8" t="n">
-        <v>94.98</v>
+        <v>72.17</v>
       </c>
       <c r="F8" t="n">
-        <v>72.17</v>
+        <v>95.33</v>
       </c>
       <c r="G8" t="n">
-        <v>95.33</v>
+        <v>1691.897</v>
       </c>
       <c r="H8" t="n">
-        <v>1691.897</v>
+        <v>81.5</v>
       </c>
       <c r="I8" t="n">
-        <v>81.5</v>
+        <v>42.52</v>
       </c>
       <c r="J8" t="n">
-        <v>42.52</v>
+        <v>29.3725409835617</v>
       </c>
       <c r="K8" t="n">
-        <v>29.3725409835617</v>
+        <v>42281.0014410145</v>
       </c>
       <c r="L8" t="n">
-        <v>42281.0014410145</v>
-      </c>
-      <c r="M8" t="n">
         <v>15.9232697881169</v>
       </c>
     </row>
@@ -797,33 +771,30 @@
         <v>47527.5</v>
       </c>
       <c r="D9" t="n">
-        <v>4476.5</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>94.95999999999999</v>
+        <v>70.73</v>
       </c>
       <c r="F9" t="n">
-        <v>70.73</v>
+        <v>94.92</v>
       </c>
       <c r="G9" t="n">
-        <v>94.92</v>
+        <v>1761.339</v>
       </c>
       <c r="H9" t="n">
-        <v>1761.339</v>
+        <v>81.7</v>
       </c>
       <c r="I9" t="n">
-        <v>81.7</v>
+        <v>42.52</v>
       </c>
       <c r="J9" t="n">
-        <v>42.52</v>
+        <v>30.12779672163</v>
       </c>
       <c r="K9" t="n">
-        <v>30.12779672163</v>
+        <v>47132.0383936251</v>
       </c>
       <c r="L9" t="n">
-        <v>47132.0383936251</v>
-      </c>
-      <c r="M9" t="n">
         <v>18.4525766859019</v>
       </c>
     </row>
@@ -840,33 +811,30 @@
         <v>34519.6</v>
       </c>
       <c r="D10" t="n">
-        <v>4629</v>
+        <v>85.97</v>
       </c>
       <c r="E10" t="n">
-        <v>85.97</v>
+        <v>59.63</v>
       </c>
       <c r="F10" t="n">
-        <v>59.63</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>87.68000000000001</v>
+        <v>1045.478</v>
       </c>
       <c r="H10" t="n">
-        <v>1045.478</v>
+        <v>72.8</v>
       </c>
       <c r="I10" t="n">
-        <v>72.8</v>
+        <v>36.72</v>
       </c>
       <c r="J10" t="n">
-        <v>36.72</v>
+        <v>38.4911160919085</v>
       </c>
       <c r="K10" t="n">
-        <v>38.4911160919085</v>
+        <v>8300.544045190411</v>
       </c>
       <c r="L10" t="n">
-        <v>8300.544045190411</v>
-      </c>
-      <c r="M10" t="n">
         <v>11.4917903557909</v>
       </c>
     </row>
@@ -883,33 +851,30 @@
         <v>35579.3</v>
       </c>
       <c r="D11" t="n">
-        <v>4744.1</v>
+        <v>87.27</v>
       </c>
       <c r="E11" t="n">
-        <v>87.27</v>
+        <v>60.52</v>
       </c>
       <c r="F11" t="n">
-        <v>60.52</v>
+        <v>88.66</v>
       </c>
       <c r="G11" t="n">
-        <v>88.66</v>
+        <v>1154.376</v>
       </c>
       <c r="H11" t="n">
-        <v>1154.376</v>
+        <v>73.7</v>
       </c>
       <c r="I11" t="n">
-        <v>73.7</v>
+        <v>36.29</v>
       </c>
       <c r="J11" t="n">
-        <v>36.29</v>
+        <v>39.4006967604533</v>
       </c>
       <c r="K11" t="n">
-        <v>39.4006967604533</v>
+        <v>13973.2427973124</v>
       </c>
       <c r="L11" t="n">
-        <v>13973.2427973124</v>
-      </c>
-      <c r="M11" t="n">
         <v>11.7058640594516</v>
       </c>
     </row>
@@ -926,33 +891,30 @@
         <v>36884.8</v>
       </c>
       <c r="D12" t="n">
-        <v>4819.5</v>
+        <v>89.73</v>
       </c>
       <c r="E12" t="n">
-        <v>89.73</v>
+        <v>66.16</v>
       </c>
       <c r="F12" t="n">
-        <v>66.16</v>
+        <v>90.28</v>
       </c>
       <c r="G12" t="n">
-        <v>90.28</v>
+        <v>1319.006</v>
       </c>
       <c r="H12" t="n">
-        <v>1319.006</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>74.09999999999999</v>
+        <v>43.13</v>
       </c>
       <c r="J12" t="n">
-        <v>43.13</v>
+        <v>39.9517850127817</v>
       </c>
       <c r="K12" t="n">
-        <v>39.9517850127817</v>
+        <v>19655.5307781892</v>
       </c>
       <c r="L12" t="n">
-        <v>19655.5307781892</v>
-      </c>
-      <c r="M12" t="n">
         <v>14.1440138847213</v>
       </c>
     </row>
@@ -969,33 +931,30 @@
         <v>35850.5</v>
       </c>
       <c r="D13" t="n">
-        <v>4789.8</v>
+        <v>90.86</v>
       </c>
       <c r="E13" t="n">
-        <v>90.86</v>
+        <v>72.72</v>
       </c>
       <c r="F13" t="n">
-        <v>72.72</v>
+        <v>91.53</v>
       </c>
       <c r="G13" t="n">
-        <v>91.53</v>
+        <v>1355.634</v>
       </c>
       <c r="H13" t="n">
-        <v>1355.634</v>
+        <v>75</v>
       </c>
       <c r="I13" t="n">
-        <v>75</v>
+        <v>49.97</v>
       </c>
       <c r="J13" t="n">
-        <v>49.97</v>
+        <v>41.0239697084264</v>
       </c>
       <c r="K13" t="n">
-        <v>41.0239697084264</v>
+        <v>24215.3210215031</v>
       </c>
       <c r="L13" t="n">
-        <v>24215.3210215031</v>
-      </c>
-      <c r="M13" t="n">
         <v>15.2618615789713</v>
       </c>
     </row>
@@ -1012,33 +971,30 @@
         <v>38699.2</v>
       </c>
       <c r="D14" t="n">
-        <v>4847.6</v>
+        <v>91.97</v>
       </c>
       <c r="E14" t="n">
-        <v>91.97</v>
+        <v>75.19</v>
       </c>
       <c r="F14" t="n">
-        <v>75.19</v>
+        <v>92.79000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>92.79000000000001</v>
+        <v>1491.629</v>
       </c>
       <c r="H14" t="n">
-        <v>1491.629</v>
+        <v>77.3</v>
       </c>
       <c r="I14" t="n">
-        <v>77.3</v>
+        <v>49.1</v>
       </c>
       <c r="J14" t="n">
-        <v>49.1</v>
+        <v>43.0218054966431</v>
       </c>
       <c r="K14" t="n">
-        <v>43.0218054966431</v>
+        <v>28369.365438783</v>
       </c>
       <c r="L14" t="n">
-        <v>28369.365438783</v>
-      </c>
-      <c r="M14" t="n">
         <v>21.3799638763737</v>
       </c>
     </row>
@@ -1055,33 +1011,30 @@
         <v>42520.1</v>
       </c>
       <c r="D15" t="n">
-        <v>4984.2</v>
+        <v>94.44</v>
       </c>
       <c r="E15" t="n">
-        <v>94.44</v>
+        <v>74.83</v>
       </c>
       <c r="F15" t="n">
-        <v>74.83</v>
+        <v>94.01000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>94.01000000000001</v>
+        <v>1550.728</v>
       </c>
       <c r="H15" t="n">
-        <v>1550.728</v>
+        <v>78.3</v>
       </c>
       <c r="I15" t="n">
-        <v>78.3</v>
+        <v>48.105</v>
       </c>
       <c r="J15" t="n">
-        <v>48.105</v>
+        <v>43.5657139519422</v>
       </c>
       <c r="K15" t="n">
-        <v>43.5657139519422</v>
+        <v>30850.8151822613</v>
       </c>
       <c r="L15" t="n">
-        <v>30850.8151822613</v>
-      </c>
-      <c r="M15" t="n">
         <v>22.8179135173265</v>
       </c>
     </row>
@@ -1098,33 +1051,30 @@
         <v>45365.7</v>
       </c>
       <c r="D16" t="n">
-        <v>5021.7</v>
+        <v>94.48</v>
       </c>
       <c r="E16" t="n">
-        <v>94.48</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>75.26000000000001</v>
+        <v>94.63</v>
       </c>
       <c r="G16" t="n">
-        <v>94.63</v>
+        <v>1661.43</v>
       </c>
       <c r="H16" t="n">
-        <v>1661.43</v>
+        <v>77.5</v>
       </c>
       <c r="I16" t="n">
-        <v>77.5</v>
+        <v>47.11</v>
       </c>
       <c r="J16" t="n">
-        <v>47.11</v>
+        <v>43.7026445985633</v>
       </c>
       <c r="K16" t="n">
-        <v>43.7026445985633</v>
+        <v>33664.5855592207</v>
       </c>
       <c r="L16" t="n">
-        <v>33664.5855592207</v>
-      </c>
-      <c r="M16" t="n">
         <v>18.6668227645892</v>
       </c>
     </row>
@@ -1141,33 +1091,30 @@
         <v>46587.9</v>
       </c>
       <c r="D17" t="n">
-        <v>5056.3</v>
+        <v>94.62</v>
       </c>
       <c r="E17" t="n">
-        <v>94.62</v>
+        <v>76.08</v>
       </c>
       <c r="F17" t="n">
-        <v>76.08</v>
+        <v>95.78</v>
       </c>
       <c r="G17" t="n">
-        <v>95.78</v>
+        <v>1765.982</v>
       </c>
       <c r="H17" t="n">
-        <v>1765.982</v>
+        <v>77.5</v>
       </c>
       <c r="I17" t="n">
-        <v>77.5</v>
+        <v>47.11</v>
       </c>
       <c r="J17" t="n">
-        <v>47.11</v>
+        <v>44.2321563183446</v>
       </c>
       <c r="K17" t="n">
-        <v>44.2321563183446</v>
+        <v>36731.8766702</v>
       </c>
       <c r="L17" t="n">
-        <v>36731.8766702</v>
-      </c>
-      <c r="M17" t="n">
         <v>20.3921453422236</v>
       </c>
     </row>
@@ -1184,33 +1131,30 @@
         <v>15329.3</v>
       </c>
       <c r="D18" t="n">
-        <v>3146.2</v>
+        <v>67.33</v>
       </c>
       <c r="E18" t="n">
-        <v>67.33</v>
+        <v>17.73</v>
       </c>
       <c r="F18" t="n">
-        <v>17.73</v>
+        <v>63.41</v>
       </c>
       <c r="G18" t="n">
-        <v>63.41</v>
+        <v>56.75</v>
       </c>
       <c r="H18" t="n">
-        <v>56.75</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>78.59999999999999</v>
+        <v>6.74</v>
       </c>
       <c r="J18" t="n">
-        <v>6.74</v>
+        <v>25.3925159519229</v>
       </c>
       <c r="K18" t="n">
-        <v>25.3925159519229</v>
+        <v>33602.2746046575</v>
       </c>
       <c r="L18" t="n">
-        <v>33602.2746046575</v>
-      </c>
-      <c r="M18" t="n">
         <v>9.63608854549453</v>
       </c>
     </row>
@@ -1227,33 +1171,30 @@
         <v>16273.7</v>
       </c>
       <c r="D19" t="n">
-        <v>3148</v>
+        <v>72.13</v>
       </c>
       <c r="E19" t="n">
-        <v>72.13</v>
+        <v>20.76</v>
       </c>
       <c r="F19" t="n">
-        <v>20.76</v>
+        <v>64.78</v>
       </c>
       <c r="G19" t="n">
-        <v>64.78</v>
+        <v>62.719</v>
       </c>
       <c r="H19" t="n">
-        <v>62.719</v>
+        <v>78.5</v>
       </c>
       <c r="I19" t="n">
-        <v>78.5</v>
+        <v>6.58</v>
       </c>
       <c r="J19" t="n">
-        <v>6.58</v>
+        <v>27.103417988838</v>
       </c>
       <c r="K19" t="n">
-        <v>27.103417988838</v>
+        <v>40013.7211699711</v>
       </c>
       <c r="L19" t="n">
-        <v>40013.7211699711</v>
-      </c>
-      <c r="M19" t="n">
         <v>10.3728902592084</v>
       </c>
     </row>
@@ -1270,33 +1211,30 @@
         <v>17407.9</v>
       </c>
       <c r="D20" t="n">
-        <v>3039.9</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>75.06999999999999</v>
+        <v>21.71</v>
       </c>
       <c r="F20" t="n">
-        <v>21.71</v>
+        <v>67.95</v>
       </c>
       <c r="G20" t="n">
-        <v>67.95</v>
+        <v>76.887</v>
       </c>
       <c r="H20" t="n">
-        <v>76.887</v>
+        <v>78.5</v>
       </c>
       <c r="I20" t="n">
-        <v>78.5</v>
+        <v>7.465</v>
       </c>
       <c r="J20" t="n">
-        <v>7.465</v>
+        <v>28.8836779290396</v>
       </c>
       <c r="K20" t="n">
-        <v>28.8836779290396</v>
+        <v>42421.4331982313</v>
       </c>
       <c r="L20" t="n">
-        <v>42421.4331982313</v>
-      </c>
-      <c r="M20" t="n">
         <v>10.8523101760506</v>
       </c>
     </row>
@@ -1313,33 +1251,30 @@
         <v>17473</v>
       </c>
       <c r="D21" t="n">
-        <v>2927.7</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>78.84999999999999</v>
+        <v>30.95</v>
       </c>
       <c r="F21" t="n">
-        <v>30.95</v>
+        <v>70.16</v>
       </c>
       <c r="G21" t="n">
-        <v>70.16</v>
+        <v>79.684</v>
       </c>
       <c r="H21" t="n">
-        <v>79.684</v>
+        <v>79</v>
       </c>
       <c r="I21" t="n">
-        <v>79</v>
+        <v>8.35</v>
       </c>
       <c r="J21" t="n">
-        <v>8.35</v>
+        <v>30.5042854761098</v>
       </c>
       <c r="K21" t="n">
-        <v>30.5042854761098</v>
+        <v>50889.4016757914</v>
       </c>
       <c r="L21" t="n">
-        <v>50889.4016757914</v>
-      </c>
-      <c r="M21" t="n">
         <v>11.3032725784223</v>
       </c>
     </row>
@@ -1356,33 +1291,30 @@
         <v>19748.1</v>
       </c>
       <c r="D22" t="n">
-        <v>2873.5</v>
+        <v>83.53</v>
       </c>
       <c r="E22" t="n">
-        <v>83.53</v>
+        <v>33.04</v>
       </c>
       <c r="F22" t="n">
-        <v>33.04</v>
+        <v>75.27</v>
       </c>
       <c r="G22" t="n">
-        <v>75.27</v>
+        <v>84.06699999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>84.06699999999999</v>
+        <v>79.5</v>
       </c>
       <c r="I22" t="n">
-        <v>79.5</v>
+        <v>10.04</v>
       </c>
       <c r="J22" t="n">
-        <v>10.04</v>
+        <v>32.7688420838347</v>
       </c>
       <c r="K22" t="n">
-        <v>32.7688420838347</v>
+        <v>55100.7245553879</v>
       </c>
       <c r="L22" t="n">
-        <v>55100.7245553879</v>
-      </c>
-      <c r="M22" t="n">
         <v>10.9244735738213</v>
       </c>
     </row>
@@ -1399,33 +1331,30 @@
         <v>22421.1</v>
       </c>
       <c r="D23" t="n">
-        <v>2934.9</v>
+        <v>87.31</v>
       </c>
       <c r="E23" t="n">
-        <v>87.31</v>
+        <v>40.54</v>
       </c>
       <c r="F23" t="n">
-        <v>40.54</v>
+        <v>79.13</v>
       </c>
       <c r="G23" t="n">
-        <v>79.13</v>
+        <v>99.82599999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>99.82599999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>80.40000000000001</v>
+        <v>12.35</v>
       </c>
       <c r="J23" t="n">
-        <v>12.35</v>
+        <v>34.9667968772891</v>
       </c>
       <c r="K23" t="n">
-        <v>34.9667968772891</v>
+        <v>57819.5501165721</v>
       </c>
       <c r="L23" t="n">
-        <v>57819.5501165721</v>
-      </c>
-      <c r="M23" t="n">
         <v>10.3826775418569</v>
       </c>
     </row>
@@ -1442,33 +1371,30 @@
         <v>24253.5</v>
       </c>
       <c r="D24" t="n">
-        <v>2924</v>
+        <v>88.5</v>
       </c>
       <c r="E24" t="n">
-        <v>88.5</v>
+        <v>45.19</v>
       </c>
       <c r="F24" t="n">
-        <v>45.19</v>
+        <v>80.39</v>
       </c>
       <c r="G24" t="n">
-        <v>80.39</v>
+        <v>116.371</v>
       </c>
       <c r="H24" t="n">
-        <v>116.371</v>
+        <v>81.3</v>
       </c>
       <c r="I24" t="n">
-        <v>81.3</v>
+        <v>14.66</v>
       </c>
       <c r="J24" t="n">
-        <v>14.66</v>
+        <v>37.0235717545079</v>
       </c>
       <c r="K24" t="n">
-        <v>37.0235717545079</v>
+        <v>54104.3676383629</v>
       </c>
       <c r="L24" t="n">
-        <v>54104.3676383629</v>
-      </c>
-      <c r="M24" t="n">
         <v>12.0578944173221</v>
       </c>
     </row>
@@ -1485,33 +1411,30 @@
         <v>26324.2</v>
       </c>
       <c r="D25" t="n">
-        <v>2925.4</v>
+        <v>92.12</v>
       </c>
       <c r="E25" t="n">
-        <v>92.12</v>
+        <v>49.78</v>
       </c>
       <c r="F25" t="n">
-        <v>49.78</v>
+        <v>82.44</v>
       </c>
       <c r="G25" t="n">
-        <v>82.44</v>
+        <v>124.871</v>
       </c>
       <c r="H25" t="n">
-        <v>124.871</v>
+        <v>82.8</v>
       </c>
       <c r="I25" t="n">
-        <v>82.8</v>
+        <v>14.66</v>
       </c>
       <c r="J25" t="n">
-        <v>14.66</v>
+        <v>37.0235717545079</v>
       </c>
       <c r="K25" t="n">
-        <v>37.0235717545079</v>
+        <v>50750.6030113542</v>
       </c>
       <c r="L25" t="n">
-        <v>50750.6030113542</v>
-      </c>
-      <c r="M25" t="n">
         <v>13.4299683659831</v>
       </c>
     </row>
@@ -1528,33 +1451,30 @@
         <v>19169.3</v>
       </c>
       <c r="D26" t="n">
-        <v>1559.7</v>
+        <v>76.45</v>
       </c>
       <c r="E26" t="n">
-        <v>76.45</v>
+        <v>28.78</v>
       </c>
       <c r="F26" t="n">
-        <v>28.78</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G26" t="n">
-        <v>67.09999999999999</v>
+        <v>103.834</v>
       </c>
       <c r="H26" t="n">
-        <v>103.834</v>
+        <v>80.2</v>
       </c>
       <c r="I26" t="n">
-        <v>80.2</v>
+        <v>28.91</v>
       </c>
       <c r="J26" t="n">
-        <v>28.91</v>
+        <v>26.865096097274</v>
       </c>
       <c r="K26" t="n">
-        <v>26.865096097274</v>
+        <v>14908.4217451991</v>
       </c>
       <c r="L26" t="n">
-        <v>14908.4217451991</v>
-      </c>
-      <c r="M26" t="n">
         <v>8.738101360163959</v>
       </c>
     </row>
@@ -1571,33 +1491,30 @@
         <v>20216.2</v>
       </c>
       <c r="D27" t="n">
-        <v>1570.7</v>
+        <v>81.52</v>
       </c>
       <c r="E27" t="n">
-        <v>81.52</v>
+        <v>35.21</v>
       </c>
       <c r="F27" t="n">
-        <v>35.21</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>75.29000000000001</v>
+        <v>124.991</v>
       </c>
       <c r="H27" t="n">
-        <v>124.991</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>81.40000000000001</v>
+        <v>28.53</v>
       </c>
       <c r="J27" t="n">
-        <v>28.53</v>
+        <v>28.0156020023514</v>
       </c>
       <c r="K27" t="n">
-        <v>28.0156020023514</v>
+        <v>20040.4886211932</v>
       </c>
       <c r="L27" t="n">
-        <v>20040.4886211932</v>
-      </c>
-      <c r="M27" t="n">
         <v>8.837531015021311</v>
       </c>
     </row>
@@ -1614,33 +1531,30 @@
         <v>21518.8</v>
       </c>
       <c r="D28" t="n">
-        <v>1584.5</v>
+        <v>80.52</v>
       </c>
       <c r="E28" t="n">
-        <v>80.52</v>
+        <v>45.3</v>
       </c>
       <c r="F28" t="n">
-        <v>45.3</v>
+        <v>79.08</v>
       </c>
       <c r="G28" t="n">
-        <v>79.08</v>
+        <v>151.374</v>
       </c>
       <c r="H28" t="n">
-        <v>151.374</v>
+        <v>82</v>
       </c>
       <c r="I28" t="n">
-        <v>82</v>
+        <v>32.015</v>
       </c>
       <c r="J28" t="n">
-        <v>32.015</v>
+        <v>28.9682951804841</v>
       </c>
       <c r="K28" t="n">
-        <v>28.9682951804841</v>
+        <v>23423.1109107989</v>
       </c>
       <c r="L28" t="n">
-        <v>23423.1109107989</v>
-      </c>
-      <c r="M28" t="n">
         <v>8.289270835363959</v>
       </c>
     </row>
@@ -1657,33 +1571,30 @@
         <v>20213.9</v>
       </c>
       <c r="D29" t="n">
-        <v>1559.7</v>
+        <v>85</v>
       </c>
       <c r="E29" t="n">
-        <v>85</v>
+        <v>55.01</v>
       </c>
       <c r="F29" t="n">
-        <v>55.01</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>78.31999999999999</v>
+        <v>159.295</v>
       </c>
       <c r="H29" t="n">
-        <v>159.295</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>82.59999999999999</v>
+        <v>35.5</v>
       </c>
       <c r="J29" t="n">
-        <v>35.5</v>
+        <v>26.0744550144438</v>
       </c>
       <c r="K29" t="n">
-        <v>26.0744550144438</v>
+        <v>23114.2663416284</v>
       </c>
       <c r="L29" t="n">
-        <v>23114.2663416284</v>
-      </c>
-      <c r="M29" t="n">
         <v>9.68004103299381</v>
       </c>
     </row>
@@ -1700,33 +1611,30 @@
         <v>23588.3</v>
       </c>
       <c r="D30" t="n">
-        <v>1581.4</v>
+        <v>86.09</v>
       </c>
       <c r="E30" t="n">
-        <v>86.09</v>
+        <v>57.35</v>
       </c>
       <c r="F30" t="n">
-        <v>57.35</v>
+        <v>81.25</v>
       </c>
       <c r="G30" t="n">
-        <v>81.25</v>
+        <v>186.276</v>
       </c>
       <c r="H30" t="n">
-        <v>186.276</v>
+        <v>83.2</v>
       </c>
       <c r="I30" t="n">
-        <v>83.2</v>
+        <v>35.7</v>
       </c>
       <c r="J30" t="n">
-        <v>35.7</v>
+        <v>26.7157501000099</v>
       </c>
       <c r="K30" t="n">
-        <v>26.7157501000099</v>
+        <v>25479.3720309535</v>
       </c>
       <c r="L30" t="n">
-        <v>25479.3720309535</v>
-      </c>
-      <c r="M30" t="n">
         <v>9.60673351412275</v>
       </c>
     </row>
@@ -1743,33 +1651,30 @@
         <v>26007.7</v>
       </c>
       <c r="D31" t="n">
-        <v>1603.3</v>
+        <v>85.52</v>
       </c>
       <c r="E31" t="n">
-        <v>85.52</v>
+        <v>56.15</v>
       </c>
       <c r="F31" t="n">
-        <v>56.15</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>82.06999999999999</v>
+        <v>248.396</v>
       </c>
       <c r="H31" t="n">
-        <v>248.396</v>
+        <v>84</v>
       </c>
       <c r="I31" t="n">
-        <v>84</v>
+        <v>38.87</v>
       </c>
       <c r="J31" t="n">
-        <v>38.87</v>
+        <v>27.6606739600213</v>
       </c>
       <c r="K31" t="n">
-        <v>27.6606739600213</v>
+        <v>29826.9470627582</v>
       </c>
       <c r="L31" t="n">
-        <v>29826.9470627582</v>
-      </c>
-      <c r="M31" t="n">
         <v>12.0638540428638</v>
       </c>
     </row>
@@ -1786,33 +1691,30 @@
         <v>29846.2</v>
       </c>
       <c r="D32" t="n">
-        <v>1617.5</v>
+        <v>89.56</v>
       </c>
       <c r="E32" t="n">
-        <v>89.56</v>
+        <v>59.14</v>
       </c>
       <c r="F32" t="n">
-        <v>59.14</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>83.40000000000001</v>
+        <v>280.952</v>
       </c>
       <c r="H32" t="n">
-        <v>280.952</v>
+        <v>84.8</v>
       </c>
       <c r="I32" t="n">
-        <v>84.8</v>
+        <v>42.04</v>
       </c>
       <c r="J32" t="n">
-        <v>42.04</v>
+        <v>28.4709561519529</v>
       </c>
       <c r="K32" t="n">
-        <v>28.4709561519529</v>
+        <v>29421.5643448716</v>
       </c>
       <c r="L32" t="n">
-        <v>29421.5643448716</v>
-      </c>
-      <c r="M32" t="n">
         <v>11.0335908814715</v>
       </c>
     </row>
@@ -1829,33 +1731,30 @@
         <v>31053</v>
       </c>
       <c r="D33" t="n">
-        <v>1681.4</v>
+        <v>88.37</v>
       </c>
       <c r="E33" t="n">
-        <v>88.37</v>
+        <v>59.3</v>
       </c>
       <c r="F33" t="n">
-        <v>59.3</v>
+        <v>83.63</v>
       </c>
       <c r="G33" t="n">
-        <v>83.63</v>
+        <v>300.367</v>
       </c>
       <c r="H33" t="n">
-        <v>300.367</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>85.59999999999999</v>
+        <v>37.85</v>
       </c>
       <c r="J33" t="n">
-        <v>37.85</v>
+        <v>29.5997367962687</v>
       </c>
       <c r="K33" t="n">
-        <v>29.5997367962687</v>
+        <v>29458.6415601883</v>
       </c>
       <c r="L33" t="n">
-        <v>29458.6415601883</v>
-      </c>
-      <c r="M33" t="n">
         <v>11.6739199311189</v>
       </c>
     </row>
@@ -1872,33 +1771,30 @@
         <v>25941.8</v>
       </c>
       <c r="D34" t="n">
-        <v>378</v>
+        <v>79.41</v>
       </c>
       <c r="E34" t="n">
-        <v>79.41</v>
+        <v>31.91</v>
       </c>
       <c r="F34" t="n">
-        <v>31.91</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>80.73999999999999</v>
+        <v>126.701</v>
       </c>
       <c r="H34" t="n">
-        <v>126.701</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>77.09999999999999</v>
+        <v>19.54</v>
       </c>
       <c r="J34" t="n">
-        <v>19.54</v>
+        <v>33.6542226269064</v>
       </c>
       <c r="K34" t="n">
-        <v>33.6542226269064</v>
+        <v>16331.3467939646</v>
       </c>
       <c r="L34" t="n">
-        <v>16331.3467939646</v>
-      </c>
-      <c r="M34" t="n">
         <v>13.3499611387371</v>
       </c>
     </row>
@@ -1915,33 +1811,30 @@
         <v>27303.3</v>
       </c>
       <c r="D35" t="n">
-        <v>398.7</v>
+        <v>86.17</v>
       </c>
       <c r="E35" t="n">
-        <v>86.17</v>
+        <v>32.25</v>
       </c>
       <c r="F35" t="n">
-        <v>32.25</v>
+        <v>84.43000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>84.43000000000001</v>
+        <v>151.487</v>
       </c>
       <c r="H35" t="n">
-        <v>151.487</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>78.09999999999999</v>
+        <v>24.1</v>
       </c>
       <c r="J35" t="n">
-        <v>24.1</v>
+        <v>35.2355650415637</v>
       </c>
       <c r="K35" t="n">
-        <v>35.2355650415637</v>
+        <v>5963.46844390303</v>
       </c>
       <c r="L35" t="n">
-        <v>5963.46844390303</v>
-      </c>
-      <c r="M35" t="n">
         <v>19.8567940881369</v>
       </c>
     </row>
@@ -1958,33 +1851,30 @@
         <v>28873.4</v>
       </c>
       <c r="D36" t="n">
-        <v>422.5</v>
+        <v>89.61</v>
       </c>
       <c r="E36" t="n">
-        <v>89.61</v>
+        <v>38.63</v>
       </c>
       <c r="F36" t="n">
-        <v>38.63</v>
+        <v>86.06</v>
       </c>
       <c r="G36" t="n">
-        <v>86.06</v>
+        <v>184.718</v>
       </c>
       <c r="H36" t="n">
-        <v>184.718</v>
+        <v>79</v>
       </c>
       <c r="I36" t="n">
-        <v>79</v>
+        <v>28.03</v>
       </c>
       <c r="J36" t="n">
-        <v>28.03</v>
+        <v>36.1884973404255</v>
       </c>
       <c r="K36" t="n">
-        <v>36.1884973404255</v>
+        <v>7658.52342984337</v>
       </c>
       <c r="L36" t="n">
-        <v>7658.52342984337</v>
-      </c>
-      <c r="M36" t="n">
         <v>19.874215891301</v>
       </c>
     </row>
@@ -2001,33 +1891,30 @@
         <v>27194.2</v>
       </c>
       <c r="D37" t="n">
-        <v>427.7</v>
+        <v>92.78</v>
       </c>
       <c r="E37" t="n">
-        <v>92.78</v>
+        <v>47.19</v>
       </c>
       <c r="F37" t="n">
-        <v>47.19</v>
+        <v>90.8</v>
       </c>
       <c r="G37" t="n">
-        <v>90.8</v>
+        <v>204.741</v>
       </c>
       <c r="H37" t="n">
-        <v>204.741</v>
+        <v>79.5</v>
       </c>
       <c r="I37" t="n">
-        <v>79.5</v>
+        <v>31.96</v>
       </c>
       <c r="J37" t="n">
-        <v>31.96</v>
+        <v>36.3127392017496</v>
       </c>
       <c r="K37" t="n">
-        <v>36.3127392017496</v>
+        <v>23168.4158228047</v>
       </c>
       <c r="L37" t="n">
-        <v>23168.4158228047</v>
-      </c>
-      <c r="M37" t="n">
         <v>12.2448277312995</v>
       </c>
     </row>
@@ -2044,33 +1931,30 @@
         <v>30382.9</v>
       </c>
       <c r="D38" t="n">
-        <v>442.2</v>
+        <v>93.41</v>
       </c>
       <c r="E38" t="n">
-        <v>93.41</v>
+        <v>54.01</v>
       </c>
       <c r="F38" t="n">
-        <v>54.01</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>90.76000000000001</v>
+        <v>218.154</v>
       </c>
       <c r="H38" t="n">
-        <v>218.154</v>
+        <v>80.8</v>
       </c>
       <c r="I38" t="n">
-        <v>80.8</v>
+        <v>47.71</v>
       </c>
       <c r="J38" t="n">
-        <v>47.71</v>
+        <v>36.6502473650247</v>
       </c>
       <c r="K38" t="n">
-        <v>36.6502473650247</v>
+        <v>55321.8720892365</v>
       </c>
       <c r="L38" t="n">
-        <v>55321.8720892365</v>
-      </c>
-      <c r="M38" t="n">
         <v>15.9690026786633</v>
       </c>
     </row>
@@ -2087,33 +1971,30 @@
         <v>34492.4</v>
       </c>
       <c r="D39" t="n">
-        <v>463.9</v>
+        <v>94</v>
       </c>
       <c r="E39" t="n">
-        <v>94</v>
+        <v>50.06</v>
       </c>
       <c r="F39" t="n">
-        <v>50.06</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>89.59999999999999</v>
+        <v>222.653</v>
       </c>
       <c r="H39" t="n">
-        <v>222.653</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>81.59999999999999</v>
+        <v>48.61</v>
       </c>
       <c r="J39" t="n">
-        <v>48.61</v>
+        <v>36.7656727425982</v>
       </c>
       <c r="K39" t="n">
-        <v>36.7656727425982</v>
+        <v>58909.2438615862</v>
       </c>
       <c r="L39" t="n">
-        <v>58909.2438615862</v>
-      </c>
-      <c r="M39" t="n">
         <v>17.6595981229011</v>
       </c>
     </row>
@@ -2130,33 +2011,30 @@
         <v>37398.6</v>
       </c>
       <c r="D40" t="n">
-        <v>477.7</v>
+        <v>92.3</v>
       </c>
       <c r="E40" t="n">
-        <v>92.3</v>
+        <v>56.83</v>
       </c>
       <c r="F40" t="n">
-        <v>56.83</v>
+        <v>91.22</v>
       </c>
       <c r="G40" t="n">
-        <v>91.22</v>
+        <v>225.022</v>
       </c>
       <c r="H40" t="n">
-        <v>225.022</v>
+        <v>82.3</v>
       </c>
       <c r="I40" t="n">
-        <v>82.3</v>
+        <v>49.51</v>
       </c>
       <c r="J40" t="n">
-        <v>49.51</v>
+        <v>36.9005587748344</v>
       </c>
       <c r="K40" t="n">
-        <v>36.9005587748344</v>
+        <v>557174.2544104879</v>
       </c>
       <c r="L40" t="n">
-        <v>557174.2544104879</v>
-      </c>
-      <c r="M40" t="n">
         <v>18.7419533928829</v>
       </c>
     </row>
@@ -2173,33 +2051,30 @@
         <v>39456.3</v>
       </c>
       <c r="D41" t="n">
-        <v>485</v>
+        <v>94.92</v>
       </c>
       <c r="E41" t="n">
-        <v>94.92</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>64.56999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>94.59999999999999</v>
+        <v>232.728</v>
       </c>
       <c r="H41" t="n">
-        <v>232.728</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>82.09999999999999</v>
+        <v>49.51</v>
       </c>
       <c r="J41" t="n">
-        <v>49.51</v>
+        <v>37.5627069536424</v>
       </c>
       <c r="K41" t="n">
-        <v>37.5627069536424</v>
+        <v>221297.933713323</v>
       </c>
       <c r="L41" t="n">
-        <v>221297.933713323</v>
-      </c>
-      <c r="M41" t="n">
         <v>18.0329234506901</v>
       </c>
     </row>
@@ -2216,33 +2091,30 @@
         <v>27214.7</v>
       </c>
       <c r="D42" t="n">
-        <v>5210.3</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>83.23999999999999</v>
+        <v>55.58</v>
       </c>
       <c r="F42" t="n">
-        <v>55.58</v>
+        <v>84.64</v>
       </c>
       <c r="G42" t="n">
-        <v>84.64</v>
+        <v>324.548</v>
       </c>
       <c r="H42" t="n">
-        <v>324.548</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>87.90000000000001</v>
+        <v>19.97</v>
       </c>
       <c r="J42" t="n">
-        <v>19.97</v>
+        <v>29.8452606888193</v>
       </c>
       <c r="K42" t="n">
-        <v>29.8452606888193</v>
+        <v>25419.9420488373</v>
       </c>
       <c r="L42" t="n">
-        <v>25419.9420488373</v>
-      </c>
-      <c r="M42" t="n">
         <v>17.8292568189487</v>
       </c>
     </row>
@@ -2259,33 +2131,30 @@
         <v>28492.8</v>
       </c>
       <c r="D43" t="n">
-        <v>5280.8</v>
+        <v>86.36</v>
       </c>
       <c r="E43" t="n">
-        <v>86.36</v>
+        <v>58.59</v>
       </c>
       <c r="F43" t="n">
-        <v>58.59</v>
+        <v>86.5</v>
       </c>
       <c r="G43" t="n">
-        <v>86.5</v>
+        <v>377.61</v>
       </c>
       <c r="H43" t="n">
-        <v>377.61</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>87.90000000000001</v>
+        <v>23.78</v>
       </c>
       <c r="J43" t="n">
-        <v>23.78</v>
+        <v>30.5512773467128</v>
       </c>
       <c r="K43" t="n">
-        <v>30.5512773467128</v>
+        <v>42344.5953726121</v>
       </c>
       <c r="L43" t="n">
-        <v>42344.5953726121</v>
-      </c>
-      <c r="M43" t="n">
         <v>19.5549977904499</v>
       </c>
     </row>
@@ -2302,33 +2171,30 @@
         <v>30008.3</v>
       </c>
       <c r="D44" t="n">
-        <v>5288</v>
+        <v>87</v>
       </c>
       <c r="E44" t="n">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="F44" t="n">
-        <v>64</v>
+        <v>87.03</v>
       </c>
       <c r="G44" t="n">
-        <v>87.03</v>
+        <v>408.303</v>
       </c>
       <c r="H44" t="n">
-        <v>408.303</v>
+        <v>87.7</v>
       </c>
       <c r="I44" t="n">
-        <v>87.7</v>
+        <v>24.755</v>
       </c>
       <c r="J44" t="n">
-        <v>24.755</v>
+        <v>35.4302064212035</v>
       </c>
       <c r="K44" t="n">
-        <v>35.4302064212035</v>
+        <v>56186.8725912141</v>
       </c>
       <c r="L44" t="n">
-        <v>56186.8725912141</v>
-      </c>
-      <c r="M44" t="n">
         <v>20.7104130233292</v>
       </c>
     </row>
@@ -2345,33 +2211,30 @@
         <v>29178.2</v>
       </c>
       <c r="D45" t="n">
-        <v>5222</v>
+        <v>88.02</v>
       </c>
       <c r="E45" t="n">
-        <v>88.02</v>
+        <v>71.64</v>
       </c>
       <c r="F45" t="n">
-        <v>71.64</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>87.59999999999999</v>
+        <v>400.775</v>
       </c>
       <c r="H45" t="n">
-        <v>400.775</v>
+        <v>87.7</v>
       </c>
       <c r="I45" t="n">
-        <v>87.7</v>
+        <v>25.73</v>
       </c>
       <c r="J45" t="n">
-        <v>25.73</v>
+        <v>36.4490898642092</v>
       </c>
       <c r="K45" t="n">
-        <v>36.4490898642092</v>
+        <v>67601.7572863652</v>
       </c>
       <c r="L45" t="n">
-        <v>67601.7572863652</v>
-      </c>
-      <c r="M45" t="n">
         <v>22.58251525965</v>
       </c>
     </row>
@@ -2388,33 +2251,30 @@
         <v>30502.4</v>
       </c>
       <c r="D46" t="n">
-        <v>5198.8</v>
+        <v>89.31</v>
       </c>
       <c r="E46" t="n">
-        <v>89.31</v>
+        <v>75.48</v>
       </c>
       <c r="F46" t="n">
-        <v>75.48</v>
+        <v>88.84999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>88.84999999999999</v>
+        <v>453.125</v>
       </c>
       <c r="H46" t="n">
-        <v>453.125</v>
+        <v>88</v>
       </c>
       <c r="I46" t="n">
-        <v>88</v>
+        <v>42.08</v>
       </c>
       <c r="J46" t="n">
-        <v>42.08</v>
+        <v>37.4984794433561</v>
       </c>
       <c r="K46" t="n">
-        <v>37.4984794433561</v>
+        <v>75932.7348813586</v>
       </c>
       <c r="L46" t="n">
-        <v>75932.7348813586</v>
-      </c>
-      <c r="M46" t="n">
         <v>20.3560909262553</v>
       </c>
     </row>
@@ -2431,33 +2291,30 @@
         <v>32419.5</v>
       </c>
       <c r="D47" t="n">
-        <v>5155.6</v>
+        <v>91.48</v>
       </c>
       <c r="E47" t="n">
-        <v>91.48</v>
+        <v>77</v>
       </c>
       <c r="F47" t="n">
-        <v>77</v>
+        <v>90.64</v>
       </c>
       <c r="G47" t="n">
-        <v>90.64</v>
+        <v>515.979</v>
       </c>
       <c r="H47" t="n">
-        <v>515.979</v>
+        <v>87.7</v>
       </c>
       <c r="I47" t="n">
-        <v>87.7</v>
+        <v>42.51</v>
       </c>
       <c r="J47" t="n">
-        <v>42.51</v>
+        <v>37.7136856539825</v>
       </c>
       <c r="K47" t="n">
-        <v>37.7136856539825</v>
+        <v>85606.06245170831</v>
       </c>
       <c r="L47" t="n">
-        <v>85606.06245170831</v>
-      </c>
-      <c r="M47" t="n">
         <v>21.8353618959526</v>
       </c>
     </row>
@@ -2474,33 +2331,30 @@
         <v>34972.6</v>
       </c>
       <c r="D48" t="n">
-        <v>5042</v>
+        <v>92.8</v>
       </c>
       <c r="E48" t="n">
-        <v>92.8</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>77.68000000000001</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>92.04000000000001</v>
+        <v>537.506</v>
       </c>
       <c r="H48" t="n">
-        <v>537.506</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>86.59999999999999</v>
+        <v>42.94</v>
       </c>
       <c r="J48" t="n">
-        <v>42.94</v>
+        <v>37.9099783935119</v>
       </c>
       <c r="K48" t="n">
-        <v>37.9099783935119</v>
+        <v>80152.0281309664</v>
       </c>
       <c r="L48" t="n">
-        <v>80152.0281309664</v>
-      </c>
-      <c r="M48" t="n">
         <v>20.302723987427</v>
       </c>
     </row>
@@ -2517,33 +2371,30 @@
         <v>36175.9</v>
       </c>
       <c r="D49" t="n">
-        <v>5171</v>
+        <v>94.56</v>
       </c>
       <c r="E49" t="n">
-        <v>94.56</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>81.23999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="G49" t="n">
-        <v>93.7</v>
+        <v>536.397</v>
       </c>
       <c r="H49" t="n">
-        <v>536.397</v>
+        <v>86.5</v>
       </c>
       <c r="I49" t="n">
-        <v>86.5</v>
+        <v>42.94</v>
       </c>
       <c r="J49" t="n">
-        <v>42.94</v>
+        <v>38.8656371139002</v>
       </c>
       <c r="K49" t="n">
-        <v>38.8656371139002</v>
+        <v>79335.8806598204</v>
       </c>
       <c r="L49" t="n">
-        <v>79335.8806598204</v>
-      </c>
-      <c r="M49" t="n">
         <v>22.4045215279558</v>
       </c>
     </row>
@@ -2560,33 +2411,30 @@
         <v>37964.1</v>
       </c>
       <c r="D50" t="n">
-        <v>2788.5</v>
+        <v>97</v>
       </c>
       <c r="E50" t="n">
-        <v>97</v>
+        <v>80.19</v>
       </c>
       <c r="F50" t="n">
-        <v>80.19</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>97.09999999999999</v>
+        <v>1503.199</v>
       </c>
       <c r="H50" t="n">
-        <v>1503.199</v>
+        <v>73.3</v>
       </c>
       <c r="I50" t="n">
-        <v>73.3</v>
+        <v>48.82</v>
       </c>
       <c r="J50" t="n">
-        <v>48.82</v>
+        <v>43.5697797531659</v>
       </c>
       <c r="K50" t="n">
-        <v>43.5697797531659</v>
+        <v>43757.82743392</v>
       </c>
       <c r="L50" t="n">
-        <v>43757.82743392</v>
-      </c>
-      <c r="M50" t="n">
         <v>12.4279222825429</v>
       </c>
     </row>
@@ -2603,33 +2451,30 @@
         <v>38810.6</v>
       </c>
       <c r="D51" t="n">
-        <v>2832.3</v>
+        <v>92.66</v>
       </c>
       <c r="E51" t="n">
-        <v>92.66</v>
+        <v>84.39</v>
       </c>
       <c r="F51" t="n">
-        <v>84.39</v>
+        <v>97.61</v>
       </c>
       <c r="G51" t="n">
-        <v>97.61</v>
+        <v>1551.092</v>
       </c>
       <c r="H51" t="n">
-        <v>1551.092</v>
+        <v>73.5</v>
       </c>
       <c r="I51" t="n">
-        <v>73.5</v>
+        <v>53.74</v>
       </c>
       <c r="J51" t="n">
-        <v>53.74</v>
+        <v>43.7690892923223</v>
       </c>
       <c r="K51" t="n">
-        <v>43.7690892923223</v>
+        <v>123154.440492982</v>
       </c>
       <c r="L51" t="n">
-        <v>123154.440492982</v>
-      </c>
-      <c r="M51" t="n">
         <v>12.3547301877073</v>
       </c>
     </row>
@@ -2646,33 +2491,30 @@
         <v>39393</v>
       </c>
       <c r="D52" t="n">
-        <v>2877.7</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>95.43000000000001</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>84.15000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="G52" t="n">
-        <v>97.06</v>
+        <v>1568.648</v>
       </c>
       <c r="H52" t="n">
-        <v>1568.648</v>
+        <v>74</v>
       </c>
       <c r="I52" t="n">
-        <v>74</v>
+        <v>59.295</v>
       </c>
       <c r="J52" t="n">
-        <v>59.295</v>
+        <v>43.6229516711158</v>
       </c>
       <c r="K52" t="n">
-        <v>43.6229516711158</v>
+        <v>277330.575592896</v>
       </c>
       <c r="L52" t="n">
-        <v>277330.575592896</v>
-      </c>
-      <c r="M52" t="n">
         <v>12.039996737934</v>
       </c>
     </row>
@@ -2689,33 +2531,30 @@
         <v>40054.4</v>
       </c>
       <c r="D53" t="n">
-        <v>2853</v>
+        <v>95.27</v>
       </c>
       <c r="E53" t="n">
-        <v>95.27</v>
+        <v>89.31</v>
       </c>
       <c r="F53" t="n">
-        <v>89.31</v>
+        <v>98.66</v>
       </c>
       <c r="G53" t="n">
-        <v>98.66</v>
+        <v>1589.506</v>
       </c>
       <c r="H53" t="n">
-        <v>1589.506</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>74.09999999999999</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>64.84999999999999</v>
+        <v>44.4185659681079</v>
       </c>
       <c r="K53" t="n">
-        <v>44.4185659681079</v>
+        <v>277081.814259482</v>
       </c>
       <c r="L53" t="n">
-        <v>277081.814259482</v>
-      </c>
-      <c r="M53" t="n">
         <v>13.2343925466707</v>
       </c>
     </row>
@@ -2732,33 +2571,30 @@
         <v>44240.3</v>
       </c>
       <c r="D54" t="n">
-        <v>2888.9</v>
+        <v>96.14</v>
       </c>
       <c r="E54" t="n">
-        <v>96.14</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="F54" t="n">
-        <v>90.81999999999999</v>
+        <v>98.89</v>
       </c>
       <c r="G54" t="n">
-        <v>98.89</v>
+        <v>1621.669</v>
       </c>
       <c r="H54" t="n">
-        <v>1621.669</v>
+        <v>74.5</v>
       </c>
       <c r="I54" t="n">
-        <v>74.5</v>
+        <v>61.73</v>
       </c>
       <c r="J54" t="n">
-        <v>61.73</v>
+        <v>44.9598379722906</v>
       </c>
       <c r="K54" t="n">
-        <v>44.9598379722906</v>
+        <v>259654.486554193</v>
       </c>
       <c r="L54" t="n">
-        <v>259654.486554193</v>
-      </c>
-      <c r="M54" t="n">
         <v>13.9247982031326</v>
       </c>
     </row>
@@ -2775,33 +2611,30 @@
         <v>48465.4</v>
       </c>
       <c r="D55" t="n">
-        <v>2971.8</v>
+        <v>95.16</v>
       </c>
       <c r="E55" t="n">
-        <v>95.16</v>
+        <v>88.3</v>
       </c>
       <c r="F55" t="n">
-        <v>88.3</v>
+        <v>97.86</v>
       </c>
       <c r="G55" t="n">
-        <v>97.86</v>
+        <v>1866.229</v>
       </c>
       <c r="H55" t="n">
-        <v>1866.229</v>
+        <v>74.2</v>
       </c>
       <c r="I55" t="n">
-        <v>74.2</v>
+        <v>64.17999999999999</v>
       </c>
       <c r="J55" t="n">
-        <v>64.17999999999999</v>
+        <v>44.8863644064006</v>
       </c>
       <c r="K55" t="n">
-        <v>44.8863644064006</v>
+        <v>258760.024712703</v>
       </c>
       <c r="L55" t="n">
-        <v>258760.024712703</v>
-      </c>
-      <c r="M55" t="n">
         <v>15.988289228272</v>
       </c>
     </row>
@@ -2818,33 +2651,30 @@
         <v>48353.1</v>
       </c>
       <c r="D56" t="n">
-        <v>3001.5</v>
+        <v>96.09</v>
       </c>
       <c r="E56" t="n">
-        <v>96.09</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>89.01000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="G56" t="n">
-        <v>98.8</v>
+        <v>1934.231</v>
       </c>
       <c r="H56" t="n">
-        <v>1934.231</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>74.40000000000001</v>
+        <v>66.63</v>
       </c>
       <c r="J56" t="n">
-        <v>66.63</v>
+        <v>44.0352069959396</v>
       </c>
       <c r="K56" t="n">
-        <v>44.0352069959396</v>
+        <v>261262.408036924</v>
       </c>
       <c r="L56" t="n">
-        <v>261262.408036924</v>
-      </c>
-      <c r="M56" t="n">
         <v>17.1321575837404</v>
       </c>
     </row>
@@ -2861,33 +2691,30 @@
         <v>50767.5</v>
       </c>
       <c r="D57" t="n">
-        <v>3061.4</v>
+        <v>96.92</v>
       </c>
       <c r="E57" t="n">
-        <v>96.92</v>
+        <v>90.86</v>
       </c>
       <c r="F57" t="n">
-        <v>90.86</v>
+        <v>99.77</v>
       </c>
       <c r="G57" t="n">
-        <v>99.77</v>
+        <v>1983.35</v>
       </c>
       <c r="H57" t="n">
-        <v>1983.35</v>
+        <v>75.8</v>
       </c>
       <c r="I57" t="n">
-        <v>75.8</v>
+        <v>66.63</v>
       </c>
       <c r="J57" t="n">
-        <v>66.63</v>
+        <v>43.3933280824544</v>
       </c>
       <c r="K57" t="n">
-        <v>43.3933280824544</v>
+        <v>246545.586810222</v>
       </c>
       <c r="L57" t="n">
-        <v>246545.586810222</v>
-      </c>
-      <c r="M57" t="n">
         <v>17.6194498489345</v>
       </c>
     </row>
@@ -2904,33 +2731,30 @@
         <v>23734</v>
       </c>
       <c r="D58" t="n">
-        <v>650.3</v>
+        <v>88.27</v>
       </c>
       <c r="E58" t="n">
-        <v>88.27</v>
+        <v>58.16</v>
       </c>
       <c r="F58" t="n">
-        <v>58.16</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>88.09999999999999</v>
+        <v>231.31</v>
       </c>
       <c r="H58" t="n">
-        <v>231.31</v>
+        <v>82.3</v>
       </c>
       <c r="I58" t="n">
-        <v>82.3</v>
+        <v>31.72</v>
       </c>
       <c r="J58" t="n">
-        <v>31.72</v>
+        <v>32.5220031500844</v>
       </c>
       <c r="K58" t="n">
-        <v>32.5220031500844</v>
+        <v>29131.217625233</v>
       </c>
       <c r="L58" t="n">
-        <v>29131.217625233</v>
-      </c>
-      <c r="M58" t="n">
         <v>17.9646942764807</v>
       </c>
     </row>
@@ -2947,33 +2771,30 @@
         <v>25227.3</v>
       </c>
       <c r="D59" t="n">
-        <v>656.5</v>
+        <v>90.47</v>
       </c>
       <c r="E59" t="n">
-        <v>90.47</v>
+        <v>61.26</v>
       </c>
       <c r="F59" t="n">
-        <v>61.26</v>
+        <v>89.36</v>
       </c>
       <c r="G59" t="n">
-        <v>89.36</v>
+        <v>277.182</v>
       </c>
       <c r="H59" t="n">
-        <v>277.182</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>82.09999999999999</v>
+        <v>31.72</v>
       </c>
       <c r="J59" t="n">
-        <v>31.72</v>
+        <v>33.3725174267095</v>
       </c>
       <c r="K59" t="n">
-        <v>33.3725174267095</v>
+        <v>48893.4376316683</v>
       </c>
       <c r="L59" t="n">
-        <v>48893.4376316683</v>
-      </c>
-      <c r="M59" t="n">
         <v>18.2045260067525</v>
       </c>
     </row>
@@ -2990,33 +2811,30 @@
         <v>26438.1</v>
       </c>
       <c r="D60" t="n">
-        <v>662.2</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="E60" t="n">
-        <v>90.43000000000001</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="F60" t="n">
-        <v>68.23999999999999</v>
+        <v>90.23</v>
       </c>
       <c r="G60" t="n">
-        <v>90.23</v>
+        <v>341.911</v>
       </c>
       <c r="H60" t="n">
-        <v>341.911</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>82.90000000000001</v>
+        <v>42.665</v>
       </c>
       <c r="J60" t="n">
-        <v>42.665</v>
+        <v>33.8508104327483</v>
       </c>
       <c r="K60" t="n">
-        <v>33.8508104327483</v>
+        <v>83313.1107289332</v>
       </c>
       <c r="L60" t="n">
-        <v>83313.1107289332</v>
-      </c>
-      <c r="M60" t="n">
         <v>16.9644248677655</v>
       </c>
     </row>
@@ -3033,33 +2851,30 @@
         <v>25994.6</v>
       </c>
       <c r="D61" t="n">
-        <v>646.8</v>
+        <v>89.98</v>
       </c>
       <c r="E61" t="n">
-        <v>89.98</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>68.43000000000001</v>
+        <v>89.06</v>
       </c>
       <c r="G61" t="n">
-        <v>89.06</v>
+        <v>361.85</v>
       </c>
       <c r="H61" t="n">
-        <v>361.85</v>
+        <v>83.2</v>
       </c>
       <c r="I61" t="n">
-        <v>83.2</v>
+        <v>53.61</v>
       </c>
       <c r="J61" t="n">
-        <v>53.61</v>
+        <v>34.2700326171401</v>
       </c>
       <c r="K61" t="n">
-        <v>34.2700326171401</v>
+        <v>84354.3769866162</v>
       </c>
       <c r="L61" t="n">
-        <v>84354.3769866162</v>
-      </c>
-      <c r="M61" t="n">
         <v>20.6216264338951</v>
       </c>
     </row>
@@ -3076,33 +2891,30 @@
         <v>28242.8</v>
       </c>
       <c r="D62" t="n">
-        <v>650.5</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="E62" t="n">
-        <v>91.81999999999999</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="F62" t="n">
-        <v>70.31999999999999</v>
+        <v>90.98</v>
       </c>
       <c r="G62" t="n">
-        <v>90.98</v>
+        <v>414.236</v>
       </c>
       <c r="H62" t="n">
-        <v>414.236</v>
+        <v>83.3</v>
       </c>
       <c r="I62" t="n">
-        <v>83.3</v>
+        <v>54.54</v>
       </c>
       <c r="J62" t="n">
-        <v>54.54</v>
+        <v>37.357189680638</v>
       </c>
       <c r="K62" t="n">
-        <v>37.357189680638</v>
+        <v>96297.9325765704</v>
       </c>
       <c r="L62" t="n">
-        <v>96297.9325765704</v>
-      </c>
-      <c r="M62" t="n">
         <v>20.6301155577085</v>
       </c>
     </row>
@@ -3119,33 +2931,30 @@
         <v>30029.1</v>
       </c>
       <c r="D63" t="n">
-        <v>677.3</v>
+        <v>92.41</v>
       </c>
       <c r="E63" t="n">
-        <v>92.41</v>
+        <v>70.83</v>
       </c>
       <c r="F63" t="n">
-        <v>70.83</v>
+        <v>91.5</v>
       </c>
       <c r="G63" t="n">
-        <v>91.5</v>
+        <v>481.859</v>
       </c>
       <c r="H63" t="n">
-        <v>481.859</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>83.09999999999999</v>
+        <v>54.61499999999999</v>
       </c>
       <c r="J63" t="n">
-        <v>54.61499999999999</v>
+        <v>39.7219150412824</v>
       </c>
       <c r="K63" t="n">
-        <v>39.7219150412824</v>
+        <v>104101.301859375</v>
       </c>
       <c r="L63" t="n">
-        <v>104101.301859375</v>
-      </c>
-      <c r="M63" t="n">
         <v>18.0186438315616</v>
       </c>
     </row>
@@ -3162,33 +2971,30 @@
         <v>30609.9</v>
       </c>
       <c r="D64" t="n">
-        <v>694.6</v>
+        <v>93.22</v>
       </c>
       <c r="E64" t="n">
-        <v>93.22</v>
+        <v>73.12</v>
       </c>
       <c r="F64" t="n">
-        <v>73.12</v>
+        <v>93.2</v>
       </c>
       <c r="G64" t="n">
-        <v>93.2</v>
+        <v>514.091</v>
       </c>
       <c r="H64" t="n">
-        <v>514.091</v>
+        <v>82.5</v>
       </c>
       <c r="I64" t="n">
-        <v>82.5</v>
+        <v>54.69</v>
       </c>
       <c r="J64" t="n">
-        <v>54.69</v>
+        <v>35.2539796781149</v>
       </c>
       <c r="K64" t="n">
-        <v>35.2539796781149</v>
+        <v>112224.017467886</v>
       </c>
       <c r="L64" t="n">
-        <v>112224.017467886</v>
-      </c>
-      <c r="M64" t="n">
         <v>16.581160524959</v>
       </c>
     </row>
@@ -3205,33 +3011,30 @@
         <v>31555.3</v>
       </c>
       <c r="D65" t="n">
-        <v>698.6</v>
+        <v>92.89</v>
       </c>
       <c r="E65" t="n">
-        <v>92.89</v>
+        <v>73.06</v>
       </c>
       <c r="F65" t="n">
-        <v>73.06</v>
+        <v>92.25</v>
       </c>
       <c r="G65" t="n">
-        <v>92.25</v>
+        <v>575.45</v>
       </c>
       <c r="H65" t="n">
-        <v>575.45</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>81.59999999999999</v>
+        <v>54.69</v>
       </c>
       <c r="J65" t="n">
-        <v>54.69</v>
+        <v>35.3527186879385</v>
       </c>
       <c r="K65" t="n">
-        <v>35.3527186879385</v>
+        <v>139022.298393767</v>
       </c>
       <c r="L65" t="n">
-        <v>139022.298393767</v>
-      </c>
-      <c r="M65" t="n">
         <v>18.382980141257</v>
       </c>
     </row>
@@ -3248,33 +3051,30 @@
         <v>32444.6</v>
       </c>
       <c r="D66" t="n">
-        <v>2473.2</v>
+        <v>94.42</v>
       </c>
       <c r="E66" t="n">
-        <v>94.42</v>
+        <v>70.81999999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>70.81999999999999</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>93.68000000000001</v>
+        <v>1121.728</v>
       </c>
       <c r="H66" t="n">
-        <v>1121.728</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>81.59999999999999</v>
+        <v>62.34</v>
       </c>
       <c r="J66" t="n">
-        <v>62.34</v>
+        <v>31.0435197469463</v>
       </c>
       <c r="K66" t="n">
-        <v>31.0435197469463</v>
+        <v>22324.1144951885</v>
       </c>
       <c r="L66" t="n">
-        <v>22324.1144951885</v>
-      </c>
-      <c r="M66" t="n">
         <v>9.6573147330322</v>
       </c>
     </row>
@@ -3291,33 +3091,30 @@
         <v>33393.2</v>
       </c>
       <c r="D67" t="n">
-        <v>2539.9</v>
+        <v>94.28</v>
       </c>
       <c r="E67" t="n">
-        <v>94.28</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>69.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G67" t="n">
-        <v>94.40000000000001</v>
+        <v>1167.703</v>
       </c>
       <c r="H67" t="n">
-        <v>1167.703</v>
+        <v>82.3</v>
       </c>
       <c r="I67" t="n">
-        <v>82.3</v>
+        <v>62.3</v>
       </c>
       <c r="J67" t="n">
-        <v>62.3</v>
+        <v>31.491717515124</v>
       </c>
       <c r="K67" t="n">
-        <v>31.491717515124</v>
+        <v>33999.120663944</v>
       </c>
       <c r="L67" t="n">
-        <v>33999.120663944</v>
-      </c>
-      <c r="M67" t="n">
         <v>9.017653550321519</v>
       </c>
     </row>
@@ -3334,33 +3131,30 @@
         <v>33999.7</v>
       </c>
       <c r="D68" t="n">
-        <v>2565.6</v>
+        <v>94.36</v>
       </c>
       <c r="E68" t="n">
-        <v>94.36</v>
+        <v>73.14</v>
       </c>
       <c r="F68" t="n">
-        <v>73.14</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>95.29000000000001</v>
+        <v>1216.962</v>
       </c>
       <c r="H68" t="n">
-        <v>1216.962</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>83.09999999999999</v>
+        <v>67.63499999999999</v>
       </c>
       <c r="J68" t="n">
-        <v>67.63499999999999</v>
+        <v>32.5439773811208</v>
       </c>
       <c r="K68" t="n">
-        <v>32.5439773811208</v>
+        <v>57692.6350775481</v>
       </c>
       <c r="L68" t="n">
-        <v>57692.6350775481</v>
-      </c>
-      <c r="M68" t="n">
         <v>9.21470120593618</v>
       </c>
     </row>
@@ -3377,33 +3171,30 @@
         <v>34039.9</v>
       </c>
       <c r="D69" t="n">
-        <v>2528.2</v>
+        <v>96</v>
       </c>
       <c r="E69" t="n">
-        <v>96</v>
+        <v>75.83</v>
       </c>
       <c r="F69" t="n">
-        <v>75.83</v>
+        <v>97</v>
       </c>
       <c r="G69" t="n">
-        <v>97</v>
+        <v>1254.721</v>
       </c>
       <c r="H69" t="n">
-        <v>1254.721</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>84.09999999999999</v>
+        <v>72.97</v>
       </c>
       <c r="J69" t="n">
-        <v>72.97</v>
+        <v>33.3838974597133</v>
       </c>
       <c r="K69" t="n">
-        <v>33.3838974597133</v>
+        <v>81650.5089118576</v>
       </c>
       <c r="L69" t="n">
-        <v>81650.5089118576</v>
-      </c>
-      <c r="M69" t="n">
         <v>9.982300252858341</v>
       </c>
     </row>
@@ -3420,33 +3211,30 @@
         <v>36222.4</v>
       </c>
       <c r="D70" t="n">
-        <v>2554.6</v>
+        <v>96.56</v>
       </c>
       <c r="E70" t="n">
-        <v>96.56</v>
+        <v>78.64</v>
       </c>
       <c r="F70" t="n">
-        <v>78.64</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>96.70999999999999</v>
+        <v>1353.701</v>
       </c>
       <c r="H70" t="n">
-        <v>1353.701</v>
+        <v>81.8</v>
       </c>
       <c r="I70" t="n">
-        <v>81.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J70" t="n">
-        <v>71.40000000000001</v>
+        <v>33.6396818306917</v>
       </c>
       <c r="K70" t="n">
-        <v>33.6396818306917</v>
+        <v>104960.876315666</v>
       </c>
       <c r="L70" t="n">
-        <v>104960.876315666</v>
-      </c>
-      <c r="M70" t="n">
         <v>10.2937538536253</v>
       </c>
     </row>
@@ -3463,33 +3251,30 @@
         <v>38350.4</v>
       </c>
       <c r="D71" t="n">
-        <v>2619.2</v>
+        <v>97.59</v>
       </c>
       <c r="E71" t="n">
-        <v>97.59</v>
+        <v>78.64</v>
       </c>
       <c r="F71" t="n">
-        <v>78.64</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>97.26000000000001</v>
+        <v>1430.388</v>
       </c>
       <c r="H71" t="n">
-        <v>1430.388</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>81.90000000000001</v>
+        <v>73.20500000000001</v>
       </c>
       <c r="J71" t="n">
-        <v>73.20500000000001</v>
+        <v>34.2951599474189</v>
       </c>
       <c r="K71" t="n">
-        <v>34.2951599474189</v>
+        <v>131286.012181913</v>
       </c>
       <c r="L71" t="n">
-        <v>131286.012181913</v>
-      </c>
-      <c r="M71" t="n">
         <v>9.62392843667484</v>
       </c>
     </row>
@@ -3506,33 +3291,30 @@
         <v>39689</v>
       </c>
       <c r="D72" t="n">
-        <v>2627.7</v>
+        <v>96.78</v>
       </c>
       <c r="E72" t="n">
-        <v>96.78</v>
+        <v>79.14</v>
       </c>
       <c r="F72" t="n">
-        <v>79.14</v>
+        <v>97.7</v>
       </c>
       <c r="G72" t="n">
-        <v>97.7</v>
+        <v>1516.784</v>
       </c>
       <c r="H72" t="n">
-        <v>1516.784</v>
+        <v>81.5</v>
       </c>
       <c r="I72" t="n">
-        <v>81.5</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="J72" t="n">
-        <v>75.01000000000001</v>
+        <v>35.3318092510781</v>
       </c>
       <c r="K72" t="n">
-        <v>35.3318092510781</v>
+        <v>153868.49826224</v>
       </c>
       <c r="L72" t="n">
-        <v>153868.49826224</v>
-      </c>
-      <c r="M72" t="n">
         <v>9.714022595491331</v>
       </c>
     </row>
@@ -3549,33 +3331,30 @@
         <v>40848.2</v>
       </c>
       <c r="D73" t="n">
-        <v>2602.3</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="E73" t="n">
-        <v>97.34999999999999</v>
+        <v>78.94</v>
       </c>
       <c r="F73" t="n">
-        <v>78.94</v>
+        <v>97.95</v>
       </c>
       <c r="G73" t="n">
-        <v>97.95</v>
+        <v>1586.873</v>
       </c>
       <c r="H73" t="n">
-        <v>1586.873</v>
+        <v>81.3</v>
       </c>
       <c r="I73" t="n">
-        <v>81.3</v>
+        <v>75.01000000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>75.01000000000001</v>
+        <v>36.4765341417867</v>
       </c>
       <c r="K73" t="n">
-        <v>36.4765341417867</v>
+        <v>177933.600727841</v>
       </c>
       <c r="L73" t="n">
-        <v>177933.600727841</v>
-      </c>
-      <c r="M73" t="n">
         <v>9.285226596339569</v>
       </c>
     </row>
@@ -3592,33 +3371,30 @@
         <v>30585.2</v>
       </c>
       <c r="D74" t="n">
-        <v>26773.8</v>
+        <v>86.41</v>
       </c>
       <c r="E74" t="n">
-        <v>86.41</v>
+        <v>66.7</v>
       </c>
       <c r="F74" t="n">
-        <v>66.7</v>
+        <v>86.56</v>
       </c>
       <c r="G74" t="n">
-        <v>86.56</v>
+        <v>756.08</v>
       </c>
       <c r="H74" t="n">
-        <v>756.08</v>
+        <v>74.8</v>
       </c>
       <c r="I74" t="n">
-        <v>74.8</v>
+        <v>15.93</v>
       </c>
       <c r="J74" t="n">
-        <v>15.93</v>
+        <v>43.6242593525939</v>
       </c>
       <c r="K74" t="n">
-        <v>43.6242593525939</v>
+        <v>14819.4761291503</v>
       </c>
       <c r="L74" t="n">
-        <v>14819.4761291503</v>
-      </c>
-      <c r="M74" t="n">
         <v>26.0180218998669</v>
       </c>
     </row>
@@ -3635,33 +3411,30 @@
         <v>31463.5</v>
       </c>
       <c r="D75" t="n">
-        <v>26987.8</v>
+        <v>88.56</v>
       </c>
       <c r="E75" t="n">
-        <v>88.56</v>
+        <v>67.12</v>
       </c>
       <c r="F75" t="n">
-        <v>67.12</v>
+        <v>88.17</v>
       </c>
       <c r="G75" t="n">
-        <v>88.17</v>
+        <v>774.53</v>
       </c>
       <c r="H75" t="n">
-        <v>774.53</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>75.59999999999999</v>
+        <v>15.93</v>
       </c>
       <c r="J75" t="n">
-        <v>15.93</v>
+        <v>44.4142292018123</v>
       </c>
       <c r="K75" t="n">
-        <v>44.4142292018123</v>
+        <v>20362.9338827691</v>
       </c>
       <c r="L75" t="n">
-        <v>20362.9338827691</v>
-      </c>
-      <c r="M75" t="n">
         <v>25.9347849255776</v>
       </c>
     </row>
@@ -3678,33 +3451,30 @@
         <v>33247.6</v>
       </c>
       <c r="D76" t="n">
-        <v>27096.3</v>
+        <v>90.17</v>
       </c>
       <c r="E76" t="n">
-        <v>90.17</v>
+        <v>70.17</v>
       </c>
       <c r="F76" t="n">
-        <v>70.17</v>
+        <v>89.39</v>
       </c>
       <c r="G76" t="n">
-        <v>89.39</v>
+        <v>793.9880000000001</v>
       </c>
       <c r="H76" t="n">
-        <v>793.9880000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>76.59999999999999</v>
+        <v>19.85</v>
       </c>
       <c r="J76" t="n">
-        <v>19.85</v>
+        <v>45.2765022757908</v>
       </c>
       <c r="K76" t="n">
-        <v>45.2765022757908</v>
+        <v>29255.7243091748</v>
       </c>
       <c r="L76" t="n">
-        <v>29255.7243091748</v>
-      </c>
-      <c r="M76" t="n">
         <v>26.9265976407414</v>
       </c>
     </row>
@@ -3721,33 +3491,30 @@
         <v>31598</v>
       </c>
       <c r="D77" t="n">
-        <v>26958.4</v>
+        <v>91.75</v>
       </c>
       <c r="E77" t="n">
-        <v>91.75</v>
+        <v>72.92500000000001</v>
       </c>
       <c r="F77" t="n">
-        <v>72.92500000000001</v>
+        <v>90.47</v>
       </c>
       <c r="G77" t="n">
-        <v>90.47</v>
+        <v>781.376</v>
       </c>
       <c r="H77" t="n">
-        <v>781.376</v>
+        <v>77.7</v>
       </c>
       <c r="I77" t="n">
-        <v>77.7</v>
+        <v>23.77</v>
       </c>
       <c r="J77" t="n">
-        <v>23.77</v>
+        <v>46.471240838575</v>
       </c>
       <c r="K77" t="n">
-        <v>46.471240838575</v>
+        <v>36107.8390576723</v>
       </c>
       <c r="L77" t="n">
-        <v>36107.8390576723</v>
-      </c>
-      <c r="M77" t="n">
         <v>21.1920405248012</v>
       </c>
     </row>
@@ -3764,33 +3531,30 @@
         <v>33452.3</v>
       </c>
       <c r="D78" t="n">
-        <v>27696.2</v>
+        <v>93.33</v>
       </c>
       <c r="E78" t="n">
-        <v>93.33</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="F78" t="n">
-        <v>75.68000000000001</v>
+        <v>91.55</v>
       </c>
       <c r="G78" t="n">
-        <v>91.55</v>
+        <v>819.431</v>
       </c>
       <c r="H78" t="n">
-        <v>819.431</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>77.90000000000001</v>
+        <v>25.89</v>
       </c>
       <c r="J78" t="n">
-        <v>25.89</v>
+        <v>47.6442336298287</v>
       </c>
       <c r="K78" t="n">
-        <v>47.6442336298287</v>
+        <v>39644.0530743928</v>
       </c>
       <c r="L78" t="n">
-        <v>39644.0530743928</v>
-      </c>
-      <c r="M78" t="n">
         <v>22.305003085565</v>
       </c>
     </row>
@@ -3807,33 +3571,30 @@
         <v>35188.1</v>
       </c>
       <c r="D79" t="n">
-        <v>28301.6</v>
+        <v>92.25</v>
       </c>
       <c r="E79" t="n">
-        <v>92.25</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>75.84999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="G79" t="n">
-        <v>90.59999999999999</v>
+        <v>865.509</v>
       </c>
       <c r="H79" t="n">
-        <v>865.509</v>
+        <v>78.7</v>
       </c>
       <c r="I79" t="n">
-        <v>78.7</v>
+        <v>24.525</v>
       </c>
       <c r="J79" t="n">
-        <v>24.525</v>
+        <v>48.250226559098</v>
       </c>
       <c r="K79" t="n">
-        <v>48.250226559098</v>
+        <v>47329.437557888</v>
       </c>
       <c r="L79" t="n">
-        <v>47329.437557888</v>
-      </c>
-      <c r="M79" t="n">
         <v>21.9264611257156</v>
       </c>
     </row>
@@ -3850,33 +3611,30 @@
         <v>38056.4</v>
       </c>
       <c r="D80" t="n">
-        <v>28539.1</v>
+        <v>93.34</v>
       </c>
       <c r="E80" t="n">
-        <v>93.34</v>
+        <v>76.93000000000001</v>
       </c>
       <c r="F80" t="n">
-        <v>76.93000000000001</v>
+        <v>92.83</v>
       </c>
       <c r="G80" t="n">
-        <v>92.83</v>
+        <v>900.476</v>
       </c>
       <c r="H80" t="n">
-        <v>900.476</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>78.90000000000001</v>
+        <v>23.16</v>
       </c>
       <c r="J80" t="n">
-        <v>23.16</v>
+        <v>48.6688340139444</v>
       </c>
       <c r="K80" t="n">
-        <v>48.6688340139444</v>
+        <v>52017.9916172468</v>
       </c>
       <c r="L80" t="n">
-        <v>52017.9916172468</v>
-      </c>
-      <c r="M80" t="n">
         <v>22.3835449721792</v>
       </c>
     </row>
@@ -3893,33 +3651,30 @@
         <v>39216.6</v>
       </c>
       <c r="D81" t="n">
-        <v>28912.7</v>
+        <v>94.44</v>
       </c>
       <c r="E81" t="n">
-        <v>94.44</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="F81" t="n">
-        <v>80.29000000000001</v>
+        <v>94.14</v>
       </c>
       <c r="G81" t="n">
-        <v>94.14</v>
+        <v>926.182</v>
       </c>
       <c r="H81" t="n">
-        <v>926.182</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>79.09999999999999</v>
+        <v>23.16</v>
       </c>
       <c r="J81" t="n">
-        <v>23.16</v>
+        <v>48.9251978969333</v>
       </c>
       <c r="K81" t="n">
-        <v>48.9251978969333</v>
+        <v>57274.6363971705</v>
       </c>
       <c r="L81" t="n">
-        <v>57274.6363971705</v>
-      </c>
-      <c r="M81" t="n">
         <v>23.1371073769038</v>
       </c>
     </row>
@@ -3936,33 +3691,30 @@
         <v>37470.1</v>
       </c>
       <c r="D82" t="n">
-        <v>41489.8</v>
+        <v>92.86</v>
       </c>
       <c r="E82" t="n">
-        <v>92.86</v>
+        <v>74.86</v>
       </c>
       <c r="F82" t="n">
-        <v>74.86</v>
+        <v>90.25</v>
       </c>
       <c r="G82" t="n">
-        <v>90.25</v>
+        <v>1206.394</v>
       </c>
       <c r="H82" t="n">
-        <v>1206.394</v>
+        <v>80.2</v>
       </c>
       <c r="I82" t="n">
-        <v>80.2</v>
+        <v>20.47</v>
       </c>
       <c r="J82" t="n">
-        <v>20.47</v>
+        <v>39.9888046312857</v>
       </c>
       <c r="K82" t="n">
-        <v>39.9888046312857</v>
+        <v>34181.2784354313</v>
       </c>
       <c r="L82" t="n">
-        <v>34181.2784354313</v>
-      </c>
-      <c r="M82" t="n">
         <v>15.850578794452</v>
       </c>
     </row>
@@ -3979,33 +3731,30 @@
         <v>38540.9</v>
       </c>
       <c r="D83" t="n">
-        <v>41735.2</v>
+        <v>94.39</v>
       </c>
       <c r="E83" t="n">
-        <v>94.39</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="F83" t="n">
-        <v>76.79000000000001</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="G83" t="n">
-        <v>92.34999999999999</v>
+        <v>1264.236</v>
       </c>
       <c r="H83" t="n">
-        <v>1264.236</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>80.40000000000001</v>
+        <v>20.47</v>
       </c>
       <c r="J83" t="n">
-        <v>20.47</v>
+        <v>40.9651498488548</v>
       </c>
       <c r="K83" t="n">
-        <v>40.9651498488548</v>
+        <v>56406.6207107244</v>
       </c>
       <c r="L83" t="n">
-        <v>56406.6207107244</v>
-      </c>
-      <c r="M83" t="n">
         <v>15.7474335584013</v>
       </c>
     </row>
@@ -4022,33 +3771,30 @@
         <v>38992.6</v>
       </c>
       <c r="D84" t="n">
-        <v>42221.2</v>
+        <v>94.83</v>
       </c>
       <c r="E84" t="n">
-        <v>94.83</v>
+        <v>79.41</v>
       </c>
       <c r="F84" t="n">
-        <v>79.41</v>
+        <v>92.98</v>
       </c>
       <c r="G84" t="n">
-        <v>92.98</v>
+        <v>1325.301</v>
       </c>
       <c r="H84" t="n">
-        <v>1325.301</v>
+        <v>80.5</v>
       </c>
       <c r="I84" t="n">
-        <v>80.5</v>
+        <v>25.545</v>
       </c>
       <c r="J84" t="n">
-        <v>25.545</v>
+        <v>42.1155574684512</v>
       </c>
       <c r="K84" t="n">
-        <v>42.1155574684512</v>
+        <v>77970.0331298817</v>
       </c>
       <c r="L84" t="n">
-        <v>77970.0331298817</v>
-      </c>
-      <c r="M84" t="n">
         <v>16.3869405629417</v>
       </c>
     </row>
@@ -4065,33 +3811,30 @@
         <v>37974.3</v>
       </c>
       <c r="D85" t="n">
-        <v>41300.9</v>
+        <v>95.8</v>
       </c>
       <c r="E85" t="n">
-        <v>95.8</v>
+        <v>82.55</v>
       </c>
       <c r="F85" t="n">
-        <v>82.55</v>
+        <v>94.3</v>
       </c>
       <c r="G85" t="n">
-        <v>94.3</v>
+        <v>1281.558</v>
       </c>
       <c r="H85" t="n">
-        <v>1281.558</v>
+        <v>80</v>
       </c>
       <c r="I85" t="n">
-        <v>80</v>
+        <v>30.62</v>
       </c>
       <c r="J85" t="n">
-        <v>30.62</v>
+        <v>43.3048696627</v>
       </c>
       <c r="K85" t="n">
-        <v>43.3048696627</v>
+        <v>97517.56929049001</v>
       </c>
       <c r="L85" t="n">
-        <v>97517.56929049001</v>
-      </c>
-      <c r="M85" t="n">
         <v>15.5031959869375</v>
       </c>
     </row>
@@ -4108,33 +3851,30 @@
         <v>40535.9</v>
       </c>
       <c r="D86" t="n">
-        <v>40682.3</v>
+        <v>91.88</v>
       </c>
       <c r="E86" t="n">
-        <v>91.88</v>
+        <v>76.02</v>
       </c>
       <c r="F86" t="n">
-        <v>76.02</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="G86" t="n">
-        <v>91.43000000000001</v>
+        <v>1361.115</v>
       </c>
       <c r="H86" t="n">
-        <v>1361.115</v>
+        <v>78.3</v>
       </c>
       <c r="I86" t="n">
-        <v>78.3</v>
+        <v>38.42</v>
       </c>
       <c r="J86" t="n">
-        <v>38.42</v>
+        <v>44.0643361489671</v>
       </c>
       <c r="K86" t="n">
-        <v>44.0643361489671</v>
+        <v>113297.576359309</v>
       </c>
       <c r="L86" t="n">
-        <v>113297.576359309</v>
-      </c>
-      <c r="M86" t="n">
         <v>15.3851048227765</v>
       </c>
     </row>
@@ -4151,33 +3891,30 @@
         <v>43346.6</v>
       </c>
       <c r="D87" t="n">
-        <v>41735.2</v>
+        <v>91.41</v>
       </c>
       <c r="E87" t="n">
-        <v>91.41</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="F87" t="n">
-        <v>76.18000000000001</v>
+        <v>91.63</v>
       </c>
       <c r="G87" t="n">
-        <v>91.63</v>
+        <v>1458.739</v>
       </c>
       <c r="H87" t="n">
-        <v>1458.739</v>
+        <v>77.7</v>
       </c>
       <c r="I87" t="n">
-        <v>77.7</v>
+        <v>40.88</v>
       </c>
       <c r="J87" t="n">
-        <v>40.88</v>
+        <v>44.6186317766404</v>
       </c>
       <c r="K87" t="n">
-        <v>44.6186317766404</v>
+        <v>126884.076646738</v>
       </c>
       <c r="L87" t="n">
-        <v>126884.076646738</v>
-      </c>
-      <c r="M87" t="n">
         <v>17.4981505573659</v>
       </c>
     </row>
@@ -4194,33 +3931,30 @@
         <v>45136.5</v>
       </c>
       <c r="D88" t="n">
-        <v>42270.4</v>
+        <v>91.66</v>
       </c>
       <c r="E88" t="n">
-        <v>91.66</v>
+        <v>77.48</v>
       </c>
       <c r="F88" t="n">
-        <v>77.48</v>
+        <v>92.48</v>
       </c>
       <c r="G88" t="n">
-        <v>92.48</v>
+        <v>1588.191</v>
       </c>
       <c r="H88" t="n">
-        <v>1588.191</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I88" t="n">
-        <v>77.40000000000001</v>
+        <v>43.34</v>
       </c>
       <c r="J88" t="n">
-        <v>43.34</v>
+        <v>45.380522509099</v>
       </c>
       <c r="K88" t="n">
-        <v>45.380522509099</v>
+        <v>139972.802327193</v>
       </c>
       <c r="L88" t="n">
-        <v>139972.802327193</v>
-      </c>
-      <c r="M88" t="n">
         <v>17.7818374796623</v>
       </c>
     </row>
@@ -4237,33 +3971,30 @@
         <v>46387.1</v>
       </c>
       <c r="D89" t="n">
-        <v>42480.1</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="E89" t="n">
-        <v>92.65000000000001</v>
+        <v>77.89</v>
       </c>
       <c r="F89" t="n">
-        <v>77.89</v>
+        <v>93.5</v>
       </c>
       <c r="G89" t="n">
-        <v>93.5</v>
+        <v>1624.448</v>
       </c>
       <c r="H89" t="n">
-        <v>1624.448</v>
+        <v>78.2</v>
       </c>
       <c r="I89" t="n">
-        <v>78.2</v>
+        <v>43.34</v>
       </c>
       <c r="J89" t="n">
-        <v>43.34</v>
+        <v>45.6069242965787</v>
       </c>
       <c r="K89" t="n">
-        <v>45.6069242965787</v>
+        <v>152113.844011812</v>
       </c>
       <c r="L89" t="n">
-        <v>152113.844011812</v>
-      </c>
-      <c r="M89" t="n">
         <v>17.9772990379432</v>
       </c>
     </row>
@@ -4280,33 +4011,30 @@
         <v>19700.8</v>
       </c>
       <c r="D90" t="n">
-        <v>3747.9</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="E90" t="n">
-        <v>70.95999999999999</v>
+        <v>32.06</v>
       </c>
       <c r="F90" t="n">
-        <v>32.06</v>
+        <v>69.89</v>
       </c>
       <c r="G90" t="n">
-        <v>69.89</v>
+        <v>189.301</v>
       </c>
       <c r="H90" t="n">
-        <v>189.301</v>
+        <v>70.7</v>
       </c>
       <c r="I90" t="n">
-        <v>70.7</v>
+        <v>8.92</v>
       </c>
       <c r="J90" t="n">
-        <v>8.92</v>
+        <v>35.1351318678243</v>
       </c>
       <c r="K90" t="n">
-        <v>35.1351318678243</v>
+        <v>3695.69375338864</v>
       </c>
       <c r="L90" t="n">
-        <v>3695.69375338864</v>
-      </c>
-      <c r="M90" t="n">
         <v>12.1148895809545</v>
       </c>
     </row>
@@ -4323,33 +4051,30 @@
         <v>20203</v>
       </c>
       <c r="D91" t="n">
-        <v>3823.6</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="E91" t="n">
-        <v>76.48999999999999</v>
+        <v>35.94</v>
       </c>
       <c r="F91" t="n">
-        <v>35.94</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="G91" t="n">
-        <v>72.23999999999999</v>
+        <v>202.893</v>
       </c>
       <c r="H91" t="n">
-        <v>202.893</v>
+        <v>71.3</v>
       </c>
       <c r="I91" t="n">
-        <v>71.3</v>
+        <v>10.03</v>
       </c>
       <c r="J91" t="n">
-        <v>10.03</v>
+        <v>36.9203391643751</v>
       </c>
       <c r="K91" t="n">
-        <v>36.9203391643751</v>
+        <v>5035.36701512231</v>
       </c>
       <c r="L91" t="n">
-        <v>5035.36701512231</v>
-      </c>
-      <c r="M91" t="n">
         <v>12.9551889486437</v>
       </c>
     </row>
@@ -4366,33 +4091,30 @@
         <v>20765.1</v>
       </c>
       <c r="D92" t="n">
-        <v>3904.6</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="E92" t="n">
-        <v>78.54000000000001</v>
+        <v>38.93</v>
       </c>
       <c r="F92" t="n">
-        <v>38.93</v>
+        <v>75.67</v>
       </c>
       <c r="G92" t="n">
-        <v>75.67</v>
+        <v>217.972</v>
       </c>
       <c r="H92" t="n">
-        <v>217.972</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="I92" t="n">
-        <v>74.09999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="J92" t="n">
-        <v>12.8</v>
+        <v>38.3565690069278</v>
       </c>
       <c r="K92" t="n">
-        <v>38.3565690069278</v>
+        <v>6647.33991681452</v>
       </c>
       <c r="L92" t="n">
-        <v>6647.33991681452</v>
-      </c>
-      <c r="M92" t="n">
         <v>12.5222555558252</v>
       </c>
     </row>
@@ -4409,33 +4131,30 @@
         <v>18866.4</v>
       </c>
       <c r="D93" t="n">
-        <v>3870.6</v>
+        <v>80.38</v>
       </c>
       <c r="E93" t="n">
-        <v>80.38</v>
+        <v>46.35</v>
       </c>
       <c r="F93" t="n">
-        <v>46.35</v>
+        <v>78.12</v>
       </c>
       <c r="G93" t="n">
-        <v>78.12</v>
+        <v>232.699</v>
       </c>
       <c r="H93" t="n">
-        <v>232.699</v>
+        <v>75.7</v>
       </c>
       <c r="I93" t="n">
-        <v>75.7</v>
+        <v>15.57</v>
       </c>
       <c r="J93" t="n">
-        <v>15.57</v>
+        <v>39.7876360746134</v>
       </c>
       <c r="K93" t="n">
-        <v>39.7876360746134</v>
+        <v>8907.70838312568</v>
       </c>
       <c r="L93" t="n">
-        <v>8907.70838312568</v>
-      </c>
-      <c r="M93" t="n">
         <v>13.2518669714424</v>
       </c>
     </row>
@@ -4452,33 +4171,30 @@
         <v>21245.7</v>
       </c>
       <c r="D94" t="n">
-        <v>3923</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="E94" t="n">
-        <v>85.06999999999999</v>
+        <v>54.22</v>
       </c>
       <c r="F94" t="n">
-        <v>54.22</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="G94" t="n">
-        <v>78.48999999999999</v>
+        <v>247.779</v>
       </c>
       <c r="H94" t="n">
-        <v>247.779</v>
+        <v>76.5</v>
       </c>
       <c r="I94" t="n">
-        <v>76.5</v>
+        <v>18.34</v>
       </c>
       <c r="J94" t="n">
-        <v>18.34</v>
+        <v>41.9213046741732</v>
       </c>
       <c r="K94" t="n">
-        <v>41.9213046741732</v>
+        <v>11384.3924146816</v>
       </c>
       <c r="L94" t="n">
-        <v>11384.3924146816</v>
-      </c>
-      <c r="M94" t="n">
         <v>12.2848681524393</v>
       </c>
     </row>
@@ -4495,33 +4211,30 @@
         <v>24026.4</v>
       </c>
       <c r="D95" t="n">
-        <v>4133.7</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="E95" t="n">
-        <v>85.48999999999999</v>
+        <v>58.69</v>
       </c>
       <c r="F95" t="n">
-        <v>58.69</v>
+        <v>83.17</v>
       </c>
       <c r="G95" t="n">
-        <v>83.17</v>
+        <v>293.482</v>
       </c>
       <c r="H95" t="n">
-        <v>293.482</v>
+        <v>77.3</v>
       </c>
       <c r="I95" t="n">
-        <v>77.3</v>
+        <v>19.79</v>
       </c>
       <c r="J95" t="n">
-        <v>19.79</v>
+        <v>42.923040428409</v>
       </c>
       <c r="K95" t="n">
-        <v>42.923040428409</v>
+        <v>13068.1749587664</v>
       </c>
       <c r="L95" t="n">
-        <v>13068.1749587664</v>
-      </c>
-      <c r="M95" t="n">
         <v>14.4708651762207</v>
       </c>
     </row>
@@ -4538,33 +4251,30 @@
         <v>26262.1</v>
       </c>
       <c r="D96" t="n">
-        <v>4186.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="E96" t="n">
-        <v>86.90000000000001</v>
+        <v>57.53</v>
       </c>
       <c r="F96" t="n">
-        <v>57.53</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="G96" t="n">
-        <v>85.01000000000001</v>
+        <v>323.135</v>
       </c>
       <c r="H96" t="n">
-        <v>323.135</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I96" t="n">
-        <v>77.59999999999999</v>
+        <v>21.24</v>
       </c>
       <c r="J96" t="n">
-        <v>21.24</v>
+        <v>43.8539621755853</v>
       </c>
       <c r="K96" t="n">
-        <v>43.8539621755853</v>
+        <v>14227.2514879146</v>
       </c>
       <c r="L96" t="n">
-        <v>14227.2514879146</v>
-      </c>
-      <c r="M96" t="n">
         <v>15.1515337740903</v>
       </c>
     </row>
@@ -4581,33 +4291,30 @@
         <v>27373.1</v>
       </c>
       <c r="D97" t="n">
-        <v>4265.9</v>
+        <v>86.89</v>
       </c>
       <c r="E97" t="n">
-        <v>86.89</v>
+        <v>64.94</v>
       </c>
       <c r="F97" t="n">
-        <v>64.94</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="G97" t="n">
-        <v>86.29000000000001</v>
+        <v>352.295</v>
       </c>
       <c r="H97" t="n">
-        <v>352.295</v>
+        <v>78.2</v>
       </c>
       <c r="I97" t="n">
-        <v>78.2</v>
+        <v>21.24</v>
       </c>
       <c r="J97" t="n">
-        <v>21.24</v>
+        <v>44.6759828527928</v>
       </c>
       <c r="K97" t="n">
-        <v>44.6759828527928</v>
+        <v>15657.9434729048</v>
       </c>
       <c r="L97" t="n">
-        <v>15657.9434729048</v>
-      </c>
-      <c r="M97" t="n">
         <v>15.011494857431</v>
       </c>
     </row>
@@ -4624,33 +4331,30 @@
         <v>20419.5</v>
       </c>
       <c r="D98" t="n">
-        <v>4421.4</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="E98" t="n">
-        <v>82.34999999999999</v>
+        <v>38.56</v>
       </c>
       <c r="F98" t="n">
-        <v>38.56</v>
+        <v>76.75</v>
       </c>
       <c r="G98" t="n">
-        <v>76.75</v>
+        <v>171.763</v>
       </c>
       <c r="H98" t="n">
-        <v>171.763</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I98" t="n">
-        <v>78.90000000000001</v>
+        <v>14.58</v>
       </c>
       <c r="J98" t="n">
-        <v>14.58</v>
+        <v>30.2136178819417</v>
       </c>
       <c r="K98" t="n">
-        <v>30.2136178819417</v>
+        <v>13712.8966738756</v>
       </c>
       <c r="L98" t="n">
-        <v>13712.8966738756</v>
-      </c>
-      <c r="M98" t="n">
         <v>17.2630732776764</v>
       </c>
     </row>
@@ -4667,33 +4371,30 @@
         <v>21875.5</v>
       </c>
       <c r="D99" t="n">
-        <v>4459.3</v>
+        <v>83.31</v>
       </c>
       <c r="E99" t="n">
-        <v>83.31</v>
+        <v>41.16</v>
       </c>
       <c r="F99" t="n">
-        <v>41.16</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="G99" t="n">
-        <v>76.06999999999999</v>
+        <v>211.185</v>
       </c>
       <c r="H99" t="n">
-        <v>211.185</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I99" t="n">
-        <v>79.90000000000001</v>
+        <v>15.39</v>
       </c>
       <c r="J99" t="n">
-        <v>15.39</v>
+        <v>31.5062908247816</v>
       </c>
       <c r="K99" t="n">
-        <v>31.5062908247816</v>
+        <v>19379.9008629269</v>
       </c>
       <c r="L99" t="n">
-        <v>19379.9008629269</v>
-      </c>
-      <c r="M99" t="n">
         <v>16.8209858629646</v>
       </c>
     </row>
@@ -4710,33 +4411,30 @@
         <v>23171.4</v>
       </c>
       <c r="D100" t="n">
-        <v>4495</v>
+        <v>86.2</v>
       </c>
       <c r="E100" t="n">
-        <v>86.2</v>
+        <v>49.18</v>
       </c>
       <c r="F100" t="n">
-        <v>49.18</v>
+        <v>80.37</v>
       </c>
       <c r="G100" t="n">
-        <v>80.37</v>
+        <v>222.532</v>
       </c>
       <c r="H100" t="n">
-        <v>222.532</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I100" t="n">
-        <v>80.09999999999999</v>
+        <v>18.88</v>
       </c>
       <c r="J100" t="n">
-        <v>18.88</v>
+        <v>32.6466329851573</v>
       </c>
       <c r="K100" t="n">
-        <v>32.6466329851573</v>
+        <v>26447.1020825133</v>
       </c>
       <c r="L100" t="n">
-        <v>26447.1020825133</v>
-      </c>
-      <c r="M100" t="n">
         <v>17.3787600622128</v>
       </c>
     </row>
@@ -4753,33 +4451,30 @@
         <v>22731.5</v>
       </c>
       <c r="D101" t="n">
-        <v>4430.5</v>
+        <v>87.63</v>
       </c>
       <c r="E101" t="n">
-        <v>87.63</v>
+        <v>60.02</v>
       </c>
       <c r="F101" t="n">
-        <v>60.02</v>
+        <v>84.77</v>
       </c>
       <c r="G101" t="n">
-        <v>84.77</v>
+        <v>226.682</v>
       </c>
       <c r="H101" t="n">
-        <v>226.682</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>80.40000000000001</v>
+        <v>22.37</v>
       </c>
       <c r="J101" t="n">
-        <v>22.37</v>
+        <v>33.4922037196533</v>
       </c>
       <c r="K101" t="n">
-        <v>33.4922037196533</v>
+        <v>33083.571663234</v>
       </c>
       <c r="L101" t="n">
-        <v>33083.571663234</v>
-      </c>
-      <c r="M101" t="n">
         <v>17.4648807221778</v>
       </c>
     </row>
@@ -4796,33 +4491,30 @@
         <v>24805.4</v>
       </c>
       <c r="D102" t="n">
-        <v>4609.7</v>
+        <v>90.78</v>
       </c>
       <c r="E102" t="n">
-        <v>90.78</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="F102" t="n">
-        <v>66.01000000000001</v>
+        <v>88.64</v>
       </c>
       <c r="G102" t="n">
-        <v>88.64</v>
+        <v>262.251</v>
       </c>
       <c r="H102" t="n">
-        <v>262.251</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I102" t="n">
-        <v>80.90000000000001</v>
+        <v>22.84</v>
       </c>
       <c r="J102" t="n">
-        <v>22.84</v>
+        <v>34.8391868436369</v>
       </c>
       <c r="K102" t="n">
-        <v>34.8391868436369</v>
+        <v>42102.778838019</v>
       </c>
       <c r="L102" t="n">
-        <v>42102.778838019</v>
-      </c>
-      <c r="M102" t="n">
         <v>16.3975126429279</v>
       </c>
     </row>
@@ -4839,33 +4531,30 @@
         <v>27305.5</v>
       </c>
       <c r="D103" t="n">
-        <v>4669.7</v>
+        <v>91.44</v>
       </c>
       <c r="E103" t="n">
-        <v>91.44</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="F103" t="n">
-        <v>70.31999999999999</v>
+        <v>89.14</v>
       </c>
       <c r="G103" t="n">
-        <v>89.14</v>
+        <v>244.611</v>
       </c>
       <c r="H103" t="n">
-        <v>244.611</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>81.40000000000001</v>
+        <v>32.035</v>
       </c>
       <c r="J103" t="n">
-        <v>32.035</v>
+        <v>36.5338104764554</v>
       </c>
       <c r="K103" t="n">
-        <v>36.5338104764554</v>
+        <v>51406.6835924429</v>
       </c>
       <c r="L103" t="n">
-        <v>51406.6835924429</v>
-      </c>
-      <c r="M103" t="n">
         <v>18.4048917258431</v>
       </c>
     </row>
@@ -4882,33 +4571,30 @@
         <v>28967.5</v>
       </c>
       <c r="D104" t="n">
-        <v>4697.5</v>
+        <v>92.73</v>
       </c>
       <c r="E104" t="n">
-        <v>92.73</v>
+        <v>69.67</v>
       </c>
       <c r="F104" t="n">
-        <v>69.67</v>
+        <v>91.45</v>
       </c>
       <c r="G104" t="n">
-        <v>91.45</v>
+        <v>283.971</v>
       </c>
       <c r="H104" t="n">
-        <v>283.971</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I104" t="n">
-        <v>81.90000000000001</v>
+        <v>41.23</v>
       </c>
       <c r="J104" t="n">
-        <v>41.23</v>
+        <v>36.7901885342462</v>
       </c>
       <c r="K104" t="n">
-        <v>36.7901885342462</v>
+        <v>53717.7865400025</v>
       </c>
       <c r="L104" t="n">
-        <v>53717.7865400025</v>
-      </c>
-      <c r="M104" t="n">
         <v>18.8624569621863</v>
       </c>
     </row>
@@ -4925,33 +4611,30 @@
         <v>30445.4</v>
       </c>
       <c r="D105" t="n">
-        <v>4699.3</v>
+        <v>94.78</v>
       </c>
       <c r="E105" t="n">
-        <v>94.78</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="F105" t="n">
-        <v>74.18000000000001</v>
+        <v>93.78</v>
       </c>
       <c r="G105" t="n">
-        <v>93.78</v>
+        <v>282.228</v>
       </c>
       <c r="H105" t="n">
-        <v>282.228</v>
+        <v>82.3</v>
       </c>
       <c r="I105" t="n">
-        <v>82.3</v>
+        <v>44.45</v>
       </c>
       <c r="J105" t="n">
-        <v>44.45</v>
+        <v>37.542262483936</v>
       </c>
       <c r="K105" t="n">
-        <v>37.542262483936</v>
+        <v>55077.4335878286</v>
       </c>
       <c r="L105" t="n">
-        <v>55077.4335878286</v>
-      </c>
-      <c r="M105" t="n">
         <v>22.5745118826045</v>
       </c>
     </row>
@@ -4968,33 +4651,30 @@
         <v>55304.1</v>
       </c>
       <c r="D106" t="n">
-        <v>2184.1</v>
+        <v>88.37</v>
       </c>
       <c r="E106" t="n">
-        <v>88.37</v>
+        <v>53.09</v>
       </c>
       <c r="F106" t="n">
-        <v>53.09</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="G106" t="n">
-        <v>81.23999999999999</v>
+        <v>776.72</v>
       </c>
       <c r="H106" t="n">
-        <v>776.72</v>
+        <v>78.2</v>
       </c>
       <c r="I106" t="n">
-        <v>78.2</v>
+        <v>42.36</v>
       </c>
       <c r="J106" t="n">
-        <v>42.36</v>
+        <v>29.0794615926246</v>
       </c>
       <c r="K106" t="n">
-        <v>29.0794615926246</v>
+        <v>38437.1028566871</v>
       </c>
       <c r="L106" t="n">
-        <v>38437.1028566871</v>
-      </c>
-      <c r="M106" t="n">
         <v>29.3340262522775</v>
       </c>
     </row>
@@ -5011,33 +4691,30 @@
         <v>58660.8</v>
       </c>
       <c r="D107" t="n">
-        <v>2245.8</v>
+        <v>89.11</v>
       </c>
       <c r="E107" t="n">
-        <v>89.11</v>
+        <v>58.95</v>
       </c>
       <c r="F107" t="n">
-        <v>58.95</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="G107" t="n">
-        <v>82.20999999999999</v>
+        <v>746.484</v>
       </c>
       <c r="H107" t="n">
-        <v>746.484</v>
+        <v>78.5</v>
       </c>
       <c r="I107" t="n">
-        <v>78.5</v>
+        <v>42.36</v>
       </c>
       <c r="J107" t="n">
-        <v>42.36</v>
+        <v>29.3513301848147</v>
       </c>
       <c r="K107" t="n">
-        <v>29.3513301848147</v>
+        <v>69157.3047242336</v>
       </c>
       <c r="L107" t="n">
-        <v>69157.3047242336</v>
-      </c>
-      <c r="M107" t="n">
         <v>25.0152782298751</v>
       </c>
     </row>
@@ -5054,33 +4731,30 @@
         <v>59971.1</v>
       </c>
       <c r="D108" t="n">
-        <v>2310.8</v>
+        <v>90.59</v>
       </c>
       <c r="E108" t="n">
-        <v>90.59</v>
+        <v>66.59</v>
       </c>
       <c r="F108" t="n">
-        <v>66.59</v>
+        <v>90.34</v>
       </c>
       <c r="G108" t="n">
-        <v>90.34</v>
+        <v>837.229</v>
       </c>
       <c r="H108" t="n">
-        <v>837.229</v>
+        <v>79</v>
       </c>
       <c r="I108" t="n">
-        <v>79</v>
+        <v>44.875</v>
       </c>
       <c r="J108" t="n">
-        <v>44.875</v>
+        <v>29.6453160652366</v>
       </c>
       <c r="K108" t="n">
-        <v>29.6453160652366</v>
+        <v>94607.6886844775</v>
       </c>
       <c r="L108" t="n">
-        <v>94607.6886844775</v>
-      </c>
-      <c r="M108" t="n">
         <v>25.9769791902199</v>
       </c>
     </row>
@@ -5097,33 +4771,30 @@
         <v>62464.4</v>
       </c>
       <c r="D109" t="n">
-        <v>2279.6</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="E109" t="n">
-        <v>91.81999999999999</v>
+        <v>74.38</v>
       </c>
       <c r="F109" t="n">
-        <v>74.38</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="G109" t="n">
-        <v>91.01000000000001</v>
+        <v>857.543</v>
       </c>
       <c r="H109" t="n">
-        <v>857.543</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I109" t="n">
-        <v>80.40000000000001</v>
+        <v>47.39</v>
       </c>
       <c r="J109" t="n">
-        <v>47.39</v>
+        <v>30.4353384554187</v>
       </c>
       <c r="K109" t="n">
-        <v>30.4353384554187</v>
+        <v>114566.465340423</v>
       </c>
       <c r="L109" t="n">
-        <v>114566.465340423</v>
-      </c>
-      <c r="M109" t="n">
         <v>25.8991544690003</v>
       </c>
     </row>
@@ -5140,33 +4811,30 @@
         <v>74716.39999999999</v>
       </c>
       <c r="D110" t="n">
-        <v>2413</v>
+        <v>97.5</v>
       </c>
       <c r="E110" t="n">
-        <v>97.5</v>
+        <v>87.41</v>
       </c>
       <c r="F110" t="n">
-        <v>87.41</v>
+        <v>98.93000000000001</v>
       </c>
       <c r="G110" t="n">
-        <v>98.93000000000001</v>
+        <v>951.466</v>
       </c>
       <c r="H110" t="n">
-        <v>951.466</v>
+        <v>82.3</v>
       </c>
       <c r="I110" t="n">
-        <v>82.3</v>
+        <v>55.97</v>
       </c>
       <c r="J110" t="n">
-        <v>55.97</v>
+        <v>31.3616427884193</v>
       </c>
       <c r="K110" t="n">
-        <v>31.3616427884193</v>
+        <v>113930.009969504</v>
       </c>
       <c r="L110" t="n">
-        <v>113930.009969504</v>
-      </c>
-      <c r="M110" t="n">
         <v>28.4781475271992</v>
       </c>
     </row>
@@ -5183,33 +4851,30 @@
         <v>85692</v>
       </c>
       <c r="D111" t="n">
-        <v>2579.3</v>
+        <v>95.71000000000001</v>
       </c>
       <c r="E111" t="n">
-        <v>95.71000000000001</v>
+        <v>82</v>
       </c>
       <c r="F111" t="n">
-        <v>82</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="G111" t="n">
-        <v>92.01000000000001</v>
+        <v>1548.522</v>
       </c>
       <c r="H111" t="n">
-        <v>1548.522</v>
+        <v>82.5</v>
       </c>
       <c r="I111" t="n">
-        <v>82.5</v>
+        <v>57.7</v>
       </c>
       <c r="J111" t="n">
-        <v>57.7</v>
+        <v>31.5362809040128</v>
       </c>
       <c r="K111" t="n">
-        <v>31.5362809040128</v>
+        <v>134764.070843587</v>
       </c>
       <c r="L111" t="n">
-        <v>134764.070843587</v>
-      </c>
-      <c r="M111" t="n">
         <v>46.7867801497714</v>
       </c>
     </row>
@@ -5226,33 +4891,30 @@
         <v>83596.5</v>
       </c>
       <c r="D112" t="n">
-        <v>2667.8</v>
+        <v>93.92</v>
       </c>
       <c r="E112" t="n">
-        <v>93.92</v>
+        <v>87.12</v>
       </c>
       <c r="F112" t="n">
-        <v>87.12</v>
+        <v>93.27</v>
       </c>
       <c r="G112" t="n">
-        <v>93.27</v>
+        <v>1536.507</v>
       </c>
       <c r="H112" t="n">
-        <v>1536.507</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I112" t="n">
-        <v>82.59999999999999</v>
+        <v>59.43</v>
       </c>
       <c r="J112" t="n">
-        <v>59.43</v>
+        <v>31.8907830651788</v>
       </c>
       <c r="K112" t="n">
-        <v>31.8907830651788</v>
+        <v>149934.162195583</v>
       </c>
       <c r="L112" t="n">
-        <v>149934.162195583</v>
-      </c>
-      <c r="M112" t="n">
         <v>47.7737732849219</v>
       </c>
     </row>
@@ -5269,33 +4931,30 @@
         <v>88476.89999999999</v>
       </c>
       <c r="D113" t="n">
-        <v>2737.2</v>
+        <v>92.97</v>
       </c>
       <c r="E113" t="n">
-        <v>92.97</v>
+        <v>94.7</v>
       </c>
       <c r="F113" t="n">
-        <v>94.7</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="G113" t="n">
-        <v>98.59999999999999</v>
+        <v>1449.178</v>
       </c>
       <c r="H113" t="n">
-        <v>1449.178</v>
+        <v>83.5</v>
       </c>
       <c r="I113" t="n">
-        <v>83.5</v>
+        <v>59.43</v>
       </c>
       <c r="J113" t="n">
-        <v>59.43</v>
+        <v>32.3023693358176</v>
       </c>
       <c r="K113" t="n">
-        <v>32.3023693358176</v>
+        <v>121467.84808156</v>
       </c>
       <c r="L113" t="n">
-        <v>121467.84808156</v>
-      </c>
-      <c r="M113" t="n">
         <v>53.5184328432158</v>
       </c>
     </row>
@@ -5312,33 +4971,30 @@
         <v>28946.7</v>
       </c>
       <c r="D114" t="n">
-        <v>22950.2</v>
+        <v>81.02</v>
       </c>
       <c r="E114" t="n">
-        <v>81.02</v>
+        <v>32.17</v>
       </c>
       <c r="F114" t="n">
-        <v>32.17</v>
+        <v>70.97</v>
       </c>
       <c r="G114" t="n">
-        <v>70.97</v>
+        <v>396.12</v>
       </c>
       <c r="H114" t="n">
-        <v>396.12</v>
+        <v>59.1</v>
       </c>
       <c r="I114" t="n">
-        <v>59.1</v>
+        <v>20.31</v>
       </c>
       <c r="J114" t="n">
-        <v>20.31</v>
+        <v>27.4652917045411</v>
       </c>
       <c r="K114" t="n">
-        <v>27.4652917045411</v>
+        <v>7813.04008389552</v>
       </c>
       <c r="L114" t="n">
-        <v>7813.04008389552</v>
-      </c>
-      <c r="M114" t="n">
         <v>7.8052686500986</v>
       </c>
     </row>
@@ -5355,33 +5011,30 @@
         <v>29555.4</v>
       </c>
       <c r="D115" t="n">
-        <v>22912.6</v>
+        <v>84.34</v>
       </c>
       <c r="E115" t="n">
-        <v>84.34</v>
+        <v>35.65</v>
       </c>
       <c r="F115" t="n">
-        <v>35.65</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="G115" t="n">
-        <v>74.15000000000001</v>
+        <v>420.974</v>
       </c>
       <c r="H115" t="n">
-        <v>420.974</v>
+        <v>59.8</v>
       </c>
       <c r="I115" t="n">
-        <v>59.8</v>
+        <v>20.31</v>
       </c>
       <c r="J115" t="n">
-        <v>20.31</v>
+        <v>28.4648521996575</v>
       </c>
       <c r="K115" t="n">
-        <v>28.4648521996575</v>
+        <v>12313.6246863563</v>
       </c>
       <c r="L115" t="n">
-        <v>12313.6246863563</v>
-      </c>
-      <c r="M115" t="n">
         <v>7.47655885813922</v>
       </c>
     </row>
@@ -5398,33 +5051,30 @@
         <v>30348.1</v>
       </c>
       <c r="D116" t="n">
-        <v>23055.1</v>
+        <v>85.17</v>
       </c>
       <c r="E116" t="n">
-        <v>85.17</v>
+        <v>38.28</v>
       </c>
       <c r="F116" t="n">
-        <v>38.28</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="G116" t="n">
-        <v>75.56999999999999</v>
+        <v>439.002</v>
       </c>
       <c r="H116" t="n">
-        <v>439.002</v>
+        <v>60.3</v>
       </c>
       <c r="I116" t="n">
-        <v>60.3</v>
+        <v>39.13500000000001</v>
       </c>
       <c r="J116" t="n">
-        <v>39.13500000000001</v>
+        <v>29.0544644701951</v>
       </c>
       <c r="K116" t="n">
-        <v>29.0544644701951</v>
+        <v>15313.1771774623</v>
       </c>
       <c r="L116" t="n">
-        <v>15313.1771774623</v>
-      </c>
-      <c r="M116" t="n">
         <v>7.75802459594121</v>
       </c>
     </row>
@@ -5441,33 +5091,30 @@
         <v>28386.4</v>
       </c>
       <c r="D117" t="n">
-        <v>22543</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="E117" t="n">
-        <v>88.09999999999999</v>
+        <v>43.93</v>
       </c>
       <c r="F117" t="n">
-        <v>43.93</v>
+        <v>77.95</v>
       </c>
       <c r="G117" t="n">
-        <v>77.95</v>
+        <v>419.645</v>
       </c>
       <c r="H117" t="n">
-        <v>419.645</v>
+        <v>60.5</v>
       </c>
       <c r="I117" t="n">
-        <v>60.5</v>
+        <v>57.96</v>
       </c>
       <c r="J117" t="n">
-        <v>57.96</v>
+        <v>30.2586365187027</v>
       </c>
       <c r="K117" t="n">
-        <v>30.2586365187027</v>
+        <v>20677.1830094764</v>
       </c>
       <c r="L117" t="n">
-        <v>20677.1830094764</v>
-      </c>
-      <c r="M117" t="n">
         <v>8.587243012964</v>
       </c>
     </row>
@@ -5484,33 +5131,30 @@
         <v>31782.5</v>
       </c>
       <c r="D118" t="n">
-        <v>22462.6</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="E118" t="n">
-        <v>90.48999999999999</v>
+        <v>51.45</v>
       </c>
       <c r="F118" t="n">
-        <v>51.45</v>
+        <v>81.59</v>
       </c>
       <c r="G118" t="n">
-        <v>81.59</v>
+        <v>438.774</v>
       </c>
       <c r="H118" t="n">
-        <v>438.774</v>
+        <v>60.8</v>
       </c>
       <c r="I118" t="n">
-        <v>60.8</v>
+        <v>58.75</v>
       </c>
       <c r="J118" t="n">
-        <v>58.75</v>
+        <v>31.2852927413407</v>
       </c>
       <c r="K118" t="n">
-        <v>31.2852927413407</v>
+        <v>24823.3931231798</v>
       </c>
       <c r="L118" t="n">
-        <v>24823.3931231798</v>
-      </c>
-      <c r="M118" t="n">
         <v>7.77024565516253</v>
       </c>
     </row>
@@ -5527,33 +5171,30 @@
         <v>35348.2</v>
       </c>
       <c r="D119" t="n">
-        <v>23027.7</v>
+        <v>91.45</v>
       </c>
       <c r="E119" t="n">
-        <v>91.45</v>
+        <v>49.3</v>
       </c>
       <c r="F119" t="n">
-        <v>49.3</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="G119" t="n">
-        <v>85.06999999999999</v>
+        <v>462.242</v>
       </c>
       <c r="H119" t="n">
-        <v>462.242</v>
+        <v>61.2</v>
       </c>
       <c r="I119" t="n">
-        <v>61.2</v>
+        <v>59.03</v>
       </c>
       <c r="J119" t="n">
-        <v>59.03</v>
+        <v>31.19136706407</v>
       </c>
       <c r="K119" t="n">
-        <v>31.19136706407</v>
+        <v>28070.9043211973</v>
       </c>
       <c r="L119" t="n">
-        <v>28070.9043211973</v>
-      </c>
-      <c r="M119" t="n">
         <v>9.159162312710251</v>
       </c>
     </row>
@@ -5570,33 +5211,30 @@
         <v>37695.7</v>
       </c>
       <c r="D120" t="n">
-        <v>23501.9</v>
+        <v>91.89</v>
       </c>
       <c r="E120" t="n">
-        <v>91.89</v>
+        <v>51.11</v>
       </c>
       <c r="F120" t="n">
-        <v>51.11</v>
+        <v>86.92</v>
       </c>
       <c r="G120" t="n">
-        <v>86.92</v>
+        <v>498.319</v>
       </c>
       <c r="H120" t="n">
-        <v>498.319</v>
+        <v>63.3</v>
       </c>
       <c r="I120" t="n">
-        <v>63.3</v>
+        <v>59.31</v>
       </c>
       <c r="J120" t="n">
-        <v>59.31</v>
+        <v>31.8410876819321</v>
       </c>
       <c r="K120" t="n">
-        <v>31.8410876819321</v>
+        <v>30244.0571559008</v>
       </c>
       <c r="L120" t="n">
-        <v>30244.0571559008</v>
-      </c>
-      <c r="M120" t="n">
         <v>9.9836968942283</v>
       </c>
     </row>
@@ -5613,33 +5251,30 @@
         <v>39068.4</v>
       </c>
       <c r="D121" t="n">
-        <v>23867.7</v>
+        <v>93.41</v>
       </c>
       <c r="E121" t="n">
-        <v>93.41</v>
+        <v>53.6</v>
       </c>
       <c r="F121" t="n">
-        <v>53.6</v>
+        <v>89.23</v>
       </c>
       <c r="G121" t="n">
-        <v>89.23</v>
+        <v>515.759</v>
       </c>
       <c r="H121" t="n">
-        <v>515.759</v>
+        <v>64.3</v>
       </c>
       <c r="I121" t="n">
-        <v>64.3</v>
+        <v>59.31</v>
       </c>
       <c r="J121" t="n">
-        <v>59.31</v>
+        <v>31.7807732477772</v>
       </c>
       <c r="K121" t="n">
-        <v>31.7807732477772</v>
+        <v>30647.1608155582</v>
       </c>
       <c r="L121" t="n">
-        <v>30647.1608155582</v>
-      </c>
-      <c r="M121" t="n">
         <v>12.2827088504022</v>
       </c>
     </row>
@@ -5656,33 +5291,30 @@
         <v>18999.8</v>
       </c>
       <c r="D122" t="n">
-        <v>894.8</v>
+        <v>78.61</v>
       </c>
       <c r="E122" t="n">
-        <v>78.61</v>
+        <v>45.58</v>
       </c>
       <c r="F122" t="n">
-        <v>45.58</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="G122" t="n">
-        <v>81.31999999999999</v>
+        <v>70.714</v>
       </c>
       <c r="H122" t="n">
-        <v>70.714</v>
+        <v>84.8</v>
       </c>
       <c r="I122" t="n">
-        <v>84.8</v>
+        <v>10.54</v>
       </c>
       <c r="J122" t="n">
-        <v>10.54</v>
+        <v>27.0886247975645</v>
       </c>
       <c r="K122" t="n">
-        <v>27.0886247975645</v>
+        <v>11948.0107586673</v>
       </c>
       <c r="L122" t="n">
-        <v>11948.0107586673</v>
-      </c>
-      <c r="M122" t="n">
         <v>16.0817754609296</v>
       </c>
     </row>
@@ -5699,33 +5331,30 @@
         <v>20230.2</v>
       </c>
       <c r="D123" t="n">
-        <v>909.4</v>
+        <v>81.58</v>
       </c>
       <c r="E123" t="n">
-        <v>81.58</v>
+        <v>44.86</v>
       </c>
       <c r="F123" t="n">
-        <v>44.86</v>
+        <v>83.58</v>
       </c>
       <c r="G123" t="n">
-        <v>83.58</v>
+        <v>96.258</v>
       </c>
       <c r="H123" t="n">
-        <v>96.258</v>
+        <v>84.7</v>
       </c>
       <c r="I123" t="n">
-        <v>84.7</v>
+        <v>12.71</v>
       </c>
       <c r="J123" t="n">
-        <v>12.71</v>
+        <v>27.2877295355647</v>
       </c>
       <c r="K123" t="n">
-        <v>27.2877295355647</v>
+        <v>14504.1392214714</v>
       </c>
       <c r="L123" t="n">
-        <v>14504.1392214714</v>
-      </c>
-      <c r="M123" t="n">
         <v>16.5920580401869</v>
       </c>
     </row>
@@ -5742,33 +5371,30 @@
         <v>20948.7</v>
       </c>
       <c r="D124" t="n">
-        <v>910</v>
+        <v>85.45</v>
       </c>
       <c r="E124" t="n">
-        <v>85.45</v>
+        <v>46.6</v>
       </c>
       <c r="F124" t="n">
-        <v>46.6</v>
+        <v>86.14</v>
       </c>
       <c r="G124" t="n">
-        <v>86.14</v>
+        <v>101.668</v>
       </c>
       <c r="H124" t="n">
-        <v>101.668</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I124" t="n">
-        <v>85.09999999999999</v>
+        <v>15.78</v>
       </c>
       <c r="J124" t="n">
-        <v>15.78</v>
+        <v>26.5858975490829</v>
       </c>
       <c r="K124" t="n">
-        <v>26.5858975490829</v>
+        <v>19857.6461133794</v>
       </c>
       <c r="L124" t="n">
-        <v>19857.6461133794</v>
-      </c>
-      <c r="M124" t="n">
         <v>17.1495055610295</v>
       </c>
     </row>
@@ -5785,33 +5411,30 @@
         <v>20911.4</v>
       </c>
       <c r="D125" t="n">
-        <v>893</v>
+        <v>89.73</v>
       </c>
       <c r="E125" t="n">
-        <v>89.73</v>
+        <v>56.22</v>
       </c>
       <c r="F125" t="n">
-        <v>56.22</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="G125" t="n">
-        <v>88.90000000000001</v>
+        <v>115.911</v>
       </c>
       <c r="H125" t="n">
-        <v>115.911</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I125" t="n">
-        <v>85.40000000000001</v>
+        <v>18.85</v>
       </c>
       <c r="J125" t="n">
-        <v>18.85</v>
+        <v>25.804169430384</v>
       </c>
       <c r="K125" t="n">
-        <v>25.804169430384</v>
+        <v>20328.8801751586</v>
       </c>
       <c r="L125" t="n">
-        <v>20328.8801751586</v>
-      </c>
-      <c r="M125" t="n">
         <v>20.0336000956914</v>
       </c>
     </row>
@@ -5828,33 +5451,30 @@
         <v>23542.2</v>
       </c>
       <c r="D126" t="n">
-        <v>864</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="E126" t="n">
-        <v>91.15000000000001</v>
+        <v>61.82</v>
       </c>
       <c r="F126" t="n">
-        <v>61.82</v>
+        <v>91.3</v>
       </c>
       <c r="G126" t="n">
-        <v>91.3</v>
+        <v>131.447</v>
       </c>
       <c r="H126" t="n">
-        <v>131.447</v>
+        <v>85.8</v>
       </c>
       <c r="I126" t="n">
-        <v>85.8</v>
+        <v>24.69</v>
       </c>
       <c r="J126" t="n">
-        <v>24.69</v>
+        <v>25.9761549056076</v>
       </c>
       <c r="K126" t="n">
-        <v>25.9761549056076</v>
+        <v>22572.6854480523</v>
       </c>
       <c r="L126" t="n">
-        <v>22572.6854480523</v>
-      </c>
-      <c r="M126" t="n">
         <v>16.9803713630842</v>
       </c>
     </row>
@@ -5871,33 +5491,30 @@
         <v>24939.3</v>
       </c>
       <c r="D127" t="n">
-        <v>886.2</v>
+        <v>91.39</v>
       </c>
       <c r="E127" t="n">
-        <v>91.39</v>
+        <v>61.98</v>
       </c>
       <c r="F127" t="n">
-        <v>61.98</v>
+        <v>91.31</v>
       </c>
       <c r="G127" t="n">
-        <v>91.31</v>
+        <v>156.311</v>
       </c>
       <c r="H127" t="n">
-        <v>156.311</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I127" t="n">
-        <v>85.09999999999999</v>
+        <v>28.33</v>
       </c>
       <c r="J127" t="n">
-        <v>28.33</v>
+        <v>25.989241189689</v>
       </c>
       <c r="K127" t="n">
-        <v>25.989241189689</v>
+        <v>22271.1389855075</v>
       </c>
       <c r="L127" t="n">
-        <v>22271.1389855075</v>
-      </c>
-      <c r="M127" t="n">
         <v>17.5505893709401</v>
       </c>
     </row>
@@ -5914,33 +5531,30 @@
         <v>26754.5</v>
       </c>
       <c r="D128" t="n">
-        <v>884.2</v>
+        <v>93.06999999999999</v>
       </c>
       <c r="E128" t="n">
-        <v>93.06999999999999</v>
+        <v>62.14</v>
       </c>
       <c r="F128" t="n">
-        <v>62.14</v>
+        <v>92.33</v>
       </c>
       <c r="G128" t="n">
-        <v>92.33</v>
+        <v>172.209</v>
       </c>
       <c r="H128" t="n">
-        <v>172.209</v>
+        <v>84</v>
       </c>
       <c r="I128" t="n">
-        <v>84</v>
+        <v>31.97</v>
       </c>
       <c r="J128" t="n">
-        <v>31.97</v>
+        <v>25.9948491178264</v>
       </c>
       <c r="K128" t="n">
-        <v>25.9948491178264</v>
+        <v>26083.1019636781</v>
       </c>
       <c r="L128" t="n">
-        <v>26083.1019636781</v>
-      </c>
-      <c r="M128" t="n">
         <v>18.554389354563</v>
       </c>
     </row>
@@ -5957,33 +5571,30 @@
         <v>27536.4</v>
       </c>
       <c r="D129" t="n">
-        <v>877.4</v>
+        <v>94.33</v>
       </c>
       <c r="E129" t="n">
-        <v>94.33</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F129" t="n">
-        <v>65.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="G129" t="n">
-        <v>93.2</v>
+        <v>199.074</v>
       </c>
       <c r="H129" t="n">
-        <v>199.074</v>
+        <v>83.5</v>
       </c>
       <c r="I129" t="n">
-        <v>83.5</v>
+        <v>31.97</v>
       </c>
       <c r="J129" t="n">
-        <v>31.97</v>
+        <v>25.7542854181725</v>
       </c>
       <c r="K129" t="n">
-        <v>25.7542854181725</v>
+        <v>28218.3820582126</v>
       </c>
       <c r="L129" t="n">
-        <v>28218.3820582126</v>
-      </c>
-      <c r="M129" t="n">
         <v>17.4901914812882</v>
       </c>
     </row>
@@ -6000,33 +5611,30 @@
         <v>23073.2</v>
       </c>
       <c r="D130" t="n">
-        <v>1346.4</v>
+        <v>74.97</v>
       </c>
       <c r="E130" t="n">
-        <v>74.97</v>
+        <v>38.14</v>
       </c>
       <c r="F130" t="n">
-        <v>38.14</v>
+        <v>77.62</v>
       </c>
       <c r="G130" t="n">
-        <v>77.62</v>
+        <v>132.527</v>
       </c>
       <c r="H130" t="n">
-        <v>132.527</v>
+        <v>88</v>
       </c>
       <c r="I130" t="n">
-        <v>88</v>
+        <v>19.91</v>
       </c>
       <c r="J130" t="n">
-        <v>19.91</v>
+        <v>28.2319064734089</v>
       </c>
       <c r="K130" t="n">
-        <v>28.2319064734089</v>
+        <v>12992.8562860075</v>
       </c>
       <c r="L130" t="n">
-        <v>12992.8562860075</v>
-      </c>
-      <c r="M130" t="n">
         <v>12.5193567980791</v>
       </c>
     </row>
@@ -6043,33 +5651,30 @@
         <v>24746.4</v>
       </c>
       <c r="D131" t="n">
-        <v>1367.1</v>
+        <v>78.38</v>
       </c>
       <c r="E131" t="n">
-        <v>78.38</v>
+        <v>43.35</v>
       </c>
       <c r="F131" t="n">
-        <v>43.35</v>
+        <v>79.72</v>
       </c>
       <c r="G131" t="n">
-        <v>79.72</v>
+        <v>150.841</v>
       </c>
       <c r="H131" t="n">
-        <v>150.841</v>
+        <v>88.3</v>
       </c>
       <c r="I131" t="n">
-        <v>88.3</v>
+        <v>18.8</v>
       </c>
       <c r="J131" t="n">
-        <v>18.8</v>
+        <v>28.1444849879285</v>
       </c>
       <c r="K131" t="n">
-        <v>28.1444849879285</v>
+        <v>18152.6674233825</v>
       </c>
       <c r="L131" t="n">
-        <v>18152.6674233825</v>
-      </c>
-      <c r="M131" t="n">
         <v>12.102708320773</v>
       </c>
     </row>
@@ -6086,33 +5691,30 @@
         <v>26382</v>
       </c>
       <c r="D132" t="n">
-        <v>1371.9</v>
+        <v>81.52</v>
       </c>
       <c r="E132" t="n">
-        <v>81.52</v>
+        <v>48.41</v>
       </c>
       <c r="F132" t="n">
-        <v>48.41</v>
+        <v>81.58</v>
       </c>
       <c r="G132" t="n">
-        <v>81.58</v>
+        <v>172.818</v>
       </c>
       <c r="H132" t="n">
-        <v>172.818</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I132" t="n">
-        <v>88.90000000000001</v>
+        <v>22.75</v>
       </c>
       <c r="J132" t="n">
-        <v>22.75</v>
+        <v>28.2791627222047</v>
       </c>
       <c r="K132" t="n">
-        <v>28.2791627222047</v>
+        <v>31265.1075793047</v>
       </c>
       <c r="L132" t="n">
-        <v>31265.1075793047</v>
-      </c>
-      <c r="M132" t="n">
         <v>12.0304039362778</v>
       </c>
     </row>
@@ -6129,33 +5731,30 @@
         <v>26359.5</v>
       </c>
       <c r="D133" t="n">
-        <v>1351.2</v>
+        <v>82.13</v>
       </c>
       <c r="E133" t="n">
-        <v>82.13</v>
+        <v>53.81</v>
       </c>
       <c r="F133" t="n">
-        <v>53.81</v>
+        <v>83.06</v>
       </c>
       <c r="G133" t="n">
-        <v>83.06</v>
+        <v>201.022</v>
       </c>
       <c r="H133" t="n">
-        <v>201.022</v>
+        <v>89.2</v>
       </c>
       <c r="I133" t="n">
-        <v>89.2</v>
+        <v>26.7</v>
       </c>
       <c r="J133" t="n">
-        <v>26.7</v>
+        <v>28.4988545174577</v>
       </c>
       <c r="K133" t="n">
-        <v>28.4988545174577</v>
+        <v>46868.5784678097</v>
       </c>
       <c r="L133" t="n">
-        <v>46868.5784678097</v>
-      </c>
-      <c r="M133" t="n">
         <v>12.0095660933711</v>
       </c>
     </row>
@@ -6172,33 +5771,30 @@
         <v>29277</v>
       </c>
       <c r="D134" t="n">
-        <v>1363.8</v>
+        <v>86.55</v>
       </c>
       <c r="E134" t="n">
-        <v>86.55</v>
+        <v>60</v>
       </c>
       <c r="F134" t="n">
-        <v>60</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="G134" t="n">
-        <v>86.93000000000001</v>
+        <v>221.905</v>
       </c>
       <c r="H134" t="n">
-        <v>221.905</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I134" t="n">
-        <v>89.09999999999999</v>
+        <v>28.75</v>
       </c>
       <c r="J134" t="n">
-        <v>28.75</v>
+        <v>28.712701575387</v>
       </c>
       <c r="K134" t="n">
-        <v>28.712701575387</v>
+        <v>53718.8699534963</v>
       </c>
       <c r="L134" t="n">
-        <v>53718.8699534963</v>
-      </c>
-      <c r="M134" t="n">
         <v>11.508956927432</v>
       </c>
     </row>
@@ -6215,33 +5811,30 @@
         <v>31269.2</v>
       </c>
       <c r="D135" t="n">
-        <v>1415.7</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="E135" t="n">
-        <v>87.70999999999999</v>
+        <v>60.06</v>
       </c>
       <c r="F135" t="n">
-        <v>60.06</v>
+        <v>87.72</v>
       </c>
       <c r="G135" t="n">
-        <v>87.72</v>
+        <v>253.112</v>
       </c>
       <c r="H135" t="n">
-        <v>253.112</v>
+        <v>88.7</v>
       </c>
       <c r="I135" t="n">
-        <v>88.7</v>
+        <v>30.73</v>
       </c>
       <c r="J135" t="n">
-        <v>30.73</v>
+        <v>28.4400438919259</v>
       </c>
       <c r="K135" t="n">
-        <v>28.4400438919259</v>
+        <v>66487.2888104734</v>
       </c>
       <c r="L135" t="n">
-        <v>66487.2888104734</v>
-      </c>
-      <c r="M135" t="n">
         <v>12.9963941333635</v>
       </c>
     </row>
@@ -6258,33 +5851,30 @@
         <v>32930.1</v>
       </c>
       <c r="D136" t="n">
-        <v>1435.5</v>
+        <v>88.59</v>
       </c>
       <c r="E136" t="n">
-        <v>88.59</v>
+        <v>60.91</v>
       </c>
       <c r="F136" t="n">
-        <v>60.91</v>
+        <v>88.5</v>
       </c>
       <c r="G136" t="n">
-        <v>88.5</v>
+        <v>271.116</v>
       </c>
       <c r="H136" t="n">
-        <v>271.116</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I136" t="n">
-        <v>88.40000000000001</v>
+        <v>32.71</v>
       </c>
       <c r="J136" t="n">
-        <v>32.71</v>
+        <v>27.9638162516437</v>
       </c>
       <c r="K136" t="n">
-        <v>27.9638162516437</v>
+        <v>96899.7957573953</v>
       </c>
       <c r="L136" t="n">
-        <v>96899.7957573953</v>
-      </c>
-      <c r="M136" t="n">
         <v>14.4028959953361</v>
       </c>
     </row>
@@ -6301,33 +5891,30 @@
         <v>34935.8</v>
       </c>
       <c r="D137" t="n">
-        <v>1455.9</v>
+        <v>90.38</v>
       </c>
       <c r="E137" t="n">
-        <v>90.38</v>
+        <v>64.38</v>
       </c>
       <c r="F137" t="n">
-        <v>64.38</v>
+        <v>89.16</v>
       </c>
       <c r="G137" t="n">
-        <v>89.16</v>
+        <v>285.994</v>
       </c>
       <c r="H137" t="n">
-        <v>285.994</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I137" t="n">
-        <v>88.09999999999999</v>
+        <v>32.71</v>
       </c>
       <c r="J137" t="n">
-        <v>32.71</v>
+        <v>27.8460080234758</v>
       </c>
       <c r="K137" t="n">
-        <v>27.8460080234758</v>
+        <v>98553.18636225459</v>
       </c>
       <c r="L137" t="n">
-        <v>98553.18636225459</v>
-      </c>
-      <c r="M137" t="n">
         <v>17.3245506640985</v>
       </c>
     </row>
@@ -6344,33 +5931,30 @@
         <v>78896.10000000001</v>
       </c>
       <c r="D138" t="n">
-        <v>271.4</v>
+        <v>97.23</v>
       </c>
       <c r="E138" t="n">
-        <v>97.23</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="F138" t="n">
-        <v>79.98999999999999</v>
+        <v>97.36</v>
       </c>
       <c r="G138" t="n">
-        <v>97.36</v>
+        <v>1220.146</v>
       </c>
       <c r="H138" t="n">
-        <v>1220.146</v>
+        <v>69.5</v>
       </c>
       <c r="I138" t="n">
-        <v>69.5</v>
+        <v>21.4</v>
       </c>
       <c r="J138" t="n">
-        <v>21.4</v>
+        <v>35.9768313229784</v>
       </c>
       <c r="K138" t="n">
-        <v>35.9768313229784</v>
+        <v>43014.3409084811</v>
       </c>
       <c r="L138" t="n">
-        <v>43014.3409084811</v>
-      </c>
-      <c r="M138" t="n">
         <v>6.9688410293022</v>
       </c>
     </row>
@@ -6387,33 +5971,30 @@
         <v>78985.2</v>
       </c>
       <c r="D139" t="n">
-        <v>279.5</v>
+        <v>92.98999999999999</v>
       </c>
       <c r="E139" t="n">
-        <v>92.98999999999999</v>
+        <v>71.81</v>
       </c>
       <c r="F139" t="n">
-        <v>71.81</v>
+        <v>96.52</v>
       </c>
       <c r="G139" t="n">
-        <v>96.52</v>
+        <v>1170.256</v>
       </c>
       <c r="H139" t="n">
-        <v>1170.256</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I139" t="n">
-        <v>72.40000000000001</v>
+        <v>21.4</v>
       </c>
       <c r="J139" t="n">
-        <v>21.4</v>
+        <v>36.8853200372964</v>
       </c>
       <c r="K139" t="n">
-        <v>36.8853200372964</v>
+        <v>43151.5749650465</v>
       </c>
       <c r="L139" t="n">
-        <v>43151.5749650465</v>
-      </c>
-      <c r="M139" t="n">
         <v>6.97324123677991</v>
       </c>
     </row>
@@ -6430,33 +6011,30 @@
         <v>78744.5</v>
       </c>
       <c r="D140" t="n">
-        <v>288.5</v>
+        <v>95.2</v>
       </c>
       <c r="E140" t="n">
-        <v>95.2</v>
+        <v>72.13</v>
       </c>
       <c r="F140" t="n">
-        <v>72.13</v>
+        <v>96.42</v>
       </c>
       <c r="G140" t="n">
-        <v>96.42</v>
+        <v>1201.836</v>
       </c>
       <c r="H140" t="n">
-        <v>1201.836</v>
+        <v>73.3</v>
       </c>
       <c r="I140" t="n">
-        <v>73.3</v>
+        <v>23.25</v>
       </c>
       <c r="J140" t="n">
-        <v>23.25</v>
+        <v>37.3611453762962</v>
       </c>
       <c r="K140" t="n">
-        <v>37.3611453762962</v>
+        <v>39864.4518315293</v>
       </c>
       <c r="L140" t="n">
-        <v>39864.4518315293</v>
-      </c>
-      <c r="M140" t="n">
         <v>6.57356994288018</v>
       </c>
     </row>
@@ -6473,33 +6051,30 @@
         <v>77888.8</v>
       </c>
       <c r="D141" t="n">
-        <v>292</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="E141" t="n">
-        <v>93.56999999999999</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="F141" t="n">
-        <v>78.56999999999999</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="G141" t="n">
-        <v>98.45999999999999</v>
+        <v>1129.332</v>
       </c>
       <c r="H141" t="n">
-        <v>1129.332</v>
+        <v>72.8</v>
       </c>
       <c r="I141" t="n">
-        <v>72.8</v>
+        <v>25.1</v>
       </c>
       <c r="J141" t="n">
-        <v>25.1</v>
+        <v>37.2960860898482</v>
       </c>
       <c r="K141" t="n">
-        <v>37.2960860898482</v>
+        <v>44903.4689627058</v>
       </c>
       <c r="L141" t="n">
-        <v>44903.4689627058</v>
-      </c>
-      <c r="M141" t="n">
         <v>5.61923854995663</v>
       </c>
     </row>
@@ -6516,33 +6091,30 @@
         <v>87098.2</v>
       </c>
       <c r="D142" t="n">
-        <v>306.2</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="E142" t="n">
-        <v>99.18000000000001</v>
+        <v>80.97</v>
       </c>
       <c r="F142" t="n">
-        <v>80.97</v>
+        <v>98.66</v>
       </c>
       <c r="G142" t="n">
-        <v>98.66</v>
+        <v>1186.996</v>
       </c>
       <c r="H142" t="n">
-        <v>1186.996</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I142" t="n">
-        <v>74.90000000000001</v>
+        <v>28.63</v>
       </c>
       <c r="J142" t="n">
-        <v>28.63</v>
+        <v>38.0399641403524</v>
       </c>
       <c r="K142" t="n">
-        <v>38.0399641403524</v>
+        <v>49199.7675232477</v>
       </c>
       <c r="L142" t="n">
-        <v>49199.7675232477</v>
-      </c>
-      <c r="M142" t="n">
         <v>6.0752020682151</v>
       </c>
     </row>
@@ -6559,33 +6131,30 @@
         <v>90394.7</v>
       </c>
       <c r="D143" t="n">
-        <v>311.4</v>
+        <v>97.64</v>
       </c>
       <c r="E143" t="n">
-        <v>97.64</v>
+        <v>80.81</v>
       </c>
       <c r="F143" t="n">
-        <v>80.81</v>
+        <v>98.23999999999999</v>
       </c>
       <c r="G143" t="n">
-        <v>98.23999999999999</v>
+        <v>1266.536</v>
       </c>
       <c r="H143" t="n">
-        <v>1266.536</v>
+        <v>75.8</v>
       </c>
       <c r="I143" t="n">
-        <v>75.8</v>
+        <v>30.9</v>
       </c>
       <c r="J143" t="n">
-        <v>30.9</v>
+        <v>38.3269581349215</v>
       </c>
       <c r="K143" t="n">
-        <v>38.3269581349215</v>
+        <v>63898.0375224122</v>
       </c>
       <c r="L143" t="n">
-        <v>63898.0375224122</v>
-      </c>
-      <c r="M143" t="n">
         <v>5.9904603893658</v>
       </c>
     </row>
@@ -6602,33 +6171,30 @@
         <v>95125.39999999999</v>
       </c>
       <c r="D144" t="n">
-        <v>321.1</v>
+        <v>99.06</v>
       </c>
       <c r="E144" t="n">
-        <v>99.06</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="F144" t="n">
-        <v>79.79000000000001</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="G144" t="n">
-        <v>99.34999999999999</v>
+        <v>1311.999</v>
       </c>
       <c r="H144" t="n">
-        <v>1311.999</v>
+        <v>76.3</v>
       </c>
       <c r="I144" t="n">
-        <v>76.3</v>
+        <v>33.17</v>
       </c>
       <c r="J144" t="n">
-        <v>33.17</v>
+        <v>38.3793065082138</v>
       </c>
       <c r="K144" t="n">
-        <v>38.3793065082138</v>
+        <v>60480.4705670513</v>
       </c>
       <c r="L144" t="n">
-        <v>60480.4705670513</v>
-      </c>
-      <c r="M144" t="n">
         <v>5.979250210644</v>
       </c>
     </row>
@@ -6645,33 +6211,30 @@
         <v>97689.39999999999</v>
       </c>
       <c r="D145" t="n">
-        <v>323.2</v>
+        <v>98.84</v>
       </c>
       <c r="E145" t="n">
-        <v>98.84</v>
+        <v>80.36</v>
       </c>
       <c r="F145" t="n">
-        <v>80.36</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="G145" t="n">
-        <v>98.76000000000001</v>
+        <v>1272.717</v>
       </c>
       <c r="H145" t="n">
-        <v>1272.717</v>
+        <v>77.2</v>
       </c>
       <c r="I145" t="n">
-        <v>77.2</v>
+        <v>33.17</v>
       </c>
       <c r="J145" t="n">
-        <v>33.17</v>
+        <v>40.3174570156723</v>
       </c>
       <c r="K145" t="n">
-        <v>40.3174570156723</v>
+        <v>58437.6643250046</v>
       </c>
       <c r="L145" t="n">
-        <v>58437.6643250046</v>
-      </c>
-      <c r="M145" t="n">
         <v>5.0736120319212</v>
       </c>
     </row>
@@ -6688,33 +6251,30 @@
         <v>31415.2</v>
       </c>
       <c r="D146" t="n">
-        <v>220.2</v>
+        <v>84.77</v>
       </c>
       <c r="E146" t="n">
-        <v>84.77</v>
+        <v>52.51</v>
       </c>
       <c r="F146" t="n">
-        <v>52.51</v>
+        <v>80.75</v>
       </c>
       <c r="G146" t="n">
-        <v>80.75</v>
+        <v>143.516</v>
       </c>
       <c r="H146" t="n">
-        <v>143.516</v>
+        <v>55.8</v>
       </c>
       <c r="I146" t="n">
-        <v>55.8</v>
+        <v>32.88</v>
       </c>
       <c r="J146" t="n">
-        <v>32.88</v>
+        <v>38.7512769768028</v>
       </c>
       <c r="K146" t="n">
-        <v>38.7512769768028</v>
+        <v>14129.555175913</v>
       </c>
       <c r="L146" t="n">
-        <v>14129.555175913</v>
-      </c>
-      <c r="M146" t="n">
         <v>30.3770554777466</v>
       </c>
     </row>
@@ -6731,33 +6291,30 @@
         <v>32639.5</v>
       </c>
       <c r="D147" t="n">
-        <v>236.3</v>
+        <v>84.14</v>
       </c>
       <c r="E147" t="n">
-        <v>84.14</v>
+        <v>54.53</v>
       </c>
       <c r="F147" t="n">
-        <v>54.53</v>
+        <v>81.66</v>
       </c>
       <c r="G147" t="n">
-        <v>81.66</v>
+        <v>157.161</v>
       </c>
       <c r="H147" t="n">
-        <v>157.161</v>
+        <v>59</v>
       </c>
       <c r="I147" t="n">
-        <v>59</v>
+        <v>32.88</v>
       </c>
       <c r="J147" t="n">
-        <v>32.88</v>
+        <v>39.5892751744889</v>
       </c>
       <c r="K147" t="n">
-        <v>39.5892751744889</v>
+        <v>14436.777618655</v>
       </c>
       <c r="L147" t="n">
-        <v>14436.777618655</v>
-      </c>
-      <c r="M147" t="n">
         <v>33.0708086421311</v>
       </c>
     </row>
@@ -6774,33 +6331,30 @@
         <v>33381.9</v>
       </c>
       <c r="D148" t="n">
-        <v>251.2</v>
+        <v>86.08</v>
       </c>
       <c r="E148" t="n">
-        <v>86.08</v>
+        <v>57.8</v>
       </c>
       <c r="F148" t="n">
-        <v>57.8</v>
+        <v>85.78</v>
       </c>
       <c r="G148" t="n">
-        <v>85.78</v>
+        <v>162.383</v>
       </c>
       <c r="H148" t="n">
-        <v>162.383</v>
+        <v>61.2</v>
       </c>
       <c r="I148" t="n">
-        <v>61.2</v>
+        <v>40.52</v>
       </c>
       <c r="J148" t="n">
-        <v>40.52</v>
+        <v>40.1799549616579</v>
       </c>
       <c r="K148" t="n">
-        <v>40.1799549616579</v>
+        <v>10843.1630919684</v>
       </c>
       <c r="L148" t="n">
-        <v>10843.1630919684</v>
-      </c>
-      <c r="M148" t="n">
         <v>29.6218204565045</v>
       </c>
     </row>
@@ -6817,33 +6371,30 @@
         <v>31931.9</v>
       </c>
       <c r="D149" t="n">
-        <v>257.9</v>
+        <v>90.36</v>
       </c>
       <c r="E149" t="n">
-        <v>90.36</v>
+        <v>62.81</v>
       </c>
       <c r="F149" t="n">
-        <v>62.81</v>
+        <v>86.86</v>
       </c>
       <c r="G149" t="n">
-        <v>86.86</v>
+        <v>167.436</v>
       </c>
       <c r="H149" t="n">
-        <v>167.436</v>
+        <v>63.1</v>
       </c>
       <c r="I149" t="n">
-        <v>63.1</v>
+        <v>48.16</v>
       </c>
       <c r="J149" t="n">
-        <v>48.16</v>
+        <v>41.1094408219109</v>
       </c>
       <c r="K149" t="n">
-        <v>41.1094408219109</v>
+        <v>14442.5692059982</v>
       </c>
       <c r="L149" t="n">
-        <v>14442.5692059982</v>
-      </c>
-      <c r="M149" t="n">
         <v>35.3377751285137</v>
       </c>
     </row>
@@ -6860,33 +6411,30 @@
         <v>36245.5</v>
       </c>
       <c r="D150" t="n">
-        <v>265.6</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="E150" t="n">
-        <v>90.54000000000001</v>
+        <v>64.62</v>
       </c>
       <c r="F150" t="n">
-        <v>64.62</v>
+        <v>87.47</v>
       </c>
       <c r="G150" t="n">
-        <v>87.47</v>
+        <v>192.833</v>
       </c>
       <c r="H150" t="n">
-        <v>192.833</v>
+        <v>66</v>
       </c>
       <c r="I150" t="n">
-        <v>66</v>
+        <v>52.6</v>
       </c>
       <c r="J150" t="n">
-        <v>52.6</v>
+        <v>42.1830899964911</v>
       </c>
       <c r="K150" t="n">
-        <v>42.1830899964911</v>
+        <v>6185.4675287079</v>
       </c>
       <c r="L150" t="n">
-        <v>6185.4675287079</v>
-      </c>
-      <c r="M150" t="n">
         <v>30.7355590982316</v>
       </c>
     </row>
@@ -6903,33 +6451,30 @@
         <v>37360.9</v>
       </c>
       <c r="D151" t="n">
-        <v>283.3</v>
+        <v>93.39</v>
       </c>
       <c r="E151" t="n">
-        <v>93.39</v>
+        <v>67.64</v>
       </c>
       <c r="F151" t="n">
-        <v>67.64</v>
+        <v>91.54000000000001</v>
       </c>
       <c r="G151" t="n">
-        <v>91.54000000000001</v>
+        <v>201.782</v>
       </c>
       <c r="H151" t="n">
-        <v>201.782</v>
+        <v>68.5</v>
       </c>
       <c r="I151" t="n">
-        <v>68.5</v>
+        <v>57.545</v>
       </c>
       <c r="J151" t="n">
-        <v>57.545</v>
+        <v>43.4449972737186</v>
       </c>
       <c r="K151" t="n">
-        <v>43.4449972737186</v>
+        <v>5102.49231331186</v>
       </c>
       <c r="L151" t="n">
-        <v>5102.49231331186</v>
-      </c>
-      <c r="M151" t="n">
         <v>38.9615851886187</v>
       </c>
     </row>
@@ -6946,33 +6491,30 @@
         <v>41849.7</v>
       </c>
       <c r="D152" t="n">
-        <v>302.3</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="E152" t="n">
-        <v>93.54000000000001</v>
+        <v>68.69</v>
       </c>
       <c r="F152" t="n">
-        <v>68.69</v>
+        <v>92.81</v>
       </c>
       <c r="G152" t="n">
-        <v>92.81</v>
+        <v>223.249</v>
       </c>
       <c r="H152" t="n">
-        <v>223.249</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I152" t="n">
-        <v>70.40000000000001</v>
+        <v>62.49</v>
       </c>
       <c r="J152" t="n">
-        <v>62.49</v>
+        <v>44.282454836797</v>
       </c>
       <c r="K152" t="n">
-        <v>44.282454836797</v>
+        <v>4823.18311994457</v>
       </c>
       <c r="L152" t="n">
-        <v>4823.18311994457</v>
-      </c>
-      <c r="M152" t="n">
         <v>43.2692793209479</v>
       </c>
     </row>
@@ -6989,33 +6531,30 @@
         <v>43913.8</v>
       </c>
       <c r="D153" t="n">
-        <v>316.8</v>
+        <v>95.58</v>
       </c>
       <c r="E153" t="n">
-        <v>95.58</v>
+        <v>68.91</v>
       </c>
       <c r="F153" t="n">
-        <v>68.91</v>
+        <v>93.98</v>
       </c>
       <c r="G153" t="n">
-        <v>93.98</v>
+        <v>223.115</v>
       </c>
       <c r="H153" t="n">
-        <v>223.115</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I153" t="n">
-        <v>70.90000000000001</v>
+        <v>62.49</v>
       </c>
       <c r="J153" t="n">
-        <v>62.49</v>
+        <v>44.5068355303026</v>
       </c>
       <c r="K153" t="n">
-        <v>44.5068355303026</v>
+        <v>4507.36313982494</v>
       </c>
       <c r="L153" t="n">
-        <v>4507.36313982494</v>
-      </c>
-      <c r="M153" t="n">
         <v>45.179167089137</v>
       </c>
     </row>
@@ -7032,33 +6571,30 @@
         <v>38491.7</v>
       </c>
       <c r="D154" t="n">
-        <v>8579.4</v>
+        <v>98.23</v>
       </c>
       <c r="E154" t="n">
-        <v>98.23</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F154" t="n">
-        <v>78.90000000000001</v>
+        <v>95.33</v>
       </c>
       <c r="G154" t="n">
-        <v>95.33</v>
+        <v>941.427</v>
       </c>
       <c r="H154" t="n">
-        <v>941.427</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I154" t="n">
-        <v>73.40000000000001</v>
+        <v>45.05</v>
       </c>
       <c r="J154" t="n">
-        <v>45.05</v>
+        <v>42.0988982620643</v>
       </c>
       <c r="K154" t="n">
-        <v>42.0988982620643</v>
+        <v>70412.1276055238</v>
       </c>
       <c r="L154" t="n">
-        <v>70412.1276055238</v>
-      </c>
-      <c r="M154" t="n">
         <v>22.9219025245367</v>
       </c>
     </row>
@@ -7075,33 +6611,30 @@
         <v>39886.4</v>
       </c>
       <c r="D155" t="n">
-        <v>8774.5</v>
+        <v>98</v>
       </c>
       <c r="E155" t="n">
-        <v>98</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="F155" t="n">
-        <v>79.93000000000001</v>
+        <v>94.66</v>
       </c>
       <c r="G155" t="n">
-        <v>94.66</v>
+        <v>963.501</v>
       </c>
       <c r="H155" t="n">
-        <v>963.501</v>
+        <v>74</v>
       </c>
       <c r="I155" t="n">
-        <v>74</v>
+        <v>45.05</v>
       </c>
       <c r="J155" t="n">
-        <v>45.05</v>
+        <v>42.5152457224727</v>
       </c>
       <c r="K155" t="n">
-        <v>42.5152457224727</v>
+        <v>100581.523830836</v>
       </c>
       <c r="L155" t="n">
-        <v>100581.523830836</v>
-      </c>
-      <c r="M155" t="n">
         <v>22.5132061163246</v>
       </c>
     </row>
@@ -7118,33 +6651,30 @@
         <v>40548</v>
       </c>
       <c r="D156" t="n">
-        <v>8952.6</v>
+        <v>98.41</v>
       </c>
       <c r="E156" t="n">
-        <v>98.41</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="F156" t="n">
-        <v>81.34999999999999</v>
+        <v>96.05</v>
       </c>
       <c r="G156" t="n">
-        <v>96.05</v>
+        <v>1027.649</v>
       </c>
       <c r="H156" t="n">
-        <v>1027.649</v>
+        <v>74.5</v>
       </c>
       <c r="I156" t="n">
-        <v>74.5</v>
+        <v>47.315</v>
       </c>
       <c r="J156" t="n">
-        <v>47.315</v>
+        <v>42.5292659897442</v>
       </c>
       <c r="K156" t="n">
-        <v>42.5292659897442</v>
+        <v>130279.470464876</v>
       </c>
       <c r="L156" t="n">
-        <v>130279.470464876</v>
-      </c>
-      <c r="M156" t="n">
         <v>23.0482346929973</v>
       </c>
     </row>
@@ -7161,33 +6691,30 @@
         <v>39986.8</v>
       </c>
       <c r="D157" t="n">
-        <v>8951.299999999999</v>
+        <v>96.95</v>
       </c>
       <c r="E157" t="n">
-        <v>96.95</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="F157" t="n">
-        <v>86.59999999999999</v>
+        <v>94.02</v>
       </c>
       <c r="G157" t="n">
-        <v>94.02</v>
+        <v>1062.41</v>
       </c>
       <c r="H157" t="n">
-        <v>1062.41</v>
+        <v>76</v>
       </c>
       <c r="I157" t="n">
-        <v>76</v>
+        <v>49.58</v>
       </c>
       <c r="J157" t="n">
-        <v>49.58</v>
+        <v>42.6667277513049</v>
       </c>
       <c r="K157" t="n">
-        <v>42.6667277513049</v>
+        <v>136862.999168649</v>
       </c>
       <c r="L157" t="n">
-        <v>136862.999168649</v>
-      </c>
-      <c r="M157" t="n">
         <v>23.1639760853804</v>
       </c>
     </row>
@@ -7204,33 +6731,30 @@
         <v>43741.8</v>
       </c>
       <c r="D158" t="n">
-        <v>9255.299999999999</v>
+        <v>98.56</v>
       </c>
       <c r="E158" t="n">
-        <v>98.56</v>
+        <v>89.47</v>
       </c>
       <c r="F158" t="n">
-        <v>89.47</v>
+        <v>94.52</v>
       </c>
       <c r="G158" t="n">
-        <v>94.52</v>
+        <v>1130.25</v>
       </c>
       <c r="H158" t="n">
-        <v>1130.25</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I158" t="n">
-        <v>76.40000000000001</v>
+        <v>61.94</v>
       </c>
       <c r="J158" t="n">
-        <v>61.94</v>
+        <v>42.9460563127039</v>
       </c>
       <c r="K158" t="n">
-        <v>42.9460563127039</v>
+        <v>164133.506993994</v>
       </c>
       <c r="L158" t="n">
-        <v>164133.506993994</v>
-      </c>
-      <c r="M158" t="n">
         <v>22.0023211908273</v>
       </c>
     </row>
@@ -7247,33 +6771,30 @@
         <v>48540.1</v>
       </c>
       <c r="D159" t="n">
-        <v>9548</v>
+        <v>98.28</v>
       </c>
       <c r="E159" t="n">
-        <v>98.28</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="F159" t="n">
-        <v>88.20999999999999</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="G159" t="n">
-        <v>94.73999999999999</v>
+        <v>1228.973</v>
       </c>
       <c r="H159" t="n">
-        <v>1228.973</v>
+        <v>77</v>
       </c>
       <c r="I159" t="n">
-        <v>77</v>
+        <v>61.45999999999999</v>
       </c>
       <c r="J159" t="n">
-        <v>61.45999999999999</v>
+        <v>43.5643185557355</v>
       </c>
       <c r="K159" t="n">
-        <v>43.5643185557355</v>
+        <v>181183.789690312</v>
       </c>
       <c r="L159" t="n">
-        <v>181183.789690312</v>
-      </c>
-      <c r="M159" t="n">
         <v>21.9578380124342</v>
       </c>
     </row>
@@ -7290,33 +6811,30 @@
         <v>50214.7</v>
       </c>
       <c r="D160" t="n">
-        <v>9737</v>
+        <v>98.86</v>
       </c>
       <c r="E160" t="n">
-        <v>98.86</v>
+        <v>92.41</v>
       </c>
       <c r="F160" t="n">
-        <v>92.41</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="G160" t="n">
-        <v>99.15000000000001</v>
+        <v>1358.94</v>
       </c>
       <c r="H160" t="n">
-        <v>1358.94</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I160" t="n">
-        <v>76.40000000000001</v>
+        <v>60.98</v>
       </c>
       <c r="J160" t="n">
-        <v>60.98</v>
+        <v>43.2644444744139</v>
       </c>
       <c r="K160" t="n">
-        <v>43.2644444744139</v>
+        <v>194962.867894191</v>
       </c>
       <c r="L160" t="n">
-        <v>194962.867894191</v>
-      </c>
-      <c r="M160" t="n">
         <v>24.5106465274936</v>
       </c>
     </row>
@@ -7333,33 +6851,30 @@
         <v>53449.2</v>
       </c>
       <c r="D161" t="n">
-        <v>9797.6</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="E161" t="n">
-        <v>99.04000000000001</v>
+        <v>94.06</v>
       </c>
       <c r="F161" t="n">
-        <v>94.06</v>
+        <v>99.52</v>
       </c>
       <c r="G161" t="n">
-        <v>99.52</v>
+        <v>1431.087</v>
       </c>
       <c r="H161" t="n">
-        <v>1431.087</v>
+        <v>76.3</v>
       </c>
       <c r="I161" t="n">
-        <v>76.3</v>
+        <v>68.03</v>
       </c>
       <c r="J161" t="n">
-        <v>68.03</v>
+        <v>42.9782483069868</v>
       </c>
       <c r="K161" t="n">
-        <v>42.9782483069868</v>
+        <v>198682.41199523</v>
       </c>
       <c r="L161" t="n">
-        <v>198682.41199523</v>
-      </c>
-      <c r="M161" t="n">
         <v>23.4680052763745</v>
       </c>
     </row>
@@ -7376,33 +6891,30 @@
         <v>20730.1</v>
       </c>
       <c r="D162" t="n">
-        <v>16390.7</v>
+        <v>81.88</v>
       </c>
       <c r="E162" t="n">
-        <v>81.88</v>
+        <v>44.98</v>
       </c>
       <c r="F162" t="n">
-        <v>44.98</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="G162" t="n">
-        <v>75.98999999999999</v>
+        <v>127.302</v>
       </c>
       <c r="H162" t="n">
-        <v>127.302</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I162" t="n">
-        <v>86.09999999999999</v>
+        <v>7.61</v>
       </c>
       <c r="J162" t="n">
-        <v>7.61</v>
+        <v>19.9531726069815</v>
       </c>
       <c r="K162" t="n">
-        <v>19.9531726069815</v>
+        <v>6534.93448528243</v>
       </c>
       <c r="L162" t="n">
-        <v>6534.93448528243</v>
-      </c>
-      <c r="M162" t="n">
         <v>10.6673187252222</v>
       </c>
     </row>
@@ -7419,33 +6931,30 @@
         <v>21945</v>
       </c>
       <c r="D163" t="n">
-        <v>16456.5</v>
+        <v>84.19</v>
       </c>
       <c r="E163" t="n">
-        <v>84.19</v>
+        <v>47.78</v>
       </c>
       <c r="F163" t="n">
-        <v>47.78</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="G163" t="n">
-        <v>77.54000000000001</v>
+        <v>158.479</v>
       </c>
       <c r="H163" t="n">
-        <v>158.479</v>
+        <v>86.5</v>
       </c>
       <c r="I163" t="n">
-        <v>86.5</v>
+        <v>8.76</v>
       </c>
       <c r="J163" t="n">
-        <v>8.76</v>
+        <v>20.5313862679212</v>
       </c>
       <c r="K163" t="n">
-        <v>20.5313862679212</v>
+        <v>16227.0719359574</v>
       </c>
       <c r="L163" t="n">
-        <v>16227.0719359574</v>
-      </c>
-      <c r="M163" t="n">
         <v>10.3950333891095</v>
       </c>
     </row>
@@ -7462,33 +6971,30 @@
         <v>23348</v>
       </c>
       <c r="D164" t="n">
-        <v>16892</v>
+        <v>86.75</v>
       </c>
       <c r="E164" t="n">
-        <v>86.75</v>
+        <v>53.95</v>
       </c>
       <c r="F164" t="n">
-        <v>53.95</v>
+        <v>80.44</v>
       </c>
       <c r="G164" t="n">
-        <v>80.44</v>
+        <v>185.578</v>
       </c>
       <c r="H164" t="n">
-        <v>185.578</v>
+        <v>86.8</v>
       </c>
       <c r="I164" t="n">
-        <v>86.8</v>
+        <v>14.655</v>
       </c>
       <c r="J164" t="n">
-        <v>14.655</v>
+        <v>20.5043205670712</v>
       </c>
       <c r="K164" t="n">
-        <v>20.5043205670712</v>
+        <v>20606.063798754</v>
       </c>
       <c r="L164" t="n">
-        <v>20606.063798754</v>
-      </c>
-      <c r="M164" t="n">
         <v>9.852934836196701</v>
       </c>
     </row>
@@ -7505,33 +7011,30 @@
         <v>23916.5</v>
       </c>
       <c r="D165" t="n">
-        <v>16922.8</v>
+        <v>90.38</v>
       </c>
       <c r="E165" t="n">
-        <v>90.38</v>
+        <v>60.93</v>
       </c>
       <c r="F165" t="n">
-        <v>60.93</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="G165" t="n">
-        <v>83.18000000000001</v>
+        <v>192.129</v>
       </c>
       <c r="H165" t="n">
-        <v>192.129</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I165" t="n">
-        <v>87.09999999999999</v>
+        <v>20.55</v>
       </c>
       <c r="J165" t="n">
-        <v>20.55</v>
+        <v>21.9255858346119</v>
       </c>
       <c r="K165" t="n">
-        <v>21.9255858346119</v>
+        <v>25438.6771123423</v>
       </c>
       <c r="L165" t="n">
-        <v>25438.6771123423</v>
-      </c>
-      <c r="M165" t="n">
         <v>9.86616548997166</v>
       </c>
     </row>
@@ -7548,33 +7051,30 @@
         <v>26197.3</v>
       </c>
       <c r="D166" t="n">
-        <v>17129.8</v>
+        <v>92.42</v>
       </c>
       <c r="E166" t="n">
-        <v>92.42</v>
+        <v>61.17</v>
       </c>
       <c r="F166" t="n">
-        <v>61.17</v>
+        <v>85.37</v>
       </c>
       <c r="G166" t="n">
-        <v>85.37</v>
+        <v>222.608</v>
       </c>
       <c r="H166" t="n">
-        <v>222.608</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I166" t="n">
-        <v>87.09999999999999</v>
+        <v>24.35</v>
       </c>
       <c r="J166" t="n">
-        <v>24.35</v>
+        <v>22.8165643900514</v>
       </c>
       <c r="K166" t="n">
-        <v>22.8165643900514</v>
+        <v>31394.3768568545</v>
       </c>
       <c r="L166" t="n">
-        <v>31394.3768568545</v>
-      </c>
-      <c r="M166" t="n">
         <v>9.445565142809359</v>
       </c>
     </row>
@@ -7591,33 +7091,30 @@
         <v>28144.7</v>
       </c>
       <c r="D167" t="n">
-        <v>17219.3</v>
+        <v>93.33</v>
       </c>
       <c r="E167" t="n">
-        <v>93.33</v>
+        <v>64.58</v>
       </c>
       <c r="F167" t="n">
-        <v>64.58</v>
+        <v>86.94</v>
       </c>
       <c r="G167" t="n">
-        <v>86.94</v>
+        <v>258.591</v>
       </c>
       <c r="H167" t="n">
-        <v>258.591</v>
+        <v>87.3</v>
       </c>
       <c r="I167" t="n">
-        <v>87.3</v>
+        <v>37.675</v>
       </c>
       <c r="J167" t="n">
-        <v>37.675</v>
+        <v>23.8373449056172</v>
       </c>
       <c r="K167" t="n">
-        <v>23.8373449056172</v>
+        <v>34772.62853538</v>
       </c>
       <c r="L167" t="n">
-        <v>34772.62853538</v>
-      </c>
-      <c r="M167" t="n">
         <v>11.6325877772755</v>
       </c>
     </row>
@@ -7634,33 +7131,30 @@
         <v>29518.5</v>
       </c>
       <c r="D168" t="n">
-        <v>17268.5</v>
+        <v>93.3</v>
       </c>
       <c r="E168" t="n">
-        <v>93.3</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="F168" t="n">
-        <v>64.31999999999999</v>
+        <v>86.41</v>
       </c>
       <c r="G168" t="n">
-        <v>86.41</v>
+        <v>318.182</v>
       </c>
       <c r="H168" t="n">
-        <v>318.182</v>
+        <v>88</v>
       </c>
       <c r="I168" t="n">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="J168" t="n">
-        <v>51</v>
+        <v>24.526154479274</v>
       </c>
       <c r="K168" t="n">
-        <v>24.526154479274</v>
+        <v>37340.960521191</v>
       </c>
       <c r="L168" t="n">
-        <v>37340.960521191</v>
-      </c>
-      <c r="M168" t="n">
         <v>12.1223189735947</v>
       </c>
     </row>
@@ -7677,33 +7171,30 @@
         <v>31462.9</v>
       </c>
       <c r="D169" t="n">
-        <v>17190.5</v>
+        <v>95.89</v>
       </c>
       <c r="E169" t="n">
-        <v>95.89</v>
+        <v>67.41</v>
       </c>
       <c r="F169" t="n">
-        <v>67.41</v>
+        <v>88.59</v>
       </c>
       <c r="G169" t="n">
-        <v>88.59</v>
+        <v>326.467</v>
       </c>
       <c r="H169" t="n">
-        <v>326.467</v>
+        <v>88.2</v>
       </c>
       <c r="I169" t="n">
-        <v>88.2</v>
+        <v>51</v>
       </c>
       <c r="J169" t="n">
-        <v>51</v>
+        <v>25.3612522999634</v>
       </c>
       <c r="K169" t="n">
-        <v>25.3612522999634</v>
+        <v>41131.8530670488</v>
       </c>
       <c r="L169" t="n">
-        <v>41131.8530670488</v>
-      </c>
-      <c r="M169" t="n">
         <v>13.5099699026858</v>
       </c>
     </row>
@@ -7720,33 +7211,30 @@
         <v>22559.7</v>
       </c>
       <c r="D170" t="n">
-        <v>4706.8</v>
+        <v>76.94</v>
       </c>
       <c r="E170" t="n">
-        <v>76.94</v>
+        <v>34.08</v>
       </c>
       <c r="F170" t="n">
-        <v>34.08</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="G170" t="n">
-        <v>73.79000000000001</v>
+        <v>249.901</v>
       </c>
       <c r="H170" t="n">
-        <v>249.901</v>
+        <v>48.4</v>
       </c>
       <c r="I170" t="n">
-        <v>48.4</v>
+        <v>19.65</v>
       </c>
       <c r="J170" t="n">
-        <v>19.65</v>
+        <v>34.6016066063915</v>
       </c>
       <c r="K170" t="n">
-        <v>34.6016066063915</v>
+        <v>12464.7825791482</v>
       </c>
       <c r="L170" t="n">
-        <v>12464.7825791482</v>
-      </c>
-      <c r="M170" t="n">
         <v>5.98812595371655</v>
       </c>
     </row>
@@ -7763,33 +7251,30 @@
         <v>23548.4</v>
       </c>
       <c r="D171" t="n">
-        <v>4817</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="E171" t="n">
-        <v>79.43000000000001</v>
+        <v>36.65</v>
       </c>
       <c r="F171" t="n">
-        <v>36.65</v>
+        <v>74.66</v>
       </c>
       <c r="G171" t="n">
-        <v>74.66</v>
+        <v>267.912</v>
       </c>
       <c r="H171" t="n">
-        <v>267.912</v>
+        <v>50.1</v>
       </c>
       <c r="I171" t="n">
-        <v>50.1</v>
+        <v>21.67</v>
       </c>
       <c r="J171" t="n">
-        <v>21.67</v>
+        <v>36.6542819407724</v>
       </c>
       <c r="K171" t="n">
-        <v>36.6542819407724</v>
+        <v>15977.3282734765</v>
       </c>
       <c r="L171" t="n">
-        <v>15977.3282734765</v>
-      </c>
-      <c r="M171" t="n">
         <v>5.28353269409281</v>
       </c>
     </row>
@@ -7806,33 +7291,30 @@
         <v>24464.9</v>
       </c>
       <c r="D172" t="n">
-        <v>4869.2</v>
+        <v>80.94</v>
       </c>
       <c r="E172" t="n">
-        <v>80.94</v>
+        <v>38.72</v>
       </c>
       <c r="F172" t="n">
-        <v>38.72</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="G172" t="n">
-        <v>75.34999999999999</v>
+        <v>289.531</v>
       </c>
       <c r="H172" t="n">
-        <v>289.531</v>
+        <v>52.5</v>
       </c>
       <c r="I172" t="n">
-        <v>52.5</v>
+        <v>23.44</v>
       </c>
       <c r="J172" t="n">
-        <v>23.44</v>
+        <v>38.3605751907072</v>
       </c>
       <c r="K172" t="n">
-        <v>38.3605751907072</v>
+        <v>19150.5894803584</v>
       </c>
       <c r="L172" t="n">
-        <v>19150.5894803584</v>
-      </c>
-      <c r="M172" t="n">
         <v>6.94181475443009</v>
       </c>
     </row>
@@ -7849,33 +7331,30 @@
         <v>22782.1</v>
       </c>
       <c r="D173" t="n">
-        <v>4755.1</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="E173" t="n">
-        <v>84.48999999999999</v>
+        <v>44.5</v>
       </c>
       <c r="F173" t="n">
-        <v>44.5</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="G173" t="n">
-        <v>78.26000000000001</v>
+        <v>311.912</v>
       </c>
       <c r="H173" t="n">
-        <v>311.912</v>
+        <v>54.6</v>
       </c>
       <c r="I173" t="n">
-        <v>54.6</v>
+        <v>25.21</v>
       </c>
       <c r="J173" t="n">
-        <v>25.21</v>
+        <v>40.1215406866329</v>
       </c>
       <c r="K173" t="n">
-        <v>40.1215406866329</v>
+        <v>22178.9068183498</v>
       </c>
       <c r="L173" t="n">
-        <v>22178.9068183498</v>
-      </c>
-      <c r="M173" t="n">
         <v>7.1147115711238</v>
       </c>
     </row>
@@ -7892,33 +7371,30 @@
         <v>24550.2</v>
       </c>
       <c r="D174" t="n">
-        <v>4757.1</v>
+        <v>87.34</v>
       </c>
       <c r="E174" t="n">
-        <v>87.34</v>
+        <v>51.59</v>
       </c>
       <c r="F174" t="n">
-        <v>51.59</v>
+        <v>82.31</v>
       </c>
       <c r="G174" t="n">
-        <v>82.31</v>
+        <v>347.228</v>
       </c>
       <c r="H174" t="n">
-        <v>347.228</v>
+        <v>57.4</v>
       </c>
       <c r="I174" t="n">
-        <v>57.4</v>
+        <v>28.86</v>
       </c>
       <c r="J174" t="n">
-        <v>28.86</v>
+        <v>41.5145728650954</v>
       </c>
       <c r="K174" t="n">
-        <v>41.5145728650954</v>
+        <v>24123.9217277333</v>
       </c>
       <c r="L174" t="n">
-        <v>24123.9217277333</v>
-      </c>
-      <c r="M174" t="n">
         <v>6.250331404512</v>
       </c>
     </row>
@@ -7935,33 +7411,30 @@
         <v>27841.5</v>
       </c>
       <c r="D175" t="n">
-        <v>4908.8</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="E175" t="n">
-        <v>88.15000000000001</v>
+        <v>53.53</v>
       </c>
       <c r="F175" t="n">
-        <v>53.53</v>
+        <v>84.5</v>
       </c>
       <c r="G175" t="n">
-        <v>84.5</v>
+        <v>395.747</v>
       </c>
       <c r="H175" t="n">
-        <v>395.747</v>
+        <v>58.5</v>
       </c>
       <c r="I175" t="n">
-        <v>58.5</v>
+        <v>31.26</v>
       </c>
       <c r="J175" t="n">
-        <v>31.26</v>
+        <v>42.937003513367</v>
       </c>
       <c r="K175" t="n">
-        <v>42.937003513367</v>
+        <v>27622.7553426515</v>
       </c>
       <c r="L175" t="n">
-        <v>27622.7553426515</v>
-      </c>
-      <c r="M175" t="n">
         <v>6.99049160072585</v>
       </c>
     </row>
@@ -7978,33 +7451,30 @@
         <v>31106.3</v>
       </c>
       <c r="D176" t="n">
-        <v>5016.7</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="E176" t="n">
-        <v>89.01000000000001</v>
+        <v>54.75</v>
       </c>
       <c r="F176" t="n">
-        <v>54.75</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="G176" t="n">
-        <v>85.79000000000001</v>
+        <v>431.797</v>
       </c>
       <c r="H176" t="n">
-        <v>431.797</v>
+        <v>58.9</v>
       </c>
       <c r="I176" t="n">
-        <v>58.9</v>
+        <v>33.66</v>
       </c>
       <c r="J176" t="n">
-        <v>33.66</v>
+        <v>44.1107426914567</v>
       </c>
       <c r="K176" t="n">
-        <v>44.1107426914567</v>
+        <v>28927.204260395</v>
       </c>
       <c r="L176" t="n">
-        <v>28927.204260395</v>
-      </c>
-      <c r="M176" t="n">
         <v>6.71084167998399</v>
       </c>
     </row>
@@ -8021,33 +7491,30 @@
         <v>32937</v>
       </c>
       <c r="D177" t="n">
-        <v>5083.4</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="E177" t="n">
-        <v>90.59999999999999</v>
+        <v>59.3</v>
       </c>
       <c r="F177" t="n">
-        <v>59.3</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="G177" t="n">
-        <v>88.48999999999999</v>
+        <v>471.832</v>
       </c>
       <c r="H177" t="n">
-        <v>471.832</v>
+        <v>61.3</v>
       </c>
       <c r="I177" t="n">
-        <v>61.3</v>
+        <v>33.66</v>
       </c>
       <c r="J177" t="n">
-        <v>33.66</v>
+        <v>45.2439221846256</v>
       </c>
       <c r="K177" t="n">
-        <v>45.2439221846256</v>
+        <v>28710.2532558007</v>
       </c>
       <c r="L177" t="n">
-        <v>28710.2532558007</v>
-      </c>
-      <c r="M177" t="n">
         <v>6.77343918950435</v>
       </c>
     </row>
@@ -8064,33 +7531,30 @@
         <v>18502.8</v>
       </c>
       <c r="D178" t="n">
-        <v>8670.6</v>
+        <v>76.45</v>
       </c>
       <c r="E178" t="n">
-        <v>76.45</v>
+        <v>16.06</v>
       </c>
       <c r="F178" t="n">
-        <v>16.06</v>
+        <v>63.75</v>
       </c>
       <c r="G178" t="n">
-        <v>63.75</v>
+        <v>48.102</v>
       </c>
       <c r="H178" t="n">
-        <v>48.102</v>
+        <v>73</v>
       </c>
       <c r="I178" t="n">
-        <v>73</v>
+        <v>9.51</v>
       </c>
       <c r="J178" t="n">
-        <v>9.51</v>
+        <v>24.148941859633</v>
       </c>
       <c r="K178" t="n">
-        <v>24.148941859633</v>
+        <v>12254.4025986391</v>
       </c>
       <c r="L178" t="n">
-        <v>12254.4025986391</v>
-      </c>
-      <c r="M178" t="n">
         <v>9.779597384790421</v>
       </c>
     </row>
@@ -8107,33 +7571,30 @@
         <v>19915.4</v>
       </c>
       <c r="D179" t="n">
-        <v>8688.5</v>
+        <v>80.89</v>
       </c>
       <c r="E179" t="n">
-        <v>80.89</v>
+        <v>19.81</v>
       </c>
       <c r="F179" t="n">
-        <v>19.81</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="G179" t="n">
-        <v>70.68000000000001</v>
+        <v>52.462</v>
       </c>
       <c r="H179" t="n">
-        <v>52.462</v>
+        <v>73.7</v>
       </c>
       <c r="I179" t="n">
-        <v>73.7</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="J179" t="n">
-        <v>9.130000000000001</v>
+        <v>25.9702175828069</v>
       </c>
       <c r="K179" t="n">
-        <v>25.9702175828069</v>
+        <v>15938.0958274045</v>
       </c>
       <c r="L179" t="n">
-        <v>15938.0958274045</v>
-      </c>
-      <c r="M179" t="n">
         <v>10.0771915943775</v>
       </c>
     </row>
@@ -8150,33 +7611,30 @@
         <v>21713.9</v>
       </c>
       <c r="D180" t="n">
-        <v>8680.299999999999</v>
+        <v>83.61</v>
       </c>
       <c r="E180" t="n">
-        <v>83.61</v>
+        <v>23.46</v>
       </c>
       <c r="F180" t="n">
-        <v>23.46</v>
+        <v>73.66</v>
       </c>
       <c r="G180" t="n">
-        <v>73.66</v>
+        <v>54.982</v>
       </c>
       <c r="H180" t="n">
-        <v>54.982</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I180" t="n">
-        <v>74.90000000000001</v>
+        <v>11.72</v>
       </c>
       <c r="J180" t="n">
-        <v>11.72</v>
+        <v>27.060557570268</v>
       </c>
       <c r="K180" t="n">
-        <v>27.060557570268</v>
+        <v>19164.605923048</v>
       </c>
       <c r="L180" t="n">
-        <v>19164.605923048</v>
-      </c>
-      <c r="M180" t="n">
         <v>11.0725693077429</v>
       </c>
     </row>
@@ -8193,33 +7651,30 @@
         <v>21808.9</v>
       </c>
       <c r="D181" t="n">
-        <v>8521.1</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="E181" t="n">
-        <v>86.23999999999999</v>
+        <v>37.86</v>
       </c>
       <c r="F181" t="n">
-        <v>37.86</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="G181" t="n">
-        <v>78.45999999999999</v>
+        <v>53.086</v>
       </c>
       <c r="H181" t="n">
-        <v>53.086</v>
+        <v>76.3</v>
       </c>
       <c r="I181" t="n">
-        <v>76.3</v>
+        <v>14.31</v>
       </c>
       <c r="J181" t="n">
-        <v>14.31</v>
+        <v>29.314080636148</v>
       </c>
       <c r="K181" t="n">
-        <v>29.314080636148</v>
+        <v>21374.339808723</v>
       </c>
       <c r="L181" t="n">
-        <v>21374.339808723</v>
-      </c>
-      <c r="M181" t="n">
         <v>11.9370424850698</v>
       </c>
     </row>
@@ -8236,33 +7691,30 @@
         <v>23919.2</v>
       </c>
       <c r="D182" t="n">
-        <v>7746.2</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="E182" t="n">
-        <v>88.73999999999999</v>
+        <v>38.49</v>
       </c>
       <c r="F182" t="n">
-        <v>38.49</v>
+        <v>83.59</v>
       </c>
       <c r="G182" t="n">
-        <v>83.59</v>
+        <v>59.434</v>
       </c>
       <c r="H182" t="n">
-        <v>59.434</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I182" t="n">
-        <v>78.40000000000001</v>
+        <v>12.61</v>
       </c>
       <c r="J182" t="n">
-        <v>12.61</v>
+        <v>31.6949603653045</v>
       </c>
       <c r="K182" t="n">
-        <v>31.6949603653045</v>
+        <v>23316.8405138798</v>
       </c>
       <c r="L182" t="n">
-        <v>23316.8405138798</v>
-      </c>
-      <c r="M182" t="n">
         <v>11.4879408346099</v>
       </c>
     </row>
@@ -8279,33 +7731,30 @@
         <v>25908</v>
       </c>
       <c r="D183" t="n">
-        <v>7798.9</v>
+        <v>89.41</v>
       </c>
       <c r="E183" t="n">
-        <v>89.41</v>
+        <v>45.73</v>
       </c>
       <c r="F183" t="n">
-        <v>45.73</v>
+        <v>85.5</v>
       </c>
       <c r="G183" t="n">
-        <v>85.5</v>
+        <v>68.467</v>
       </c>
       <c r="H183" t="n">
-        <v>68.467</v>
+        <v>79.3</v>
       </c>
       <c r="I183" t="n">
-        <v>79.3</v>
+        <v>14.46</v>
       </c>
       <c r="J183" t="n">
-        <v>14.46</v>
+        <v>33.2115600895132</v>
       </c>
       <c r="K183" t="n">
-        <v>33.2115600895132</v>
+        <v>24738.0607671931</v>
       </c>
       <c r="L183" t="n">
-        <v>24738.0607671931</v>
-      </c>
-      <c r="M183" t="n">
         <v>11.85733755602</v>
       </c>
     </row>
@@ -8322,33 +7771,30 @@
         <v>28714.8</v>
       </c>
       <c r="D184" t="n">
-        <v>7689.3</v>
+        <v>92</v>
       </c>
       <c r="E184" t="n">
-        <v>92</v>
+        <v>50.3</v>
       </c>
       <c r="F184" t="n">
-        <v>50.3</v>
+        <v>89.2</v>
       </c>
       <c r="G184" t="n">
-        <v>89.2</v>
+        <v>87.932</v>
       </c>
       <c r="H184" t="n">
-        <v>87.932</v>
+        <v>77.7</v>
       </c>
       <c r="I184" t="n">
-        <v>77.7</v>
+        <v>16.31</v>
       </c>
       <c r="J184" t="n">
-        <v>16.31</v>
+        <v>34.6706189336505</v>
       </c>
       <c r="K184" t="n">
-        <v>34.6706189336505</v>
+        <v>26834.6013459271</v>
       </c>
       <c r="L184" t="n">
-        <v>26834.6013459271</v>
-      </c>
-      <c r="M184" t="n">
         <v>12.6747408327123</v>
       </c>
     </row>
@@ -8365,33 +7811,30 @@
         <v>30769.4</v>
       </c>
       <c r="D185" t="n">
-        <v>7847.3</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="E185" t="n">
-        <v>94.56999999999999</v>
+        <v>56.12</v>
       </c>
       <c r="F185" t="n">
-        <v>56.12</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="G185" t="n">
-        <v>91.29000000000001</v>
+        <v>85.182</v>
       </c>
       <c r="H185" t="n">
-        <v>85.182</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>77.59999999999999</v>
+        <v>16.31</v>
       </c>
       <c r="J185" t="n">
-        <v>16.31</v>
+        <v>35.7995871488999</v>
       </c>
       <c r="K185" t="n">
-        <v>35.7995871488999</v>
+        <v>27229.5998846093</v>
       </c>
       <c r="L185" t="n">
-        <v>27229.5998846093</v>
-      </c>
-      <c r="M185" t="n">
         <v>13.4497511493721</v>
       </c>
     </row>
@@ -8408,33 +7851,30 @@
         <v>20778.3</v>
       </c>
       <c r="D186" t="n">
-        <v>2529.7</v>
+        <v>81.33</v>
       </c>
       <c r="E186" t="n">
-        <v>81.33</v>
+        <v>58.53</v>
       </c>
       <c r="F186" t="n">
-        <v>58.53</v>
+        <v>81.63</v>
       </c>
       <c r="G186" t="n">
-        <v>81.63</v>
+        <v>137.794</v>
       </c>
       <c r="H186" t="n">
-        <v>137.794</v>
+        <v>85.2</v>
       </c>
       <c r="I186" t="n">
-        <v>85.2</v>
+        <v>20.67</v>
       </c>
       <c r="J186" t="n">
-        <v>20.67</v>
+        <v>25.8590797873319</v>
       </c>
       <c r="K186" t="n">
-        <v>25.8590797873319</v>
+        <v>6963.66692944886</v>
       </c>
       <c r="L186" t="n">
-        <v>6963.66692944886</v>
-      </c>
-      <c r="M186" t="n">
         <v>11.7654202302728</v>
       </c>
     </row>
@@ -8451,33 +7891,30 @@
         <v>21370.9</v>
       </c>
       <c r="D187" t="n">
-        <v>2565.3</v>
+        <v>80.84</v>
       </c>
       <c r="E187" t="n">
-        <v>80.84</v>
+        <v>59</v>
       </c>
       <c r="F187" t="n">
-        <v>59</v>
+        <v>80.45</v>
       </c>
       <c r="G187" t="n">
-        <v>80.45</v>
+        <v>137.963</v>
       </c>
       <c r="H187" t="n">
-        <v>137.963</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I187" t="n">
-        <v>85.59999999999999</v>
+        <v>18.9</v>
       </c>
       <c r="J187" t="n">
-        <v>18.9</v>
+        <v>27.6953839189658</v>
       </c>
       <c r="K187" t="n">
-        <v>27.6953839189658</v>
+        <v>12993.3863567974</v>
       </c>
       <c r="L187" t="n">
-        <v>12993.3863567974</v>
-      </c>
-      <c r="M187" t="n">
         <v>10.6364834767426</v>
       </c>
     </row>
@@ -8494,33 +7931,30 @@
         <v>22107.4</v>
       </c>
       <c r="D188" t="n">
-        <v>2581.6</v>
+        <v>82.19</v>
       </c>
       <c r="E188" t="n">
-        <v>82.19</v>
+        <v>60.18</v>
       </c>
       <c r="F188" t="n">
-        <v>60.18</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="G188" t="n">
-        <v>82.84999999999999</v>
+        <v>142.482</v>
       </c>
       <c r="H188" t="n">
-        <v>142.482</v>
+        <v>85.5</v>
       </c>
       <c r="I188" t="n">
-        <v>85.5</v>
+        <v>20.775</v>
       </c>
       <c r="J188" t="n">
-        <v>20.775</v>
+        <v>29.181106904051</v>
       </c>
       <c r="K188" t="n">
-        <v>29.181106904051</v>
+        <v>20091.3176707558</v>
       </c>
       <c r="L188" t="n">
-        <v>20091.3176707558</v>
-      </c>
-      <c r="M188" t="n">
         <v>9.912388827026261</v>
       </c>
     </row>
@@ -8537,33 +7971,30 @@
         <v>22561.3</v>
       </c>
       <c r="D189" t="n">
-        <v>2529.1</v>
+        <v>85.78</v>
       </c>
       <c r="E189" t="n">
-        <v>85.78</v>
+        <v>62.45</v>
       </c>
       <c r="F189" t="n">
-        <v>62.45</v>
+        <v>89.92</v>
       </c>
       <c r="G189" t="n">
-        <v>89.92</v>
+        <v>153.71</v>
       </c>
       <c r="H189" t="n">
-        <v>153.71</v>
+        <v>86.5</v>
       </c>
       <c r="I189" t="n">
-        <v>86.5</v>
+        <v>22.65</v>
       </c>
       <c r="J189" t="n">
-        <v>22.65</v>
+        <v>31.192548373756</v>
       </c>
       <c r="K189" t="n">
-        <v>31.192548373756</v>
+        <v>25918.3886941279</v>
       </c>
       <c r="L189" t="n">
-        <v>25918.3886941279</v>
-      </c>
-      <c r="M189" t="n">
         <v>9.997414467981139</v>
       </c>
     </row>
@@ -8580,33 +8011,30 @@
         <v>24479.7</v>
       </c>
       <c r="D190" t="n">
-        <v>2559.4</v>
+        <v>89.95999999999999</v>
       </c>
       <c r="E190" t="n">
-        <v>89.95999999999999</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="F190" t="n">
-        <v>75.31999999999999</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="G190" t="n">
-        <v>88.93000000000001</v>
+        <v>168.202</v>
       </c>
       <c r="H190" t="n">
-        <v>168.202</v>
+        <v>86.8</v>
       </c>
       <c r="I190" t="n">
-        <v>86.8</v>
+        <v>32.55</v>
       </c>
       <c r="J190" t="n">
-        <v>32.55</v>
+        <v>32.6060735005904</v>
       </c>
       <c r="K190" t="n">
-        <v>32.6060735005904</v>
+        <v>31322.794798914</v>
       </c>
       <c r="L190" t="n">
-        <v>31322.794798914</v>
-      </c>
-      <c r="M190" t="n">
         <v>9.00138940151075</v>
       </c>
     </row>
@@ -8623,33 +8051,30 @@
         <v>25517.4</v>
       </c>
       <c r="D191" t="n">
-        <v>2601</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="E191" t="n">
-        <v>90.65000000000001</v>
+        <v>76.72</v>
       </c>
       <c r="F191" t="n">
-        <v>76.72</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="G191" t="n">
-        <v>89.06999999999999</v>
+        <v>197.802</v>
       </c>
       <c r="H191" t="n">
-        <v>197.802</v>
+        <v>87.2</v>
       </c>
       <c r="I191" t="n">
-        <v>87.2</v>
+        <v>31.295</v>
       </c>
       <c r="J191" t="n">
-        <v>31.295</v>
+        <v>33.9988127597088</v>
       </c>
       <c r="K191" t="n">
-        <v>33.9988127597088</v>
+        <v>36900.6169648393</v>
       </c>
       <c r="L191" t="n">
-        <v>36900.6169648393</v>
-      </c>
-      <c r="M191" t="n">
         <v>8.490416014205969</v>
       </c>
     </row>
@@ -8666,33 +8091,30 @@
         <v>28486.6</v>
       </c>
       <c r="D192" t="n">
-        <v>2607.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="E192" t="n">
-        <v>90.59999999999999</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="F192" t="n">
-        <v>76.81999999999999</v>
+        <v>87.20999999999999</v>
       </c>
       <c r="G192" t="n">
-        <v>87.20999999999999</v>
+        <v>235.765</v>
       </c>
       <c r="H192" t="n">
-        <v>235.765</v>
+        <v>87.2</v>
       </c>
       <c r="I192" t="n">
-        <v>87.2</v>
+        <v>30.04</v>
       </c>
       <c r="J192" t="n">
-        <v>30.04</v>
+        <v>33.17259432898</v>
       </c>
       <c r="K192" t="n">
-        <v>33.17259432898</v>
+        <v>39911.9913612961</v>
       </c>
       <c r="L192" t="n">
-        <v>39911.9913612961</v>
-      </c>
-      <c r="M192" t="n">
         <v>9.718458465991301</v>
       </c>
     </row>
@@ -8709,33 +8131,30 @@
         <v>29808.1</v>
       </c>
       <c r="D193" t="n">
-        <v>2617.9</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="E193" t="n">
-        <v>90.54000000000001</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F193" t="n">
-        <v>78.18000000000001</v>
+        <v>89.83</v>
       </c>
       <c r="G193" t="n">
-        <v>89.83</v>
+        <v>235.735</v>
       </c>
       <c r="H193" t="n">
-        <v>235.735</v>
+        <v>87.3</v>
       </c>
       <c r="I193" t="n">
-        <v>87.3</v>
+        <v>30.04</v>
       </c>
       <c r="J193" t="n">
-        <v>30.04</v>
+        <v>33.8136036435218</v>
       </c>
       <c r="K193" t="n">
-        <v>33.8136036435218</v>
+        <v>43287.3502716398</v>
       </c>
       <c r="L193" t="n">
-        <v>43287.3502716398</v>
-      </c>
-      <c r="M193" t="n">
         <v>10.5935553645599</v>
       </c>
     </row>
@@ -8752,33 +8171,30 @@
         <v>24858</v>
       </c>
       <c r="D194" t="n">
-        <v>955.9</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="E194" t="n">
-        <v>81.73999999999999</v>
+        <v>45.83</v>
       </c>
       <c r="F194" t="n">
-        <v>45.83</v>
+        <v>78.89</v>
       </c>
       <c r="G194" t="n">
-        <v>78.89</v>
+        <v>388.35</v>
       </c>
       <c r="H194" t="n">
-        <v>388.35</v>
+        <v>83.3</v>
       </c>
       <c r="I194" t="n">
-        <v>83.3</v>
+        <v>18.49</v>
       </c>
       <c r="J194" t="n">
-        <v>18.49</v>
+        <v>29.180424842781</v>
       </c>
       <c r="K194" t="n">
-        <v>29.180424842781</v>
+        <v>19594.093655209</v>
       </c>
       <c r="L194" t="n">
-        <v>19594.093655209</v>
-      </c>
-      <c r="M194" t="n">
         <v>6.50844824804584</v>
       </c>
     </row>
@@ -8795,33 +8211,30 @@
         <v>26214.2</v>
       </c>
       <c r="D195" t="n">
-        <v>976.9</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="E195" t="n">
-        <v>86.68000000000001</v>
+        <v>50.71</v>
       </c>
       <c r="F195" t="n">
-        <v>50.71</v>
+        <v>79.75</v>
       </c>
       <c r="G195" t="n">
-        <v>79.75</v>
+        <v>431.919</v>
       </c>
       <c r="H195" t="n">
-        <v>431.919</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I195" t="n">
-        <v>83.59999999999999</v>
+        <v>22.54</v>
       </c>
       <c r="J195" t="n">
-        <v>22.54</v>
+        <v>29.6086313428343</v>
       </c>
       <c r="K195" t="n">
-        <v>29.6086313428343</v>
+        <v>33018.0809626721</v>
       </c>
       <c r="L195" t="n">
-        <v>33018.0809626721</v>
-      </c>
-      <c r="M195" t="n">
         <v>6.83053982321457</v>
       </c>
     </row>
@@ -8838,33 +8251,30 @@
         <v>27550.6</v>
       </c>
       <c r="D196" t="n">
-        <v>980.3</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="E196" t="n">
-        <v>88.95999999999999</v>
+        <v>55.62</v>
       </c>
       <c r="F196" t="n">
-        <v>55.62</v>
+        <v>83.11</v>
       </c>
       <c r="G196" t="n">
-        <v>83.11</v>
+        <v>476.089</v>
       </c>
       <c r="H196" t="n">
-        <v>476.089</v>
+        <v>84.2</v>
       </c>
       <c r="I196" t="n">
-        <v>84.2</v>
+        <v>29.1</v>
       </c>
       <c r="J196" t="n">
-        <v>29.1</v>
+        <v>30.1395433223627</v>
       </c>
       <c r="K196" t="n">
-        <v>30.1395433223627</v>
+        <v>42529.9932723133</v>
       </c>
       <c r="L196" t="n">
-        <v>42529.9932723133</v>
-      </c>
-      <c r="M196" t="n">
         <v>7.35392450360767</v>
       </c>
     </row>
@@ -8881,33 +8291,30 @@
         <v>26676.9</v>
       </c>
       <c r="D197" t="n">
-        <v>975.9</v>
+        <v>89.97</v>
       </c>
       <c r="E197" t="n">
-        <v>89.97</v>
+        <v>62.91</v>
       </c>
       <c r="F197" t="n">
-        <v>62.91</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="G197" t="n">
-        <v>86.59999999999999</v>
+        <v>480.706</v>
       </c>
       <c r="H197" t="n">
-        <v>480.706</v>
+        <v>85.5</v>
       </c>
       <c r="I197" t="n">
-        <v>85.5</v>
+        <v>35.66</v>
       </c>
       <c r="J197" t="n">
-        <v>35.66</v>
+        <v>30.9930132861242</v>
       </c>
       <c r="K197" t="n">
-        <v>30.9930132861242</v>
+        <v>49112.4747255423</v>
       </c>
       <c r="L197" t="n">
-        <v>49112.4747255423</v>
-      </c>
-      <c r="M197" t="n">
         <v>7.79985278570807</v>
       </c>
     </row>
@@ -8924,33 +8331,30 @@
         <v>29298</v>
       </c>
       <c r="D198" t="n">
-        <v>969.6</v>
+        <v>93.04000000000001</v>
       </c>
       <c r="E198" t="n">
-        <v>93.04000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="F198" t="n">
-        <v>71.2</v>
+        <v>89</v>
       </c>
       <c r="G198" t="n">
-        <v>89</v>
+        <v>527.502</v>
       </c>
       <c r="H198" t="n">
-        <v>527.502</v>
+        <v>86.7</v>
       </c>
       <c r="I198" t="n">
-        <v>86.7</v>
+        <v>39.17</v>
       </c>
       <c r="J198" t="n">
-        <v>39.17</v>
+        <v>31.5502669986288</v>
       </c>
       <c r="K198" t="n">
-        <v>31.5502669986288</v>
+        <v>55445.2655711669</v>
       </c>
       <c r="L198" t="n">
-        <v>55445.2655711669</v>
-      </c>
-      <c r="M198" t="n">
         <v>6.20930603257085</v>
       </c>
     </row>
@@ -8967,33 +8371,30 @@
         <v>32340.5</v>
       </c>
       <c r="D199" t="n">
-        <v>984.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="E199" t="n">
-        <v>92.59999999999999</v>
+        <v>62.58</v>
       </c>
       <c r="F199" t="n">
-        <v>62.58</v>
+        <v>88.91</v>
       </c>
       <c r="G199" t="n">
-        <v>88.91</v>
+        <v>567.148</v>
       </c>
       <c r="H199" t="n">
-        <v>567.148</v>
+        <v>86.2</v>
       </c>
       <c r="I199" t="n">
-        <v>86.2</v>
+        <v>37.08</v>
       </c>
       <c r="J199" t="n">
-        <v>37.08</v>
+        <v>32.0104972135392</v>
       </c>
       <c r="K199" t="n">
-        <v>32.0104972135392</v>
+        <v>61863.7776292141</v>
       </c>
       <c r="L199" t="n">
-        <v>61863.7776292141</v>
-      </c>
-      <c r="M199" t="n">
         <v>8.569786439242129</v>
       </c>
     </row>
@@ -9010,33 +8411,30 @@
         <v>35071.5</v>
       </c>
       <c r="D200" t="n">
-        <v>987.8</v>
+        <v>93.72</v>
       </c>
       <c r="E200" t="n">
-        <v>93.72</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="F200" t="n">
-        <v>65.84999999999999</v>
+        <v>90.38</v>
       </c>
       <c r="G200" t="n">
-        <v>90.38</v>
+        <v>644.612</v>
       </c>
       <c r="H200" t="n">
-        <v>644.612</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I200" t="n">
-        <v>83.59999999999999</v>
+        <v>34.99</v>
       </c>
       <c r="J200" t="n">
-        <v>34.99</v>
+        <v>31.8814801387465</v>
       </c>
       <c r="K200" t="n">
-        <v>31.8814801387465</v>
+        <v>63978.5405154822</v>
       </c>
       <c r="L200" t="n">
-        <v>63978.5405154822</v>
-      </c>
-      <c r="M200" t="n">
         <v>8.203455821310261</v>
       </c>
     </row>
@@ -9053,33 +8451,30 @@
         <v>36118.5</v>
       </c>
       <c r="D201" t="n">
-        <v>996.1</v>
+        <v>94.13</v>
       </c>
       <c r="E201" t="n">
-        <v>94.13</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="F201" t="n">
-        <v>66.26000000000001</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="G201" t="n">
-        <v>90.76000000000001</v>
+        <v>686.458</v>
       </c>
       <c r="H201" t="n">
-        <v>686.458</v>
+        <v>83.8</v>
       </c>
       <c r="I201" t="n">
-        <v>83.8</v>
+        <v>34.99</v>
       </c>
       <c r="J201" t="n">
-        <v>34.99</v>
+        <v>34.2332575162942</v>
       </c>
       <c r="K201" t="n">
-        <v>34.2332575162942</v>
+        <v>68783.4915859735</v>
       </c>
       <c r="L201" t="n">
-        <v>68783.4915859735</v>
-      </c>
-      <c r="M201" t="n">
         <v>8.343380343363791</v>
       </c>
     </row>
@@ -9096,33 +8491,30 @@
         <v>27390.8</v>
       </c>
       <c r="D202" t="n">
-        <v>18815.5</v>
+        <v>83.39</v>
       </c>
       <c r="E202" t="n">
-        <v>83.39</v>
+        <v>49.86</v>
       </c>
       <c r="F202" t="n">
-        <v>49.86</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G202" t="n">
-        <v>84.59999999999999</v>
+        <v>302.447</v>
       </c>
       <c r="H202" t="n">
-        <v>302.447</v>
+        <v>58.2</v>
       </c>
       <c r="I202" t="n">
-        <v>58.2</v>
+        <v>20.85</v>
       </c>
       <c r="J202" t="n">
-        <v>20.85</v>
+        <v>31.2964612808116</v>
       </c>
       <c r="K202" t="n">
-        <v>31.2964612808116</v>
+        <v>7250.46311851917</v>
       </c>
       <c r="L202" t="n">
-        <v>7250.46311851917</v>
-      </c>
-      <c r="M202" t="n">
         <v>6.99949013494316</v>
       </c>
     </row>
@@ -9139,33 +8531,30 @@
         <v>27853.5</v>
       </c>
       <c r="D203" t="n">
-        <v>19314.8</v>
+        <v>86.36</v>
       </c>
       <c r="E203" t="n">
-        <v>86.36</v>
+        <v>53.3</v>
       </c>
       <c r="F203" t="n">
-        <v>53.3</v>
+        <v>86.11</v>
       </c>
       <c r="G203" t="n">
-        <v>86.11</v>
+        <v>320.42</v>
       </c>
       <c r="H203" t="n">
-        <v>320.42</v>
+        <v>59.2</v>
       </c>
       <c r="I203" t="n">
-        <v>59.2</v>
+        <v>18.46</v>
       </c>
       <c r="J203" t="n">
-        <v>18.46</v>
+        <v>32.2277444368856</v>
       </c>
       <c r="K203" t="n">
-        <v>32.2277444368856</v>
+        <v>11306.5682447896</v>
       </c>
       <c r="L203" t="n">
-        <v>11306.5682447896</v>
-      </c>
-      <c r="M203" t="n">
         <v>6.76693548745416</v>
       </c>
     </row>
@@ -9182,33 +8571,30 @@
         <v>28663.4</v>
       </c>
       <c r="D204" t="n">
-        <v>19763.7</v>
+        <v>91.44</v>
       </c>
       <c r="E204" t="n">
-        <v>91.44</v>
+        <v>58.01</v>
       </c>
       <c r="F204" t="n">
-        <v>58.01</v>
+        <v>90.72</v>
       </c>
       <c r="G204" t="n">
-        <v>90.72</v>
+        <v>331.891</v>
       </c>
       <c r="H204" t="n">
-        <v>331.891</v>
+        <v>60.4</v>
       </c>
       <c r="I204" t="n">
-        <v>60.4</v>
+        <v>20.325</v>
       </c>
       <c r="J204" t="n">
-        <v>20.325</v>
+        <v>32.9220023670648</v>
       </c>
       <c r="K204" t="n">
-        <v>32.9220023670648</v>
+        <v>17700.6267665434</v>
       </c>
       <c r="L204" t="n">
-        <v>17700.6267665434</v>
-      </c>
-      <c r="M204" t="n">
         <v>6.84640091103014</v>
       </c>
     </row>
@@ -9225,33 +8611,30 @@
         <v>25131.2</v>
       </c>
       <c r="D205" t="n">
-        <v>19187.2</v>
+        <v>95.38</v>
       </c>
       <c r="E205" t="n">
-        <v>95.38</v>
+        <v>62.62</v>
       </c>
       <c r="F205" t="n">
-        <v>62.62</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="G205" t="n">
-        <v>93.20999999999999</v>
+        <v>333.234</v>
       </c>
       <c r="H205" t="n">
-        <v>333.234</v>
+        <v>61.8</v>
       </c>
       <c r="I205" t="n">
-        <v>61.8</v>
+        <v>22.19</v>
       </c>
       <c r="J205" t="n">
-        <v>22.19</v>
+        <v>33.9527590155171</v>
       </c>
       <c r="K205" t="n">
-        <v>33.9527590155171</v>
+        <v>21589.3884182375</v>
       </c>
       <c r="L205" t="n">
-        <v>21589.3884182375</v>
-      </c>
-      <c r="M205" t="n">
         <v>7.76842135531122</v>
       </c>
     </row>
@@ -9268,33 +8651,30 @@
         <v>28285</v>
       </c>
       <c r="D206" t="n">
-        <v>19817.7</v>
+        <v>95.92</v>
       </c>
       <c r="E206" t="n">
-        <v>95.92</v>
+        <v>66.63</v>
       </c>
       <c r="F206" t="n">
-        <v>66.63</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="G206" t="n">
-        <v>93.90000000000001</v>
+        <v>363.902</v>
       </c>
       <c r="H206" t="n">
-        <v>363.902</v>
+        <v>61.7</v>
       </c>
       <c r="I206" t="n">
-        <v>61.7</v>
+        <v>27.36</v>
       </c>
       <c r="J206" t="n">
-        <v>27.36</v>
+        <v>34.9302420932073</v>
       </c>
       <c r="K206" t="n">
-        <v>34.9302420932073</v>
+        <v>24984.2229191447</v>
       </c>
       <c r="L206" t="n">
-        <v>24984.2229191447</v>
-      </c>
-      <c r="M206" t="n">
         <v>9.39320382214351</v>
       </c>
     </row>
@@ -9311,33 +8691,30 @@
         <v>31781.1</v>
       </c>
       <c r="D207" t="n">
-        <v>20533.7</v>
+        <v>96.08</v>
       </c>
       <c r="E207" t="n">
-        <v>96.08</v>
+        <v>67.91</v>
       </c>
       <c r="F207" t="n">
-        <v>67.91</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="G207" t="n">
-        <v>94.48999999999999</v>
+        <v>406.95</v>
       </c>
       <c r="H207" t="n">
-        <v>406.95</v>
+        <v>61.9</v>
       </c>
       <c r="I207" t="n">
-        <v>61.9</v>
+        <v>26.445</v>
       </c>
       <c r="J207" t="n">
-        <v>26.445</v>
+        <v>35.7846414290159</v>
       </c>
       <c r="K207" t="n">
-        <v>35.7846414290159</v>
+        <v>27046.3366105902</v>
       </c>
       <c r="L207" t="n">
-        <v>27046.3366105902</v>
-      </c>
-      <c r="M207" t="n">
         <v>12.5837187911388</v>
       </c>
     </row>
@@ -9354,33 +8731,30 @@
         <v>34767.2</v>
       </c>
       <c r="D208" t="n">
-        <v>21163.4</v>
+        <v>96.45</v>
       </c>
       <c r="E208" t="n">
-        <v>96.45</v>
+        <v>68.88</v>
       </c>
       <c r="F208" t="n">
-        <v>68.88</v>
+        <v>95.45</v>
       </c>
       <c r="G208" t="n">
-        <v>95.45</v>
+        <v>465.405</v>
       </c>
       <c r="H208" t="n">
-        <v>465.405</v>
+        <v>62.3</v>
       </c>
       <c r="I208" t="n">
-        <v>62.3</v>
+        <v>25.53</v>
       </c>
       <c r="J208" t="n">
-        <v>25.53</v>
+        <v>37.2148181549182</v>
       </c>
       <c r="K208" t="n">
-        <v>37.2148181549182</v>
+        <v>28733.8233897512</v>
       </c>
       <c r="L208" t="n">
-        <v>28733.8233897512</v>
-      </c>
-      <c r="M208" t="n">
         <v>9.562535616131109</v>
       </c>
     </row>
@@ -9397,33 +8771,30 @@
         <v>36413</v>
       </c>
       <c r="D209" t="n">
-        <v>21634</v>
+        <v>96.83</v>
       </c>
       <c r="E209" t="n">
-        <v>96.83</v>
+        <v>68.94</v>
       </c>
       <c r="F209" t="n">
-        <v>68.94</v>
+        <v>95.78</v>
       </c>
       <c r="G209" t="n">
-        <v>95.78</v>
+        <v>492.205</v>
       </c>
       <c r="H209" t="n">
-        <v>492.205</v>
+        <v>63</v>
       </c>
       <c r="I209" t="n">
-        <v>63</v>
+        <v>31.41</v>
       </c>
       <c r="J209" t="n">
-        <v>31.41</v>
+        <v>39.2337541858756</v>
       </c>
       <c r="K209" t="n">
-        <v>39.2337541858756</v>
+        <v>29986.3824811398</v>
       </c>
       <c r="L209" t="n">
-        <v>29986.3824811398</v>
-      </c>
-      <c r="M209" t="n">
         <v>9.28447661569937</v>
       </c>
     </row>
@@ -9440,33 +8811,30 @@
         <v>35296.2</v>
       </c>
       <c r="D210" t="n">
-        <v>5021.6</v>
+        <v>94.73</v>
       </c>
       <c r="E210" t="n">
-        <v>94.73</v>
+        <v>80.88</v>
       </c>
       <c r="F210" t="n">
-        <v>80.88</v>
+        <v>96.19</v>
       </c>
       <c r="G210" t="n">
-        <v>96.19</v>
+        <v>1615.006</v>
       </c>
       <c r="H210" t="n">
-        <v>1615.006</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I210" t="n">
-        <v>78.90000000000001</v>
+        <v>54.1</v>
       </c>
       <c r="J210" t="n">
-        <v>54.1</v>
+        <v>38.3266046004608</v>
       </c>
       <c r="K210" t="n">
-        <v>38.3266046004608</v>
+        <v>13619.1203991212</v>
       </c>
       <c r="L210" t="n">
-        <v>13619.1203991212</v>
-      </c>
-      <c r="M210" t="n">
         <v>15.1103424459526</v>
       </c>
     </row>
@@ -9483,33 +8851,30 @@
         <v>35915.6</v>
       </c>
       <c r="D211" t="n">
-        <v>5097.3</v>
+        <v>93.42</v>
       </c>
       <c r="E211" t="n">
-        <v>93.42</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="F211" t="n">
-        <v>77.65000000000001</v>
+        <v>92.08</v>
       </c>
       <c r="G211" t="n">
-        <v>92.08</v>
+        <v>1544.562</v>
       </c>
       <c r="H211" t="n">
-        <v>1544.562</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I211" t="n">
-        <v>79.09999999999999</v>
+        <v>54.1</v>
       </c>
       <c r="J211" t="n">
-        <v>54.1</v>
+        <v>38.7413375683818</v>
       </c>
       <c r="K211" t="n">
-        <v>38.7413375683818</v>
+        <v>18608.4538369414</v>
       </c>
       <c r="L211" t="n">
-        <v>18608.4538369414</v>
-      </c>
-      <c r="M211" t="n">
         <v>14.1643140590828</v>
       </c>
     </row>
@@ -9526,33 +8891,30 @@
         <v>36994.5</v>
       </c>
       <c r="D212" t="n">
-        <v>5131.6</v>
+        <v>96.06</v>
       </c>
       <c r="E212" t="n">
-        <v>96.06</v>
+        <v>82.22</v>
       </c>
       <c r="F212" t="n">
-        <v>82.22</v>
+        <v>97.55</v>
       </c>
       <c r="G212" t="n">
-        <v>97.55</v>
+        <v>1579.087</v>
       </c>
       <c r="H212" t="n">
-        <v>1579.087</v>
+        <v>79.2</v>
       </c>
       <c r="I212" t="n">
-        <v>79.2</v>
+        <v>60.215</v>
       </c>
       <c r="J212" t="n">
-        <v>60.215</v>
+        <v>39.2905524546107</v>
       </c>
       <c r="K212" t="n">
-        <v>39.2905524546107</v>
+        <v>25688.2870684346</v>
       </c>
       <c r="L212" t="n">
-        <v>25688.2870684346</v>
-      </c>
-      <c r="M212" t="n">
         <v>14.5057835745267</v>
       </c>
     </row>
@@ -9569,33 +8931,30 @@
         <v>36665.9</v>
       </c>
       <c r="D213" t="n">
-        <v>5064.3</v>
+        <v>93.94</v>
       </c>
       <c r="E213" t="n">
-        <v>93.94</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="F213" t="n">
-        <v>84.15000000000001</v>
+        <v>97.08</v>
       </c>
       <c r="G213" t="n">
-        <v>97.08</v>
+        <v>1623.759</v>
       </c>
       <c r="H213" t="n">
-        <v>1623.759</v>
+        <v>79.3</v>
       </c>
       <c r="I213" t="n">
-        <v>79.3</v>
+        <v>66.33</v>
       </c>
       <c r="J213" t="n">
-        <v>66.33</v>
+        <v>40.3679810262741</v>
       </c>
       <c r="K213" t="n">
-        <v>40.3679810262741</v>
+        <v>32739.7400787101</v>
       </c>
       <c r="L213" t="n">
-        <v>32739.7400787101</v>
-      </c>
-      <c r="M213" t="n">
         <v>15.1359508380239</v>
       </c>
     </row>
@@ -9612,33 +8971,30 @@
         <v>39670.2</v>
       </c>
       <c r="D214" t="n">
-        <v>5043.9</v>
+        <v>93.23</v>
       </c>
       <c r="E214" t="n">
-        <v>93.23</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="F214" t="n">
-        <v>86.73999999999999</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="G214" t="n">
-        <v>96.76000000000001</v>
+        <v>1772.434</v>
       </c>
       <c r="H214" t="n">
-        <v>1772.434</v>
+        <v>79.8</v>
       </c>
       <c r="I214" t="n">
-        <v>79.8</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="J214" t="n">
-        <v>72.51000000000001</v>
+        <v>40.8351431063991</v>
       </c>
       <c r="K214" t="n">
-        <v>40.8351431063991</v>
+        <v>38601.5068821813</v>
       </c>
       <c r="L214" t="n">
-        <v>38601.5068821813</v>
-      </c>
-      <c r="M214" t="n">
         <v>13.9348317468926</v>
       </c>
     </row>
@@ -9655,33 +9011,30 @@
         <v>40905.5</v>
       </c>
       <c r="D215" t="n">
-        <v>5198.6</v>
+        <v>94.33</v>
       </c>
       <c r="E215" t="n">
-        <v>94.33</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="F215" t="n">
-        <v>85.95999999999999</v>
+        <v>96.81</v>
       </c>
       <c r="G215" t="n">
-        <v>96.81</v>
+        <v>1833.083</v>
       </c>
       <c r="H215" t="n">
-        <v>1833.083</v>
+        <v>80.5</v>
       </c>
       <c r="I215" t="n">
-        <v>80.5</v>
+        <v>70.42500000000001</v>
       </c>
       <c r="J215" t="n">
-        <v>70.42500000000001</v>
+        <v>40.6093424279832</v>
       </c>
       <c r="K215" t="n">
-        <v>40.6093424279832</v>
+        <v>45805.4450768818</v>
       </c>
       <c r="L215" t="n">
-        <v>45805.4450768818</v>
-      </c>
-      <c r="M215" t="n">
         <v>17.2566541363702</v>
       </c>
     </row>
@@ -9698,33 +9051,30 @@
         <v>42507</v>
       </c>
       <c r="D216" t="n">
-        <v>5270.1</v>
+        <v>94.87</v>
       </c>
       <c r="E216" t="n">
-        <v>94.87</v>
+        <v>88.75</v>
       </c>
       <c r="F216" t="n">
-        <v>88.75</v>
+        <v>97.59</v>
       </c>
       <c r="G216" t="n">
-        <v>97.59</v>
+        <v>1851.574</v>
       </c>
       <c r="H216" t="n">
-        <v>1851.574</v>
+        <v>80.8</v>
       </c>
       <c r="I216" t="n">
-        <v>80.8</v>
+        <v>68.34</v>
       </c>
       <c r="J216" t="n">
-        <v>68.34</v>
+        <v>40.7340135908716</v>
       </c>
       <c r="K216" t="n">
-        <v>40.7340135908716</v>
+        <v>52996.3464606147</v>
       </c>
       <c r="L216" t="n">
-        <v>52996.3464606147</v>
-      </c>
-      <c r="M216" t="n">
         <v>17.6238520277113</v>
       </c>
     </row>
@@ -9741,33 +9091,30 @@
         <v>44414.4</v>
       </c>
       <c r="D217" t="n">
-        <v>5241.3</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="E217" t="n">
-        <v>95.43000000000001</v>
+        <v>88.39</v>
       </c>
       <c r="F217" t="n">
-        <v>88.39</v>
+        <v>98.08</v>
       </c>
       <c r="G217" t="n">
-        <v>98.08</v>
+        <v>1885.999</v>
       </c>
       <c r="H217" t="n">
-        <v>1885.999</v>
+        <v>81</v>
       </c>
       <c r="I217" t="n">
-        <v>81</v>
+        <v>68.34</v>
       </c>
       <c r="J217" t="n">
-        <v>68.34</v>
+        <v>40.6156538715616</v>
       </c>
       <c r="K217" t="n">
-        <v>40.6156538715616</v>
+        <v>55097.2595366627</v>
       </c>
       <c r="L217" t="n">
-        <v>55097.2595366627</v>
-      </c>
-      <c r="M217" t="n">
         <v>17.6524551082203</v>
       </c>
     </row>
